--- a/Data/Initial_Database.xlsx
+++ b/Data/Initial_Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jerry\Documents\GitHub\Methane_Prediction\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B4176E-7662-4291-B1C7-50E91EAF85E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628BF0EB-CE40-4EF8-A8EA-F1AEF28AADA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="87">
   <si>
     <t>Paper_Title</t>
   </si>
@@ -134,13 +134,349 @@
   </si>
   <si>
     <t>M209</t>
+  </si>
+  <si>
+    <r>
+      <t>477a (CH4 (kg CH4 ha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1))</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>558a(CH4 (kg CH4 ha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1))</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>394a (CH4 (kg CH4 ha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1))</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Units</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Correct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>212(15) kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>153(8)kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>这个文章所有单位都是g CH4-C ha</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="3"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 day</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="3"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1全部要乘以1.33</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>401 (0.1)</t>
+  </si>
+  <si>
+    <t>401 (0.1)kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>346 (28)</t>
+  </si>
+  <si>
+    <t>346 (28)kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>136 (56)kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>At Arbuckle-20, the herbicide drain led to a decrease in average daily CH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t> flux in the FP</t>
+    </r>
+  </si>
+  <si>
+    <t>57 (6) kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38 (0)</t>
+  </si>
+  <si>
+    <t>38 (0)kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1~3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4~5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6~10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Calmati-202</t>
+  </si>
+  <si>
+    <t>Calmati-203</t>
+  </si>
+  <si>
+    <t>Calmati-204</t>
+  </si>
+  <si>
+    <t>Calmati-205</t>
+  </si>
+  <si>
+    <t>Calmati-206</t>
+  </si>
+  <si>
+    <t>Calmati-207</t>
+  </si>
+  <si>
+    <t>Calmati-208</t>
+  </si>
+  <si>
+    <t>Calmati-209</t>
+  </si>
+  <si>
+    <t>Calmati-210</t>
+  </si>
+  <si>
+    <t>Calmati-211</t>
+  </si>
+  <si>
+    <t>69 (9.6)a kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>58 (2.9)a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60 (12)a kg CH4-C ha-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Original Data (g CH4-C ha-1 day-1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11~13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Original (kg CH4​−C ha−1)</t>
+  </si>
+  <si>
+    <t>Adjusted (kg CH4​ ha−1)</t>
+  </si>
+  <si>
+    <t>212 (15)</t>
+  </si>
+  <si>
+    <t>281.96 (19.95)</t>
+  </si>
+  <si>
+    <t>153 (8)</t>
+  </si>
+  <si>
+    <t>203.49 (10.64)</t>
+  </si>
+  <si>
+    <t>533.33 (0.13)</t>
+  </si>
+  <si>
+    <t>460.18 (37.24)</t>
+  </si>
+  <si>
+    <t>136 (56)</t>
+  </si>
+  <si>
+    <t>180.88 (74.48)</t>
+  </si>
+  <si>
+    <t>57 (6)</t>
+  </si>
+  <si>
+    <t>75.81 (7.98)</t>
+  </si>
+  <si>
+    <t>50.54 (0.00)</t>
+  </si>
+  <si>
+    <t>60 (12)</t>
+  </si>
+  <si>
+    <t>79.80 (15.96)</t>
+  </si>
+  <si>
+    <t>69 (9.6)</t>
+  </si>
+  <si>
+    <t>91.77 (12.77)</t>
+  </si>
+  <si>
+    <t>58 (2.9)</t>
+  </si>
+  <si>
+    <t>77.14 (3.86)</t>
+  </si>
+  <si>
+    <r>
+      <t>at Willows-20, both FP and MD checks were drained for an herbicide application 24 DAS, leading to lower CH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t> fluxes for both treatments</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,16 +519,114 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -200,17 +634,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -493,43 +973,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G241"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M255"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="15.25" customWidth="1"/>
-    <col min="7" max="7" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" customWidth="1"/>
+    <col min="7" max="7" width="39.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2">
+      <c r="H1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="85.5" x14ac:dyDescent="5.0999999999999996">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2">
@@ -547,12 +1034,15 @@
       <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="G2">
-        <v>72936.893200000006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3">
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
       <c r="B3">
@@ -571,8 +1061,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4">
@@ -591,8 +1081,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5">
@@ -611,8 +1101,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>1</v>
       </c>
       <c r="B6">
@@ -631,8 +1121,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <v>1</v>
       </c>
       <c r="B7" s="1">
@@ -651,8 +1141,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="8" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <v>1</v>
       </c>
       <c r="B8" s="1">
@@ -671,8 +1161,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="9" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <v>1</v>
       </c>
       <c r="B9" s="1">
@@ -691,8 +1181,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="10" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <v>1</v>
       </c>
       <c r="B10" s="1">
@@ -711,8 +1201,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A11">
+    <row r="11" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>1</v>
       </c>
       <c r="B11" s="1">
@@ -731,8 +1221,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A12">
+    <row r="12" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <v>1</v>
       </c>
       <c r="B12" s="1">
@@ -751,8 +1241,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A13">
+    <row r="13" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <v>1</v>
       </c>
       <c r="B13" s="1">
@@ -771,8 +1261,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14">
+    <row r="14" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>1</v>
       </c>
       <c r="B14" s="1">
@@ -791,8 +1281,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15">
+    <row r="15" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>1</v>
       </c>
       <c r="B15" s="1">
@@ -811,8 +1301,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16">
+    <row r="16" spans="1:9" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <v>1</v>
       </c>
       <c r="B16" s="1">
@@ -831,8 +1321,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17">
+    <row r="17" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
         <v>1</v>
       </c>
       <c r="B17" s="1">
@@ -851,8 +1341,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="18" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
       <c r="B18" s="1">
@@ -871,8 +1361,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A19">
+    <row r="19" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
         <v>1</v>
       </c>
       <c r="B19" s="1">
@@ -891,8 +1381,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="20" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
         <v>1</v>
       </c>
       <c r="B20" s="1">
@@ -911,8 +1401,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A21">
+    <row r="21" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
         <v>1</v>
       </c>
       <c r="B21" s="1">
@@ -931,8 +1421,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A22">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>1</v>
       </c>
       <c r="B22">
@@ -951,9 +1441,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A23">
-        <v>1</v>
+    <row r="23" spans="1:7" ht="85.5" x14ac:dyDescent="5.0999999999999996">
+      <c r="A23" s="4">
+        <v>2</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -970,13 +1460,13 @@
       <c r="F23" t="s">
         <v>13</v>
       </c>
-      <c r="G23">
-        <v>61043.689319999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A24">
-        <v>1</v>
+      <c r="G23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>2</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -994,9 +1484,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25">
-        <v>1</v>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>2</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1014,9 +1504,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A26">
-        <v>1</v>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>2</v>
       </c>
       <c r="B26">
         <v>849.51456310679305</v>
@@ -1034,9 +1524,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A27">
-        <v>1</v>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>2</v>
       </c>
       <c r="B27">
         <v>1820.3883495145601</v>
@@ -1054,9 +1544,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A28">
-        <v>1</v>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>2</v>
       </c>
       <c r="B28">
         <v>2912.6213592232998</v>
@@ -1074,9 +1564,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A29">
-        <v>1</v>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>2</v>
       </c>
       <c r="B29">
         <v>6067.9611650485404</v>
@@ -1094,9 +1584,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A30">
-        <v>1</v>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>2</v>
       </c>
       <c r="B30">
         <v>3640.7766990291202</v>
@@ -1114,9 +1604,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A31">
-        <v>1</v>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>2</v>
       </c>
       <c r="B31">
         <v>3883.49514563106</v>
@@ -1134,9 +1624,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A32">
-        <v>1</v>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>2</v>
       </c>
       <c r="B32">
         <v>3883.49514563106</v>
@@ -1154,9 +1644,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A33">
-        <v>1</v>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>2</v>
       </c>
       <c r="B33">
         <v>4247.5728155339802</v>
@@ -1174,9 +1664,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A34">
-        <v>1</v>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>2</v>
       </c>
       <c r="B34">
         <v>4975.7281553397997</v>
@@ -1194,9 +1684,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A35">
-        <v>1</v>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>2</v>
       </c>
       <c r="B35">
         <v>5339.8058252427199</v>
@@ -1214,9 +1704,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A36">
-        <v>1</v>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>2</v>
       </c>
       <c r="B36">
         <v>4004.85436893204</v>
@@ -1234,9 +1724,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A37">
-        <v>1</v>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>2</v>
       </c>
       <c r="B37">
         <v>5097.0873786407701</v>
@@ -1254,9 +1744,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A38">
-        <v>1</v>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>2</v>
       </c>
       <c r="B38">
         <v>3883.49514563106</v>
@@ -1274,9 +1764,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A39">
-        <v>1</v>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>2</v>
       </c>
       <c r="B39">
         <v>2669.90291262135</v>
@@ -1294,9 +1784,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A40">
-        <v>1</v>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>2</v>
       </c>
       <c r="B40">
         <v>2427.1844660194101</v>
@@ -1314,9 +1804,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A41">
-        <v>1</v>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>2</v>
       </c>
       <c r="B41">
         <v>1456.3106796116399</v>
@@ -1334,9 +1824,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A42">
-        <v>1</v>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>2</v>
       </c>
       <c r="B42">
         <v>1213.5922330097001</v>
@@ -1354,9 +1844,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A43">
-        <v>1</v>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>2</v>
       </c>
       <c r="B43">
         <v>2548.5436893203801</v>
@@ -1374,9 +1864,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A44">
-        <v>1</v>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>2</v>
       </c>
       <c r="B44">
         <v>121.35922330096901</v>
@@ -1394,9 +1884,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A45">
-        <v>1</v>
+    <row r="45" spans="1:7" ht="85.5" x14ac:dyDescent="5.0999999999999996">
+      <c r="A45" s="4">
+        <v>3</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1413,13 +1903,13 @@
       <c r="F45" t="s">
         <v>13</v>
       </c>
-      <c r="G45">
-        <v>77941.176470000006</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A46">
-        <v>1</v>
+      <c r="G45" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>3</v>
       </c>
       <c r="B46">
         <v>919.11764705882501</v>
@@ -1437,9 +1927,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A47">
-        <v>1</v>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>3</v>
       </c>
       <c r="B47">
         <v>5698.5294117646899</v>
@@ -1457,9 +1947,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A48">
-        <v>1</v>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>3</v>
       </c>
       <c r="B48">
         <v>6250</v>
@@ -1477,9 +1967,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A49">
-        <v>1</v>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>3</v>
       </c>
       <c r="B49">
         <v>6801.4705882352901</v>
@@ -1497,9 +1987,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A50">
-        <v>1</v>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>3</v>
       </c>
       <c r="B50">
         <v>4595.5882352941098</v>
@@ -1517,9 +2007,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A51">
-        <v>1</v>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>3</v>
       </c>
       <c r="B51">
         <v>2573.5294117647099</v>
@@ -1537,9 +2027,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A52">
-        <v>1</v>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>3</v>
       </c>
       <c r="B52">
         <v>7169.1176470588198</v>
@@ -1557,9 +2047,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A53">
-        <v>1</v>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>3</v>
       </c>
       <c r="B53">
         <v>6801.4705882352901</v>
@@ -1577,9 +2067,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A54">
-        <v>1</v>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <v>3</v>
       </c>
       <c r="B54">
         <v>8272.0588235294108</v>
@@ -1597,9 +2087,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A55">
-        <v>1</v>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>3</v>
       </c>
       <c r="B55">
         <v>6617.6470588235297</v>
@@ -1617,9 +2107,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A56">
-        <v>1</v>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <v>3</v>
       </c>
       <c r="B56">
         <v>7352.9411764705801</v>
@@ -1637,9 +2127,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A57">
-        <v>1</v>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>3</v>
       </c>
       <c r="B57">
         <v>3492.6470588235202</v>
@@ -1657,9 +2147,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A58">
-        <v>1</v>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <v>3</v>
       </c>
       <c r="B58">
         <v>2573.5294117647099</v>
@@ -1677,9 +2167,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A59">
-        <v>1</v>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>3</v>
       </c>
       <c r="B59">
         <v>4779.4117647058802</v>
@@ -1697,9 +2187,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A60">
-        <v>1</v>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>3</v>
       </c>
       <c r="B60">
         <v>3676.47058823528</v>
@@ -1717,9 +2207,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A61">
-        <v>1</v>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>3</v>
       </c>
       <c r="B61">
         <v>367.64705882352399</v>
@@ -1737,9 +2227,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A62">
-        <v>1</v>
+    <row r="62" spans="1:8" ht="85.5" x14ac:dyDescent="5.0999999999999996">
+      <c r="A62" s="5">
+        <v>4</v>
       </c>
       <c r="B62">
         <v>40.650406504066197</v>
@@ -1756,13 +2246,16 @@
       <c r="F62" t="s">
         <v>13</v>
       </c>
-      <c r="G62">
-        <v>50609.756099999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A63">
-        <v>1</v>
+      <c r="G62" t="s">
+        <v>37</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>4</v>
       </c>
       <c r="B63">
         <v>1016.26016260162</v>
@@ -1780,9 +2273,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A64">
-        <v>1</v>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>4</v>
       </c>
       <c r="B64">
         <v>1991.8699186991801</v>
@@ -1800,9 +2293,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A65">
-        <v>1</v>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>4</v>
       </c>
       <c r="B65">
         <v>2642.2764227642201</v>
@@ -1820,9 +2313,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A66">
-        <v>1</v>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>4</v>
       </c>
       <c r="B66">
         <v>4756.0975609756097</v>
@@ -1840,9 +2333,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A67">
-        <v>1</v>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>4</v>
       </c>
       <c r="B67">
         <v>3008.1300813008102</v>
@@ -1860,9 +2353,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A68">
-        <v>1</v>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>4</v>
       </c>
       <c r="B68">
         <v>3699.1869918699099</v>
@@ -1880,9 +2373,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A69">
-        <v>1</v>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>4</v>
       </c>
       <c r="B69">
         <v>3170.7317073170698</v>
@@ -1900,9 +2393,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A70">
-        <v>1</v>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>4</v>
       </c>
       <c r="B70">
         <v>3373.9837398373902</v>
@@ -1920,9 +2413,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A71">
-        <v>1</v>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>4</v>
       </c>
       <c r="B71">
         <v>4390.2439024390196</v>
@@ -1940,9 +2433,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A72">
-        <v>1</v>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>4</v>
       </c>
       <c r="B72">
         <v>2967.4796747967498</v>
@@ -1960,9 +2453,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A73">
-        <v>1</v>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>4</v>
       </c>
       <c r="B73">
         <v>2479.67479674796</v>
@@ -1980,9 +2473,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A74">
-        <v>1</v>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>4</v>
       </c>
       <c r="B74">
         <v>2560.9756097560899</v>
@@ -2000,9 +2493,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A75">
-        <v>1</v>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>4</v>
       </c>
       <c r="B75">
         <v>2235.7723577235702</v>
@@ -2020,9 +2513,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A76">
-        <v>1</v>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>4</v>
       </c>
       <c r="B76">
         <v>2398.3739837398298</v>
@@ -2040,9 +2533,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A77">
-        <v>1</v>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>4</v>
       </c>
       <c r="B77">
         <v>2439.0243902439001</v>
@@ -2060,9 +2553,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A78">
-        <v>1</v>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>4</v>
       </c>
       <c r="B78">
         <v>1382.1138211382099</v>
@@ -2080,9 +2573,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A79">
-        <v>1</v>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>4</v>
       </c>
       <c r="B79">
         <v>1544.71544715447</v>
@@ -2100,9 +2593,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A80">
-        <v>1</v>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
+        <v>4</v>
       </c>
       <c r="B80">
         <v>1585.3658536585301</v>
@@ -2120,9 +2613,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A81">
-        <v>1</v>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
+        <v>4</v>
       </c>
       <c r="B81">
         <v>1382.1138211382099</v>
@@ -2140,9 +2633,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A82">
-        <v>1</v>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>4</v>
       </c>
       <c r="B82">
         <v>650.40650406504199</v>
@@ -2160,9 +2653,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A83">
-        <v>1</v>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>4</v>
       </c>
       <c r="B83">
         <v>569.10569105691104</v>
@@ -2180,9 +2673,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A84">
-        <v>1</v>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>4</v>
       </c>
       <c r="B84">
         <v>325.20325203252202</v>
@@ -2200,9 +2693,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A85">
-        <v>1</v>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>5</v>
       </c>
       <c r="B85">
         <v>0.74280408542199405</v>
@@ -2219,13 +2712,13 @@
       <c r="F85" t="s">
         <v>13</v>
       </c>
-      <c r="G85">
-        <v>39164.4692</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A86">
-        <v>1</v>
+      <c r="G85" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>5</v>
       </c>
       <c r="B86">
         <v>51.562983596411797</v>
@@ -2243,9 +2736,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A87">
-        <v>1</v>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>5</v>
       </c>
       <c r="B87">
         <v>286.26844114309199</v>
@@ -2263,9 +2756,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A88">
-        <v>1</v>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
+        <v>5</v>
       </c>
       <c r="B88">
         <v>738.51232848447398</v>
@@ -2283,9 +2776,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A89">
-        <v>1</v>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>5</v>
       </c>
       <c r="B89">
         <v>922.91344269060198</v>
@@ -2303,9 +2796,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A90">
-        <v>1</v>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
+        <v>5</v>
       </c>
       <c r="B90">
         <v>2394.5321365934101</v>
@@ -2323,9 +2816,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A91">
-        <v>1</v>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>5</v>
       </c>
       <c r="B91">
         <v>1926.6687300113399</v>
@@ -2343,9 +2836,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A92">
-        <v>1</v>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
+        <v>5</v>
       </c>
       <c r="B92">
         <v>2277.8912617352698</v>
@@ -2363,9 +2856,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A93">
-        <v>1</v>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>5</v>
       </c>
       <c r="B93">
         <v>2295.0789229340699</v>
@@ -2383,9 +2876,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A94">
-        <v>1</v>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="5">
+        <v>5</v>
       </c>
       <c r="B94">
         <v>2161.6011554730198</v>
@@ -2403,9 +2896,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A95">
-        <v>1</v>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>5</v>
       </c>
       <c r="B95">
         <v>2111.6063138347199</v>
@@ -2423,9 +2916,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A96">
-        <v>1</v>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="5">
+        <v>5</v>
       </c>
       <c r="B96">
         <v>2546.2292375941302</v>
@@ -2443,9 +2936,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A97">
-        <v>1</v>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" s="5">
+        <v>5</v>
       </c>
       <c r="B97">
         <v>2646.8998246156998</v>
@@ -2463,9 +2956,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A98">
-        <v>1</v>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" s="5">
+        <v>5</v>
       </c>
       <c r="B98">
         <v>3282.2036521200798</v>
@@ -2483,9 +2976,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A99">
-        <v>1</v>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="5">
+        <v>5</v>
       </c>
       <c r="B99">
         <v>3901.1864231919899</v>
@@ -2503,9 +2996,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A100">
-        <v>1</v>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="5">
+        <v>5</v>
       </c>
       <c r="B100">
         <v>2263.4478489631701</v>
@@ -2523,9 +3016,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A101">
-        <v>1</v>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
+        <v>5</v>
       </c>
       <c r="B101">
         <v>2130.5684514598101</v>
@@ -2543,9 +3036,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A102">
-        <v>1</v>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="5">
+        <v>5</v>
       </c>
       <c r="B102">
         <v>1028.45352316104</v>
@@ -2563,9 +3056,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A103">
-        <v>1</v>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="5">
+        <v>5</v>
       </c>
       <c r="B103">
         <v>1647.6838955947501</v>
@@ -2583,9 +3076,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A104">
-        <v>1</v>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="5">
+        <v>5</v>
       </c>
       <c r="B104">
         <v>1147.2402764881799</v>
@@ -2603,2766 +3096,4380 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A105">
-        <v>1</v>
-      </c>
-      <c r="B105">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="11">
+        <v>5</v>
+      </c>
+      <c r="B105" s="12">
         <v>61.7146394305191</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="12">
         <v>97.135802469135797</v>
       </c>
-      <c r="D105" t="s">
-        <v>14</v>
-      </c>
-      <c r="E105">
+      <c r="D105" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" s="12">
         <v>2018</v>
       </c>
-      <c r="F105" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A106">
-        <v>1</v>
-      </c>
-      <c r="B106">
+      <c r="F105" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="12"/>
+      <c r="H105" s="12"/>
+      <c r="I105" s="12"/>
+      <c r="J105" s="12"/>
+      <c r="K105" s="12"/>
+      <c r="L105" s="12"/>
+      <c r="M105" s="12"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="11">
+        <v>5</v>
+      </c>
+      <c r="B106" s="12">
         <v>714.37119570824404</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="12">
         <v>104.222222222222</v>
       </c>
-      <c r="D106" t="s">
-        <v>14</v>
-      </c>
-      <c r="E106">
+      <c r="D106" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" s="12">
         <v>2018</v>
       </c>
-      <c r="F106" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A107">
-        <v>1</v>
-      </c>
-      <c r="B107">
+      <c r="F106" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="12"/>
+      <c r="H106" s="12"/>
+      <c r="I106" s="12"/>
+      <c r="J106" s="12"/>
+      <c r="K106" s="12"/>
+      <c r="L106" s="12"/>
+      <c r="M106" s="12"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="11">
+        <v>5</v>
+      </c>
+      <c r="B107" s="12">
         <v>381.05849582172698</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="12">
         <v>112.172839506172</v>
       </c>
-      <c r="D107" t="s">
-        <v>14</v>
-      </c>
-      <c r="E107">
+      <c r="D107" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" s="12">
         <v>2018</v>
       </c>
-      <c r="F107" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A108">
-        <v>1</v>
-      </c>
-      <c r="B108">
+      <c r="F107" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="12"/>
+      <c r="H107" s="12"/>
+      <c r="I107" s="12"/>
+      <c r="J107" s="12"/>
+      <c r="K107" s="12"/>
+      <c r="L107" s="12"/>
+      <c r="M107" s="12"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="11">
+        <v>5</v>
+      </c>
+      <c r="B108" s="12">
         <v>364.69617249561497</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="12">
         <v>115.111111111111</v>
       </c>
-      <c r="D108" t="s">
-        <v>14</v>
-      </c>
-      <c r="E108">
+      <c r="D108" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" s="12">
         <v>2018</v>
       </c>
-      <c r="F108" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A109">
-        <v>1</v>
-      </c>
-      <c r="B109">
+      <c r="F108" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="12"/>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="11">
+        <v>5</v>
+      </c>
+      <c r="B109" s="12">
         <v>348.23068193541798</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="12">
         <v>117.18518518518501</v>
       </c>
-      <c r="D109" t="s">
-        <v>14</v>
-      </c>
-      <c r="E109">
+      <c r="D109" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" s="12">
         <v>2018</v>
       </c>
-      <c r="F109" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A110">
-        <v>1</v>
-      </c>
-      <c r="B110">
+      <c r="F109" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="12"/>
+      <c r="H109" s="12"/>
+      <c r="I109" s="12"/>
+      <c r="J109" s="12"/>
+      <c r="K109" s="12"/>
+      <c r="L109" s="12"/>
+      <c r="M109" s="12"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" s="11">
+        <v>5</v>
+      </c>
+      <c r="B110" s="12">
         <v>1518.41535128443</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="12">
         <v>119.432098765432</v>
       </c>
-      <c r="D110" t="s">
-        <v>14</v>
-      </c>
-      <c r="E110">
+      <c r="D110" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" s="12">
         <v>2018</v>
       </c>
-      <c r="F110" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A111">
-        <v>1</v>
-      </c>
-      <c r="B111">
+      <c r="F110" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="12"/>
+      <c r="H110" s="12"/>
+      <c r="I110" s="12"/>
+      <c r="J110" s="12"/>
+      <c r="K110" s="12"/>
+      <c r="L110" s="12"/>
+      <c r="M110" s="12"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" s="11">
+        <v>5</v>
+      </c>
+      <c r="B111" s="12">
         <v>14.691014133911199</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="12">
         <v>123.234567901234</v>
       </c>
-      <c r="D111" t="s">
-        <v>14</v>
-      </c>
-      <c r="E111">
+      <c r="D111" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E111" s="12">
         <v>2018</v>
       </c>
-      <c r="F111" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A112">
-        <v>1</v>
-      </c>
-      <c r="B112">
-        <v>2892.6230836628001</v>
-      </c>
-      <c r="C112">
+      <c r="F111" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="12"/>
+      <c r="H111" s="12"/>
+      <c r="I111" s="12"/>
+      <c r="J111" s="13"/>
+      <c r="K111" s="13"/>
+      <c r="L111" s="14"/>
+      <c r="M111" s="12"/>
+    </row>
+    <row r="112" spans="1:13" ht="85.5" x14ac:dyDescent="5.0999999999999996">
+      <c r="A112" s="15">
+        <v>6</v>
+      </c>
+      <c r="B112" s="16">
+        <v>3847.1887019999999</v>
+      </c>
+      <c r="C112" s="12">
         <v>4.9301252190264497</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="12">
         <v>2017</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="G112">
-        <v>63081.962800000001</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A113">
-        <v>1</v>
-      </c>
-      <c r="B113">
-        <v>334.81649605264101</v>
-      </c>
-      <c r="C113">
+      <c r="G112" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H112" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I112" s="16">
+        <v>2892.6230839999998</v>
+      </c>
+      <c r="J112" s="16"/>
+      <c r="K112" s="16"/>
+      <c r="L112" s="16"/>
+      <c r="M112" s="12"/>
+    </row>
+    <row r="113" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A113" s="15">
+        <v>6</v>
+      </c>
+      <c r="B113" s="16">
+        <v>445.30594000000002</v>
+      </c>
+      <c r="C113" s="12">
         <v>18.093080900893199</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="12">
         <v>2017</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A114">
-        <v>1</v>
-      </c>
-      <c r="B114">
-        <v>2696.8962733568501</v>
-      </c>
-      <c r="C114">
+      <c r="G113" s="12"/>
+      <c r="H113" s="12"/>
+      <c r="I113" s="16">
+        <v>334.81649609999999</v>
+      </c>
+      <c r="J113" s="16"/>
+      <c r="K113" s="16"/>
+      <c r="L113" s="16"/>
+      <c r="M113" s="12"/>
+    </row>
+    <row r="114" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A114" s="15">
+        <v>6</v>
+      </c>
+      <c r="B114" s="16">
+        <v>3586.8720429999998</v>
+      </c>
+      <c r="C114" s="12">
         <v>32.901406042993202</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="12">
         <v>2017</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A115">
-        <v>1</v>
-      </c>
-      <c r="B115">
-        <v>1966.0119954459699</v>
-      </c>
-      <c r="C115">
+      <c r="G114" s="12"/>
+      <c r="H114" s="12"/>
+      <c r="I114" s="16">
+        <v>2696.8962729999998</v>
+      </c>
+      <c r="J114" s="16"/>
+      <c r="K114" s="16"/>
+      <c r="L114" s="16"/>
+      <c r="M114" s="12"/>
+    </row>
+    <row r="115" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A115" s="15">
+        <v>6</v>
+      </c>
+      <c r="B115" s="16">
+        <v>2614.7959529999998</v>
+      </c>
+      <c r="C115" s="12">
         <v>36.042565921620501</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="12">
         <v>2017</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A116">
-        <v>1</v>
-      </c>
-      <c r="B116">
-        <v>2896.9985813963899</v>
-      </c>
-      <c r="C116">
+      <c r="G115" s="12"/>
+      <c r="H115" s="12"/>
+      <c r="I115" s="16">
+        <v>1966.0119950000001</v>
+      </c>
+      <c r="J115" s="16"/>
+      <c r="K115" s="16"/>
+      <c r="L115" s="16"/>
+      <c r="M115" s="12"/>
+    </row>
+    <row r="116" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A116" s="15">
+        <v>6</v>
+      </c>
+      <c r="B116" s="16">
+        <v>3853.0081129999999</v>
+      </c>
+      <c r="C116" s="12">
         <v>37.8375144236933</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="12">
         <v>2017</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A117">
-        <v>1</v>
-      </c>
-      <c r="B117">
-        <v>1733.86200774022</v>
-      </c>
-      <c r="C117">
+      <c r="G116" s="12"/>
+      <c r="H116" s="12"/>
+      <c r="I116" s="16">
+        <v>2896.9985809999998</v>
+      </c>
+      <c r="J116" s="16"/>
+      <c r="K116" s="16"/>
+      <c r="L116" s="16"/>
+      <c r="M116" s="12"/>
+    </row>
+    <row r="117" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A117" s="15">
+        <v>6</v>
+      </c>
+      <c r="B117" s="16">
+        <v>2306.0364709999999</v>
+      </c>
+      <c r="C117" s="12">
         <v>40.081200051284199</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="12">
         <v>2017</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A118">
-        <v>1</v>
-      </c>
-      <c r="B118">
-        <v>2930.7765715299702</v>
-      </c>
-      <c r="C118">
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
+      <c r="I117" s="16">
+        <v>1733.8620080000001</v>
+      </c>
+      <c r="J117" s="16"/>
+      <c r="K117" s="16"/>
+      <c r="L117" s="16"/>
+      <c r="M117" s="12"/>
+    </row>
+    <row r="118" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A118" s="15">
+        <v>6</v>
+      </c>
+      <c r="B118" s="16">
+        <v>3897.9328409999998</v>
+      </c>
+      <c r="C118" s="12">
         <v>41.876148553356899</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="12">
         <v>2017</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A119">
-        <v>1</v>
-      </c>
-      <c r="B119">
-        <v>1634.51689994564</v>
-      </c>
-      <c r="C119">
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
+      <c r="I118" s="16">
+        <v>2930.7765720000002</v>
+      </c>
+      <c r="J118" s="16"/>
+      <c r="K118" s="16"/>
+      <c r="L118" s="16"/>
+      <c r="M118" s="12"/>
+    </row>
+    <row r="119" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A119" s="15">
+        <v>6</v>
+      </c>
+      <c r="B119" s="16">
+        <v>2173.9074770000002</v>
+      </c>
+      <c r="C119" s="12">
         <v>42.923201846232701</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="12">
         <v>2017</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A120">
-        <v>1</v>
-      </c>
-      <c r="B120">
-        <v>2699.0442449715201</v>
-      </c>
-      <c r="C120">
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
+      <c r="I119" s="16">
+        <v>1634.5169000000001</v>
+      </c>
+      <c r="J119" s="16"/>
+      <c r="K119" s="16"/>
+      <c r="L119" s="16"/>
+      <c r="M119" s="12"/>
+    </row>
+    <row r="120" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A120" s="15">
+        <v>6</v>
+      </c>
+      <c r="B120" s="16">
+        <v>3589.728846</v>
+      </c>
+      <c r="C120" s="12">
         <v>49.055942561647903</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="12">
         <v>2017</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>1</v>
-      </c>
-      <c r="B121">
-        <v>2367.4099290887598</v>
-      </c>
-      <c r="C121">
+      <c r="G120" s="12"/>
+      <c r="H120" s="12"/>
+      <c r="I120" s="16">
+        <v>2699.044245</v>
+      </c>
+      <c r="J120" s="16"/>
+      <c r="K120" s="16"/>
+      <c r="L120" s="16"/>
+      <c r="M120" s="12"/>
+    </row>
+    <row r="121" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A121" s="15">
+        <v>6</v>
+      </c>
+      <c r="B121" s="16">
+        <v>3148.6552059999999</v>
+      </c>
+      <c r="C121" s="12">
         <v>54.889525193384301</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="12">
         <v>2017</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A122">
-        <v>1</v>
-      </c>
-      <c r="B122">
-        <v>4761.7163836937398</v>
-      </c>
-      <c r="C122">
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="16">
+        <v>2367.4099289999999</v>
+      </c>
+      <c r="J121" s="16"/>
+      <c r="K121" s="16"/>
+      <c r="L121" s="16"/>
+      <c r="M121" s="12"/>
+    </row>
+    <row r="122" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A122" s="15">
+        <v>6</v>
+      </c>
+      <c r="B122" s="16">
+        <v>6333.0827909999998</v>
+      </c>
+      <c r="C122" s="12">
         <v>62.069319201675199</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="12">
         <v>2017</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A123">
-        <v>1</v>
-      </c>
-      <c r="B123">
-        <v>5361.1084310135102</v>
-      </c>
-      <c r="C123">
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="16">
+        <v>4761.7163840000003</v>
+      </c>
+      <c r="J122" s="16"/>
+      <c r="K122" s="16"/>
+      <c r="L122" s="16"/>
+      <c r="M122" s="12"/>
+    </row>
+    <row r="123" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A123" s="15">
+        <v>6</v>
+      </c>
+      <c r="B123" s="16">
+        <v>7130.2742129999997</v>
+      </c>
+      <c r="C123" s="12">
         <v>69.997008419163194</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="12">
         <v>2017</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>1</v>
-      </c>
-      <c r="B124">
-        <v>4696.9448110752101</v>
-      </c>
-      <c r="C124">
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="16">
+        <v>5361.1084309999997</v>
+      </c>
+      <c r="J123" s="16"/>
+      <c r="K123" s="16"/>
+      <c r="L123" s="16"/>
+      <c r="M123" s="12"/>
+    </row>
+    <row r="124" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A124" s="15">
+        <v>6</v>
+      </c>
+      <c r="B124" s="16">
+        <v>6246.9365989999997</v>
+      </c>
+      <c r="C124" s="12">
         <v>74.9331167998632</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="12">
         <v>2017</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A125">
-        <v>1</v>
-      </c>
-      <c r="B125">
-        <v>5097.04998402398</v>
-      </c>
-      <c r="C125">
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="16">
+        <v>4696.9448110000003</v>
+      </c>
+      <c r="J124" s="16"/>
+      <c r="K124" s="16"/>
+      <c r="L124" s="16"/>
+      <c r="M124" s="12"/>
+    </row>
+    <row r="125" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A125" s="15">
+        <v>6</v>
+      </c>
+      <c r="B125" s="16">
+        <v>6779.0764790000003</v>
+      </c>
+      <c r="C125" s="12">
         <v>84.057438352066299</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="12">
         <v>2017</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A126">
-        <v>1</v>
-      </c>
-      <c r="B126">
-        <v>3302.9510104073102</v>
-      </c>
-      <c r="C126">
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+      <c r="I125" s="16">
+        <v>5097.0499840000002</v>
+      </c>
+      <c r="J125" s="16"/>
+      <c r="K125" s="16"/>
+      <c r="L125" s="16"/>
+      <c r="M125" s="12"/>
+    </row>
+    <row r="126" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A126" s="15">
+        <v>6</v>
+      </c>
+      <c r="B126" s="16">
+        <v>4392.9248429999998</v>
+      </c>
+      <c r="C126" s="12">
         <v>90.938074276678407</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="12">
         <v>2017</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A127">
-        <v>1</v>
-      </c>
-      <c r="B127">
-        <v>4899.0757589730501</v>
-      </c>
-      <c r="C127">
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+      <c r="I126" s="16">
+        <v>3302.9510100000002</v>
+      </c>
+      <c r="J126" s="16"/>
+      <c r="K126" s="16"/>
+      <c r="L126" s="16"/>
+      <c r="M126" s="12"/>
+    </row>
+    <row r="127" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A127" s="15">
+        <v>6</v>
+      </c>
+      <c r="B127" s="16">
+        <v>6515.770759</v>
+      </c>
+      <c r="C127" s="12">
         <v>95.1262874481815</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="12">
         <v>2017</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F127" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A128">
-        <v>1</v>
-      </c>
-      <c r="B128">
-        <v>1509.8066908415999</v>
-      </c>
-      <c r="C128">
+      <c r="G127" s="12"/>
+      <c r="H127" s="12"/>
+      <c r="I127" s="16">
+        <v>4899.0757590000003</v>
+      </c>
+      <c r="J127" s="16"/>
+      <c r="K127" s="16"/>
+      <c r="L127" s="16"/>
+      <c r="M127" s="12"/>
+    </row>
+    <row r="128" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A128" s="15">
+        <v>6</v>
+      </c>
+      <c r="B128" s="16">
+        <v>2008.042899</v>
+      </c>
+      <c r="C128" s="12">
         <v>104.998504209581</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="12">
         <v>2017</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A129">
-        <v>1</v>
-      </c>
-      <c r="B129">
-        <v>14.8965809202491</v>
-      </c>
-      <c r="C129">
+      <c r="G128" s="12"/>
+      <c r="H128" s="12"/>
+      <c r="I128" s="16">
+        <v>1509.806691</v>
+      </c>
+      <c r="J128" s="16"/>
+      <c r="K128" s="16"/>
+      <c r="L128" s="16"/>
+      <c r="M128" s="12"/>
+    </row>
+    <row r="129" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="15">
+        <v>6</v>
+      </c>
+      <c r="B129" s="16">
+        <v>19.812453000000001</v>
+      </c>
+      <c r="C129" s="12">
         <v>112.02871917603299</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="12">
         <v>2017</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A130">
-        <v>1</v>
-      </c>
-      <c r="B130">
-        <v>1378.71223277174</v>
-      </c>
-      <c r="C130">
+      <c r="G129" s="12"/>
+      <c r="H129" s="12"/>
+      <c r="I129" s="16">
+        <v>14.89658092</v>
+      </c>
+      <c r="J129" s="16"/>
+      <c r="K129" s="16"/>
+      <c r="L129" s="16"/>
+      <c r="M129" s="12"/>
+    </row>
+    <row r="130" spans="1:13" ht="56.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="15">
+        <v>6</v>
+      </c>
+      <c r="B130" s="16">
+        <v>1833.6872699999999</v>
+      </c>
+      <c r="C130" s="12">
         <v>119.05893414248401</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="12">
         <v>2017</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A131">
-        <v>1</v>
-      </c>
-      <c r="B131">
-        <v>9889.1831800468699</v>
-      </c>
-      <c r="C131">
+      <c r="G130" s="12"/>
+      <c r="H130" s="12"/>
+      <c r="I130" s="16">
+        <v>1378.712233</v>
+      </c>
+      <c r="J130" s="16"/>
+      <c r="K130" s="16"/>
+      <c r="L130" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="M130" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="15">
+        <v>6</v>
+      </c>
+      <c r="B131" s="16">
+        <v>13152.61363</v>
+      </c>
+      <c r="C131" s="12">
         <v>124.89251677422099</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="12">
         <v>2017</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A132">
-        <v>1</v>
-      </c>
-      <c r="B132">
-        <v>17.561656812522401</v>
-      </c>
-      <c r="C132">
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
+      <c r="I131" s="16">
+        <v>9889.18318</v>
+      </c>
+      <c r="J131" s="16"/>
+      <c r="K131" s="16"/>
+      <c r="L131" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M131" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="15">
+        <v>6</v>
+      </c>
+      <c r="B132" s="16">
+        <v>23.357004</v>
+      </c>
+      <c r="C132" s="12">
         <v>132.07231078251201</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="12">
         <v>2017</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A133">
-        <v>1</v>
-      </c>
-      <c r="B133">
-        <v>21.604938271604599</v>
-      </c>
-      <c r="C133">
+      <c r="G132" s="12"/>
+      <c r="H132" s="12"/>
+      <c r="I132" s="16">
+        <v>17.561656809999999</v>
+      </c>
+      <c r="J132" s="16"/>
+      <c r="K132" s="16"/>
+      <c r="L132" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="M132" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="15">
+        <v>7</v>
+      </c>
+      <c r="B133" s="16">
+        <v>28.734567999999999</v>
+      </c>
+      <c r="C133" s="12">
         <v>5.0917992656058697</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E133">
-        <v>2020</v>
-      </c>
-      <c r="F133" s="3" t="s">
+      <c r="E133" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F133" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G133">
-        <v>48654.32099</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A134">
-        <v>1</v>
-      </c>
-      <c r="B134">
-        <v>21.604938271604599</v>
-      </c>
-      <c r="C134">
+      <c r="G133" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="H133" s="12"/>
+      <c r="I133" s="16">
+        <v>21.604938270000002</v>
+      </c>
+      <c r="J133" s="16"/>
+      <c r="K133" s="16"/>
+      <c r="L133" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M133" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="15">
+        <v>7</v>
+      </c>
+      <c r="B134" s="16">
+        <v>28.734567999999999</v>
+      </c>
+      <c r="C134" s="12">
         <v>12.925336597307201</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E134">
-        <v>2020</v>
-      </c>
-      <c r="F134" s="3" t="s">
+      <c r="E134" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F134" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A135">
-        <v>1</v>
-      </c>
-      <c r="B135">
-        <v>367.28395061728497</v>
-      </c>
-      <c r="C135">
+      <c r="G134" s="12"/>
+      <c r="H134" s="12"/>
+      <c r="I134" s="16">
+        <v>21.604938270000002</v>
+      </c>
+      <c r="J134" s="16"/>
+      <c r="K134" s="16"/>
+      <c r="L134" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M134" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="15">
+        <v>7</v>
+      </c>
+      <c r="B135" s="16">
+        <v>488.48765400000002</v>
+      </c>
+      <c r="C135" s="12">
         <v>20.1713586291309</v>
       </c>
-      <c r="D135" t="s">
-        <v>14</v>
-      </c>
-      <c r="E135">
-        <v>2020</v>
-      </c>
-      <c r="F135" s="3" t="s">
+      <c r="D135" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E135" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F135" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A136">
-        <v>1</v>
-      </c>
-      <c r="B136">
-        <v>1555.55555555555</v>
-      </c>
-      <c r="C136">
+      <c r="G135" s="12"/>
+      <c r="H135" s="12"/>
+      <c r="I135" s="16">
+        <v>367.28395060000003</v>
+      </c>
+      <c r="J135" s="16"/>
+      <c r="K135" s="16"/>
+      <c r="L135" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M135" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="15">
+        <v>7</v>
+      </c>
+      <c r="B136" s="16">
+        <v>2068.8888889999998</v>
+      </c>
+      <c r="C136" s="12">
         <v>25.067319461444299</v>
       </c>
-      <c r="D136" t="s">
-        <v>14</v>
-      </c>
-      <c r="E136">
-        <v>2020</v>
-      </c>
-      <c r="F136" s="3" t="s">
+      <c r="D136" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E136" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F136" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>1</v>
-      </c>
-      <c r="B137">
-        <v>2074.0740740740698</v>
-      </c>
-      <c r="C137">
+      <c r="G136" s="12"/>
+      <c r="H136" s="12"/>
+      <c r="I136" s="16">
+        <v>1555.555556</v>
+      </c>
+      <c r="J136" s="16"/>
+      <c r="K136" s="16"/>
+      <c r="L136" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M136" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="15">
+        <v>7</v>
+      </c>
+      <c r="B137" s="16">
+        <v>2758.5185179999999</v>
+      </c>
+      <c r="C137" s="12">
         <v>34.075887392900803</v>
       </c>
-      <c r="D137" t="s">
-        <v>14</v>
-      </c>
-      <c r="E137">
-        <v>2020</v>
-      </c>
-      <c r="F137" s="3" t="s">
+      <c r="D137" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E137" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F137" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A138">
-        <v>1</v>
-      </c>
-      <c r="B138">
-        <v>3132.71604938271</v>
-      </c>
-      <c r="C138">
+      <c r="G137" s="12"/>
+      <c r="H137" s="12"/>
+      <c r="I137" s="16">
+        <v>2074.0740740000001</v>
+      </c>
+      <c r="J137" s="16"/>
+      <c r="K137" s="16"/>
+      <c r="L137" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M137" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="15">
+        <v>7</v>
+      </c>
+      <c r="B138" s="16">
+        <v>4166.5123450000001</v>
+      </c>
+      <c r="C138" s="12">
         <v>42.301101591187198</v>
       </c>
-      <c r="D138" t="s">
-        <v>14</v>
-      </c>
-      <c r="E138">
-        <v>2020</v>
-      </c>
-      <c r="F138" s="3" t="s">
+      <c r="D138" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E138" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F138" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A139">
-        <v>1</v>
-      </c>
-      <c r="B139">
-        <v>3175.9259259259202</v>
-      </c>
-      <c r="C139">
+      <c r="G138" s="12"/>
+      <c r="H138" s="12"/>
+      <c r="I138" s="16">
+        <v>3132.7160490000001</v>
+      </c>
+      <c r="J138" s="16"/>
+      <c r="K138" s="16"/>
+      <c r="L138" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M138" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="15">
+        <v>7</v>
+      </c>
+      <c r="B139" s="16">
+        <v>4223.9814820000001</v>
+      </c>
+      <c r="C139" s="12">
         <v>44.063647490820003</v>
       </c>
-      <c r="D139" t="s">
-        <v>14</v>
-      </c>
-      <c r="E139">
-        <v>2020</v>
-      </c>
-      <c r="F139" s="3" t="s">
+      <c r="D139" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E139" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F139" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>1</v>
-      </c>
-      <c r="B140">
-        <v>3391.9753086419701</v>
-      </c>
-      <c r="C140">
+      <c r="G139" s="12"/>
+      <c r="H139" s="12"/>
+      <c r="I139" s="16">
+        <v>3175.9259259999999</v>
+      </c>
+      <c r="J139" s="16"/>
+      <c r="K139" s="16"/>
+      <c r="L139" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M139" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="15">
+        <v>7</v>
+      </c>
+      <c r="B140" s="16">
+        <v>4511.3271610000002</v>
+      </c>
+      <c r="C140" s="12">
         <v>46.217870257037902</v>
       </c>
-      <c r="D140" t="s">
-        <v>14</v>
-      </c>
-      <c r="E140">
-        <v>2020</v>
-      </c>
-      <c r="F140" s="3" t="s">
+      <c r="D140" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E140" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F140" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>1</v>
-      </c>
-      <c r="B141">
-        <v>4277.7777777777701</v>
-      </c>
-      <c r="C141">
+      <c r="G140" s="12"/>
+      <c r="H140" s="12"/>
+      <c r="I140" s="16">
+        <v>3391.9753089999999</v>
+      </c>
+      <c r="J140" s="16"/>
+      <c r="K140" s="16"/>
+      <c r="L140" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M140" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A141" s="15">
+        <v>7</v>
+      </c>
+      <c r="B141" s="16">
+        <v>5689.4444450000001</v>
+      </c>
+      <c r="C141" s="12">
         <v>48.959608323133402</v>
       </c>
-      <c r="D141" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141">
-        <v>2020</v>
-      </c>
-      <c r="F141" s="3" t="s">
+      <c r="D141" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F141" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>1</v>
-      </c>
-      <c r="B142">
-        <v>4472.2222222222199</v>
-      </c>
-      <c r="C142">
+      <c r="G141" s="12"/>
+      <c r="H141" s="12"/>
+      <c r="I141" s="16">
+        <v>4277.7777779999997</v>
+      </c>
+      <c r="J141" s="16"/>
+      <c r="K141" s="16"/>
+      <c r="L141" s="16"/>
+      <c r="M141" s="12"/>
+    </row>
+    <row r="142" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A142" s="15">
+        <v>7</v>
+      </c>
+      <c r="B142" s="16">
+        <v>5948.0555549999999</v>
+      </c>
+      <c r="C142" s="12">
         <v>53.855569155446702</v>
       </c>
-      <c r="D142" t="s">
-        <v>14</v>
-      </c>
-      <c r="E142">
-        <v>2020</v>
-      </c>
-      <c r="F142" s="3" t="s">
+      <c r="D142" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E142" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F142" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A143">
-        <v>1</v>
-      </c>
-      <c r="B143">
-        <v>4472.2222222222199</v>
-      </c>
-      <c r="C143">
+      <c r="G142" s="12"/>
+      <c r="H142" s="12"/>
+      <c r="I142" s="16">
+        <v>4472.2222220000003</v>
+      </c>
+      <c r="J142" s="16"/>
+      <c r="K142" s="16"/>
+      <c r="L142" s="16"/>
+      <c r="M142" s="12"/>
+    </row>
+    <row r="143" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A143" s="15">
+        <v>7</v>
+      </c>
+      <c r="B143" s="16">
+        <v>5948.0555549999999</v>
+      </c>
+      <c r="C143" s="12">
         <v>66.976744186046503</v>
       </c>
-      <c r="D143" t="s">
-        <v>14</v>
-      </c>
-      <c r="E143">
-        <v>2020</v>
-      </c>
-      <c r="F143" s="3" t="s">
+      <c r="D143" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F143" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A144">
-        <v>1</v>
-      </c>
-      <c r="B144">
-        <v>4407.4074074073997</v>
-      </c>
-      <c r="C144">
+      <c r="G143" s="12"/>
+      <c r="H143" s="12"/>
+      <c r="I143" s="16">
+        <v>4472.2222220000003</v>
+      </c>
+      <c r="J143" s="16"/>
+      <c r="K143" s="16"/>
+      <c r="L143" s="16"/>
+      <c r="M143" s="12"/>
+    </row>
+    <row r="144" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A144" s="15">
+        <v>7</v>
+      </c>
+      <c r="B144" s="16">
+        <v>5861.8518510000004</v>
+      </c>
+      <c r="C144" s="12">
         <v>72.851897184822505</v>
       </c>
-      <c r="D144" t="s">
-        <v>14</v>
-      </c>
-      <c r="E144">
-        <v>2020</v>
-      </c>
-      <c r="F144" s="3" t="s">
+      <c r="D144" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E144" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F144" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A145">
-        <v>1</v>
-      </c>
-      <c r="B145">
-        <v>3478.3950617283899</v>
-      </c>
-      <c r="C145">
+      <c r="G144" s="12"/>
+      <c r="H144" s="12"/>
+      <c r="I144" s="16">
+        <v>4407.4074069999997</v>
+      </c>
+      <c r="J144" s="16"/>
+      <c r="K144" s="16"/>
+      <c r="L144" s="16"/>
+      <c r="M144" s="12"/>
+    </row>
+    <row r="145" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A145" s="15">
+        <v>7</v>
+      </c>
+      <c r="B145" s="16">
+        <v>4626.2654320000001</v>
+      </c>
+      <c r="C145" s="12">
         <v>89.889840881272903</v>
       </c>
-      <c r="D145" t="s">
-        <v>14</v>
-      </c>
-      <c r="E145">
-        <v>2020</v>
-      </c>
-      <c r="F145" s="3" t="s">
+      <c r="D145" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E145" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F145" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>1</v>
-      </c>
-      <c r="B146">
-        <v>3262.34567901234</v>
-      </c>
-      <c r="C146">
+      <c r="G145" s="12"/>
+      <c r="H145" s="12"/>
+      <c r="I145" s="16">
+        <v>3478.3950620000001</v>
+      </c>
+      <c r="J145" s="16"/>
+      <c r="K145" s="16"/>
+      <c r="L145" s="16"/>
+      <c r="M145" s="12"/>
+    </row>
+    <row r="146" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A146" s="15">
+        <v>7</v>
+      </c>
+      <c r="B146" s="16">
+        <v>4338.9197530000001</v>
+      </c>
+      <c r="C146" s="12">
         <v>94.981640146878803</v>
       </c>
-      <c r="D146" t="s">
-        <v>14</v>
-      </c>
-      <c r="E146">
-        <v>2020</v>
-      </c>
-      <c r="F146" s="3" t="s">
+      <c r="D146" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E146" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F146" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A147">
-        <v>1</v>
-      </c>
-      <c r="B147">
-        <v>3089.5061728394999</v>
-      </c>
-      <c r="C147">
+      <c r="G146" s="12"/>
+      <c r="H146" s="12"/>
+      <c r="I146" s="16">
+        <v>3262.345679</v>
+      </c>
+      <c r="J146" s="16"/>
+      <c r="K146" s="16"/>
+      <c r="L146" s="16"/>
+      <c r="M146" s="12"/>
+    </row>
+    <row r="147" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A147" s="15">
+        <v>7</v>
+      </c>
+      <c r="B147" s="16">
+        <v>4109.0432099999998</v>
+      </c>
+      <c r="C147" s="12">
         <v>102.03182374540999</v>
       </c>
-      <c r="D147" t="s">
-        <v>14</v>
-      </c>
-      <c r="E147">
-        <v>2020</v>
-      </c>
-      <c r="F147" s="3" t="s">
+      <c r="D147" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E147" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F147" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A148">
-        <v>1</v>
-      </c>
-      <c r="B148">
-        <v>3024.6913580246901</v>
-      </c>
-      <c r="C148">
+      <c r="G147" s="12"/>
+      <c r="H147" s="12"/>
+      <c r="I147" s="16">
+        <v>3089.5061730000002</v>
+      </c>
+      <c r="J147" s="16"/>
+      <c r="K147" s="16"/>
+      <c r="L147" s="16"/>
+      <c r="M147" s="12"/>
+    </row>
+    <row r="148" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A148" s="15">
+        <v>7</v>
+      </c>
+      <c r="B148" s="16">
+        <v>4022.8395059999998</v>
+      </c>
+      <c r="C148" s="12">
         <v>110.844553243574</v>
       </c>
-      <c r="D148" t="s">
-        <v>14</v>
-      </c>
-      <c r="E148">
-        <v>2020</v>
-      </c>
-      <c r="F148" s="3" t="s">
+      <c r="D148" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E148" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F148" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>1</v>
-      </c>
-      <c r="B149">
-        <v>2527.7777777777701</v>
-      </c>
-      <c r="C149">
+      <c r="G148" s="12"/>
+      <c r="H148" s="12"/>
+      <c r="I148" s="16">
+        <v>3024.691358</v>
+      </c>
+      <c r="J148" s="16"/>
+      <c r="K148" s="16"/>
+      <c r="L148" s="16"/>
+      <c r="M148" s="12"/>
+    </row>
+    <row r="149" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A149" s="15">
+        <v>7</v>
+      </c>
+      <c r="B149" s="16">
+        <v>3361.9444450000001</v>
+      </c>
+      <c r="C149" s="12">
         <v>116.915544675642</v>
       </c>
-      <c r="D149" t="s">
-        <v>14</v>
-      </c>
-      <c r="E149">
-        <v>2020</v>
-      </c>
-      <c r="F149" s="3" t="s">
+      <c r="D149" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E149" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F149" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>1</v>
-      </c>
-      <c r="B150">
-        <v>1469.1358024691301</v>
-      </c>
-      <c r="C150">
+      <c r="G149" s="12"/>
+      <c r="H149" s="12"/>
+      <c r="I149" s="16">
+        <v>2527.7777780000001</v>
+      </c>
+      <c r="J149" s="16"/>
+      <c r="K149" s="16"/>
+      <c r="L149" s="16"/>
+      <c r="M149" s="12"/>
+    </row>
+    <row r="150" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A150" s="15">
+        <v>7</v>
+      </c>
+      <c r="B150" s="16">
+        <v>1953.950617</v>
+      </c>
+      <c r="C150" s="12">
         <v>124.944920440636</v>
       </c>
-      <c r="D150" t="s">
-        <v>14</v>
-      </c>
-      <c r="E150">
-        <v>2020</v>
-      </c>
-      <c r="F150" s="3" t="s">
+      <c r="D150" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F150" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A151">
-        <v>1</v>
-      </c>
-      <c r="B151">
-        <v>151.23456790123601</v>
-      </c>
-      <c r="C151">
+      <c r="G150" s="12"/>
+      <c r="H150" s="12"/>
+      <c r="I150" s="16">
+        <v>1469.135802</v>
+      </c>
+      <c r="J150" s="16"/>
+      <c r="K150" s="16"/>
+      <c r="L150" s="16"/>
+      <c r="M150" s="12"/>
+    </row>
+    <row r="151" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A151" s="15">
+        <v>7</v>
+      </c>
+      <c r="B151" s="16">
+        <v>201.141975</v>
+      </c>
+      <c r="C151" s="12">
         <v>129.84088127294899</v>
       </c>
-      <c r="D151" t="s">
-        <v>14</v>
-      </c>
-      <c r="E151">
-        <v>2020</v>
-      </c>
-      <c r="F151" s="3" t="s">
+      <c r="D151" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E151" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F151" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>1</v>
-      </c>
-      <c r="B152">
-        <v>280.86419753086301</v>
-      </c>
-      <c r="C152">
+      <c r="G151" s="12"/>
+      <c r="H151" s="12"/>
+      <c r="I151" s="16">
+        <v>151.2345679</v>
+      </c>
+      <c r="J151" s="16"/>
+      <c r="K151" s="16"/>
+      <c r="L151" s="16"/>
+      <c r="M151" s="12"/>
+    </row>
+    <row r="152" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A152" s="15">
+        <v>7</v>
+      </c>
+      <c r="B152" s="16">
+        <v>373.54938299999998</v>
+      </c>
+      <c r="C152" s="12">
         <v>131.99510403916699</v>
       </c>
-      <c r="D152" t="s">
-        <v>14</v>
-      </c>
-      <c r="E152">
-        <v>2020</v>
-      </c>
-      <c r="F152" s="3" t="s">
+      <c r="D152" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E152" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F152" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A153">
-        <v>1</v>
-      </c>
-      <c r="B153">
+      <c r="G152" s="12"/>
+      <c r="H152" s="12"/>
+      <c r="I152" s="16">
+        <v>280.86419749999999</v>
+      </c>
+      <c r="J152" s="16"/>
+      <c r="K152" s="16"/>
+      <c r="L152" s="16"/>
+      <c r="M152" s="12"/>
+    </row>
+    <row r="153" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A153" s="15">
+        <v>7</v>
+      </c>
+      <c r="B153" s="16">
         <v>0</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="12">
         <v>138.849449204406</v>
       </c>
-      <c r="D153" t="s">
-        <v>14</v>
-      </c>
-      <c r="E153">
-        <v>2020</v>
-      </c>
-      <c r="F153" s="3" t="s">
+      <c r="D153" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E153" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F153" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A154">
-        <v>1</v>
-      </c>
-      <c r="B154">
+      <c r="G153" s="12"/>
+      <c r="H153" s="12"/>
+      <c r="I153" s="16">
         <v>0</v>
       </c>
-      <c r="C154">
+      <c r="J153" s="16"/>
+      <c r="K153" s="16"/>
+      <c r="L153" s="16"/>
+      <c r="M153" s="12"/>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" s="15">
+        <v>8</v>
+      </c>
+      <c r="B154" s="16">
+        <v>0</v>
+      </c>
+      <c r="C154" s="12">
         <v>4.8999999999999897</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D154" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E154">
-        <v>2020</v>
-      </c>
-      <c r="F154" t="s">
+      <c r="E154" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F154" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G154">
-        <v>21927.71084</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A155">
-        <v>1</v>
-      </c>
-      <c r="B155">
-        <v>843.37349397590799</v>
-      </c>
-      <c r="C155">
+      <c r="G154" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H154" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="I154" s="16">
+        <v>0</v>
+      </c>
+      <c r="J154" s="16"/>
+      <c r="K154" s="16"/>
+      <c r="L154" s="16"/>
+      <c r="M154" s="12"/>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" s="15">
+        <v>8</v>
+      </c>
+      <c r="B155" s="16">
+        <v>1121.686747</v>
+      </c>
+      <c r="C155" s="12">
         <v>11.024999999999901</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D155" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E155">
-        <v>2020</v>
-      </c>
-      <c r="F155" t="s">
+      <c r="E155" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F155" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A156">
-        <v>1</v>
-      </c>
-      <c r="B156">
-        <v>6662.6506024096298</v>
-      </c>
-      <c r="C156">
+      <c r="G155" s="12"/>
+      <c r="H155" s="12"/>
+      <c r="I155" s="16">
+        <v>843.37349400000005</v>
+      </c>
+      <c r="J155" s="16"/>
+      <c r="K155" s="16"/>
+      <c r="L155" s="16"/>
+      <c r="M155" s="12"/>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" s="15">
+        <v>8</v>
+      </c>
+      <c r="B156" s="16">
+        <v>8861.3253010000008</v>
+      </c>
+      <c r="C156" s="12">
         <v>18.024999999999999</v>
       </c>
-      <c r="D156" t="s">
-        <v>14</v>
-      </c>
-      <c r="E156">
-        <v>2020</v>
-      </c>
-      <c r="F156" t="s">
+      <c r="D156" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F156" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A157">
-        <v>1</v>
-      </c>
-      <c r="B157">
-        <v>168.67469879518401</v>
-      </c>
-      <c r="C157">
+      <c r="G156" s="12"/>
+      <c r="H156" s="12"/>
+      <c r="I156" s="16">
+        <v>6662.6506019999997</v>
+      </c>
+      <c r="J156" s="16"/>
+      <c r="K156" s="16"/>
+      <c r="L156" s="16"/>
+      <c r="M156" s="12"/>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" s="15">
+        <v>8</v>
+      </c>
+      <c r="B157" s="16">
+        <v>224.33734899999999</v>
+      </c>
+      <c r="C157" s="12">
         <v>28.875</v>
       </c>
-      <c r="D157" t="s">
-        <v>14</v>
-      </c>
-      <c r="E157">
-        <v>2020</v>
-      </c>
-      <c r="F157" t="s">
+      <c r="D157" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E157" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F157" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A158">
-        <v>1</v>
-      </c>
-      <c r="B158">
-        <v>927.71084337349703</v>
-      </c>
-      <c r="C158">
+      <c r="G157" s="12"/>
+      <c r="H157" s="12"/>
+      <c r="I157" s="16">
+        <v>168.67469879999999</v>
+      </c>
+      <c r="J157" s="16"/>
+      <c r="K157" s="16"/>
+      <c r="L157" s="16"/>
+      <c r="M157" s="12"/>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" s="15">
+        <v>8</v>
+      </c>
+      <c r="B158" s="16">
+        <v>1233.8554220000001</v>
+      </c>
+      <c r="C158" s="12">
         <v>33.950000000000003</v>
       </c>
-      <c r="D158" t="s">
-        <v>14</v>
-      </c>
-      <c r="E158">
-        <v>2020</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="D158" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E158" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F158" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A159">
-        <v>1</v>
-      </c>
-      <c r="B159">
-        <v>801.20481927711</v>
-      </c>
-      <c r="C159">
+      <c r="G158" s="12"/>
+      <c r="H158" s="12"/>
+      <c r="I158" s="16">
+        <v>927.71084340000004</v>
+      </c>
+      <c r="J158" s="16"/>
+      <c r="K158" s="16"/>
+      <c r="L158" s="16"/>
+      <c r="M158" s="12"/>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" s="15">
+        <v>8</v>
+      </c>
+      <c r="B159" s="16">
+        <v>1065.60241</v>
+      </c>
+      <c r="C159" s="12">
         <v>39.9</v>
       </c>
-      <c r="D159" t="s">
-        <v>14</v>
-      </c>
-      <c r="E159">
-        <v>2020</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="D159" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E159" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F159" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A160">
-        <v>1</v>
-      </c>
-      <c r="B160">
-        <v>1644.57831325301</v>
-      </c>
-      <c r="C160">
+      <c r="G159" s="12"/>
+      <c r="H159" s="12"/>
+      <c r="I159" s="16">
+        <v>801.20481930000005</v>
+      </c>
+      <c r="J159" s="16"/>
+      <c r="K159" s="16"/>
+      <c r="L159" s="16"/>
+      <c r="M159" s="12"/>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" s="15">
+        <v>8</v>
+      </c>
+      <c r="B160" s="16">
+        <v>2187.2891559999998</v>
+      </c>
+      <c r="C160" s="12">
         <v>44.1</v>
       </c>
-      <c r="D160" t="s">
-        <v>14</v>
-      </c>
-      <c r="E160">
-        <v>2020</v>
-      </c>
-      <c r="F160" t="s">
+      <c r="D160" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F160" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A161">
-        <v>1</v>
-      </c>
-      <c r="B161">
-        <v>1391.5662650602301</v>
-      </c>
-      <c r="C161">
+      <c r="G160" s="12"/>
+      <c r="H160" s="12"/>
+      <c r="I160" s="16">
+        <v>1644.578313</v>
+      </c>
+      <c r="J160" s="16"/>
+      <c r="K160" s="16"/>
+      <c r="L160" s="16"/>
+      <c r="M160" s="12"/>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" s="15">
+        <v>8</v>
+      </c>
+      <c r="B161" s="16">
+        <v>1850.783132</v>
+      </c>
+      <c r="C161" s="12">
         <v>46.024999999999999</v>
       </c>
-      <c r="D161" t="s">
-        <v>14</v>
-      </c>
-      <c r="E161">
-        <v>2020</v>
-      </c>
-      <c r="F161" t="s">
+      <c r="D161" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E161" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F161" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A162">
-        <v>1</v>
-      </c>
-      <c r="B162">
-        <v>1602.40963855422</v>
-      </c>
-      <c r="C162">
+      <c r="G161" s="12"/>
+      <c r="H161" s="12"/>
+      <c r="I161" s="16">
+        <v>1391.5662649999999</v>
+      </c>
+      <c r="J161" s="16"/>
+      <c r="K161" s="16"/>
+      <c r="L161" s="16"/>
+      <c r="M161" s="12"/>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" s="15">
+        <v>8</v>
+      </c>
+      <c r="B162" s="16">
+        <v>2131.2048199999999</v>
+      </c>
+      <c r="C162" s="12">
         <v>47.949999999999903</v>
       </c>
-      <c r="D162" t="s">
-        <v>14</v>
-      </c>
-      <c r="E162">
-        <v>2020</v>
-      </c>
-      <c r="F162" t="s">
+      <c r="D162" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F162" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A163">
-        <v>1</v>
-      </c>
-      <c r="B163">
-        <v>1855.42168674698</v>
-      </c>
-      <c r="C163">
+      <c r="G162" s="12"/>
+      <c r="H162" s="12"/>
+      <c r="I162" s="16">
+        <v>1602.409639</v>
+      </c>
+      <c r="J162" s="16"/>
+      <c r="K162" s="16"/>
+      <c r="L162" s="16"/>
+      <c r="M162" s="12"/>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" s="15">
+        <v>8</v>
+      </c>
+      <c r="B163" s="16">
+        <v>2467.7108440000002</v>
+      </c>
+      <c r="C163" s="12">
         <v>52.85</v>
       </c>
-      <c r="D163" t="s">
-        <v>14</v>
-      </c>
-      <c r="E163">
-        <v>2020</v>
-      </c>
-      <c r="F163" t="s">
+      <c r="D163" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E163" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F163" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A164">
-        <v>1</v>
-      </c>
-      <c r="B164">
-        <v>1096.3855421686701</v>
-      </c>
-      <c r="C164">
+      <c r="G163" s="12"/>
+      <c r="H163" s="12"/>
+      <c r="I163" s="16">
+        <v>1855.421687</v>
+      </c>
+      <c r="J163" s="16"/>
+      <c r="K163" s="16"/>
+      <c r="L163" s="16"/>
+      <c r="M163" s="12"/>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" s="15">
+        <v>8</v>
+      </c>
+      <c r="B164" s="16">
+        <v>1458.192771</v>
+      </c>
+      <c r="C164" s="12">
         <v>60.9</v>
       </c>
-      <c r="D164" t="s">
-        <v>14</v>
-      </c>
-      <c r="E164">
-        <v>2020</v>
-      </c>
-      <c r="F164" t="s">
+      <c r="D164" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E164" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F164" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A165">
-        <v>1</v>
-      </c>
-      <c r="B165">
-        <v>1012.04819277108</v>
-      </c>
-      <c r="C165">
+      <c r="G164" s="12"/>
+      <c r="H164" s="12"/>
+      <c r="I164" s="16">
+        <v>1096.385542</v>
+      </c>
+      <c r="J164" s="16"/>
+      <c r="K164" s="16"/>
+      <c r="L164" s="16"/>
+      <c r="M164" s="12"/>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" s="15">
+        <v>8</v>
+      </c>
+      <c r="B165" s="16">
+        <v>1346.024097</v>
+      </c>
+      <c r="C165" s="12">
         <v>67.025000000000006</v>
       </c>
-      <c r="D165" t="s">
-        <v>14</v>
-      </c>
-      <c r="E165">
-        <v>2020</v>
-      </c>
-      <c r="F165" t="s">
+      <c r="D165" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E165" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F165" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A166">
-        <v>1</v>
-      </c>
-      <c r="B166">
-        <v>1012.04819277108</v>
-      </c>
-      <c r="C166">
+      <c r="G165" s="12"/>
+      <c r="H165" s="12"/>
+      <c r="I165" s="16">
+        <v>1012.048193</v>
+      </c>
+      <c r="J165" s="16"/>
+      <c r="K165" s="16"/>
+      <c r="L165" s="16"/>
+      <c r="M165" s="12"/>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" s="15">
+        <v>8</v>
+      </c>
+      <c r="B166" s="16">
+        <v>1346.024097</v>
+      </c>
+      <c r="C166" s="12">
         <v>77.875</v>
       </c>
-      <c r="D166" t="s">
-        <v>14</v>
-      </c>
-      <c r="E166">
-        <v>2020</v>
-      </c>
-      <c r="F166" t="s">
+      <c r="D166" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E166" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F166" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A167">
-        <v>1</v>
-      </c>
-      <c r="B167">
-        <v>1012.04819277108</v>
-      </c>
-      <c r="C167">
+      <c r="G166" s="12"/>
+      <c r="H166" s="12"/>
+      <c r="I166" s="16">
+        <v>1012.048193</v>
+      </c>
+      <c r="J166" s="16"/>
+      <c r="K166" s="16"/>
+      <c r="L166" s="16"/>
+      <c r="M166" s="12"/>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" s="15">
+        <v>8</v>
+      </c>
+      <c r="B167" s="16">
+        <v>1346.024097</v>
+      </c>
+      <c r="C167" s="12">
         <v>82.95</v>
       </c>
-      <c r="D167" t="s">
-        <v>14</v>
-      </c>
-      <c r="E167">
-        <v>2020</v>
-      </c>
-      <c r="F167" t="s">
+      <c r="D167" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E167" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F167" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A168">
-        <v>1</v>
-      </c>
-      <c r="B168">
-        <v>590.36144578313497</v>
-      </c>
-      <c r="C168">
+      <c r="G167" s="12"/>
+      <c r="H167" s="12"/>
+      <c r="I167" s="16">
+        <v>1012.048193</v>
+      </c>
+      <c r="J167" s="16"/>
+      <c r="K167" s="16"/>
+      <c r="L167" s="16"/>
+      <c r="M167" s="12"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" s="15">
+        <v>8</v>
+      </c>
+      <c r="B168" s="16">
+        <v>785.18072299999994</v>
+      </c>
+      <c r="C168" s="12">
         <v>89.95</v>
       </c>
-      <c r="D168" t="s">
-        <v>14</v>
-      </c>
-      <c r="E168">
-        <v>2020</v>
-      </c>
-      <c r="F168" t="s">
+      <c r="D168" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E168" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F168" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A169">
-        <v>1</v>
-      </c>
-      <c r="B169">
-        <v>253.01204819277299</v>
-      </c>
-      <c r="C169">
+      <c r="G168" s="12"/>
+      <c r="H168" s="12"/>
+      <c r="I168" s="16">
+        <v>590.36144579999996</v>
+      </c>
+      <c r="J168" s="16"/>
+      <c r="K168" s="16"/>
+      <c r="L168" s="16"/>
+      <c r="M168" s="12"/>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" s="15">
+        <v>8</v>
+      </c>
+      <c r="B169" s="16">
+        <v>336.50602400000002</v>
+      </c>
+      <c r="C169" s="12">
         <v>96.075000000000003</v>
       </c>
-      <c r="D169" t="s">
-        <v>14</v>
-      </c>
-      <c r="E169">
-        <v>2020</v>
-      </c>
-      <c r="F169" t="s">
+      <c r="D169" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F169" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A170">
-        <v>1</v>
-      </c>
-      <c r="B170">
-        <v>674.69879518072401</v>
-      </c>
-      <c r="C170">
+      <c r="G169" s="12"/>
+      <c r="H169" s="12"/>
+      <c r="I169" s="16">
+        <v>253.01204820000001</v>
+      </c>
+      <c r="J169" s="16"/>
+      <c r="K169" s="16"/>
+      <c r="L169" s="16"/>
+      <c r="M169" s="12"/>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" s="15">
+        <v>8</v>
+      </c>
+      <c r="B170" s="16">
+        <v>897.34939799999995</v>
+      </c>
+      <c r="C170" s="12">
         <v>102.9</v>
       </c>
-      <c r="D170" t="s">
-        <v>14</v>
-      </c>
-      <c r="E170">
-        <v>2020</v>
-      </c>
-      <c r="F170" t="s">
+      <c r="D170" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F170" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A171">
-        <v>1</v>
-      </c>
-      <c r="B171">
-        <v>168.67469879518401</v>
-      </c>
-      <c r="C171">
+      <c r="G170" s="12"/>
+      <c r="H170" s="12"/>
+      <c r="I170" s="16">
+        <v>674.69879519999995</v>
+      </c>
+      <c r="J170" s="16"/>
+      <c r="K170" s="16"/>
+      <c r="L170" s="16"/>
+      <c r="M170" s="12"/>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" s="15">
+        <v>8</v>
+      </c>
+      <c r="B171" s="16">
+        <v>224.33734899999999</v>
+      </c>
+      <c r="C171" s="12">
         <v>109.02500000000001</v>
       </c>
-      <c r="D171" t="s">
-        <v>14</v>
-      </c>
-      <c r="E171">
-        <v>2020</v>
-      </c>
-      <c r="F171" t="s">
+      <c r="D171" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F171" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A172">
-        <v>1</v>
-      </c>
-      <c r="B172">
-        <v>126.506024096386</v>
-      </c>
-      <c r="C172">
+      <c r="G171" s="12"/>
+      <c r="H171" s="12"/>
+      <c r="I171" s="16">
+        <v>168.67469879999999</v>
+      </c>
+      <c r="J171" s="16"/>
+      <c r="K171" s="16"/>
+      <c r="L171" s="16"/>
+      <c r="M171" s="12"/>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" s="15">
+        <v>8</v>
+      </c>
+      <c r="B172" s="16">
+        <v>168.25301200000001</v>
+      </c>
+      <c r="C172" s="12">
         <v>110.95</v>
       </c>
-      <c r="D172" t="s">
-        <v>14</v>
-      </c>
-      <c r="E172">
-        <v>2020</v>
-      </c>
-      <c r="F172" t="s">
+      <c r="D172" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E172" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F172" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A173">
-        <v>1</v>
-      </c>
-      <c r="B173">
-        <v>84.337349397595901</v>
-      </c>
-      <c r="C173">
+      <c r="G172" s="12"/>
+      <c r="H172" s="12"/>
+      <c r="I172" s="16">
+        <v>126.5060241</v>
+      </c>
+      <c r="J172" s="16"/>
+      <c r="K172" s="16"/>
+      <c r="L172" s="16"/>
+      <c r="M172" s="12"/>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" s="15">
+        <v>8</v>
+      </c>
+      <c r="B173" s="16">
+        <v>112.16867499999999</v>
+      </c>
+      <c r="C173" s="12">
         <v>113.05</v>
       </c>
-      <c r="D173" t="s">
-        <v>14</v>
-      </c>
-      <c r="E173">
-        <v>2020</v>
-      </c>
-      <c r="F173" t="s">
+      <c r="D173" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E173" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F173" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A174">
-        <v>1</v>
-      </c>
-      <c r="B174">
+      <c r="G173" s="12"/>
+      <c r="H173" s="12"/>
+      <c r="I173" s="16">
+        <v>84.337349399999994</v>
+      </c>
+      <c r="J173" s="16"/>
+      <c r="K173" s="16"/>
+      <c r="L173" s="16"/>
+      <c r="M173" s="12"/>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" s="15">
+        <v>8</v>
+      </c>
+      <c r="B174" s="16">
         <v>0</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="12">
         <v>118.125</v>
       </c>
-      <c r="D174" t="s">
-        <v>14</v>
-      </c>
-      <c r="E174">
-        <v>2020</v>
-      </c>
-      <c r="F174" t="s">
+      <c r="D174" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E174" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F174" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A175">
-        <v>1</v>
-      </c>
-      <c r="B175">
+      <c r="G174" s="12"/>
+      <c r="H174" s="12"/>
+      <c r="I174" s="16">
         <v>0</v>
       </c>
-      <c r="C175">
+      <c r="J174" s="16"/>
+      <c r="K174" s="16"/>
+      <c r="L174" s="16"/>
+      <c r="M174" s="12"/>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" s="15">
+        <v>8</v>
+      </c>
+      <c r="B175" s="16">
+        <v>0</v>
+      </c>
+      <c r="C175" s="12">
         <v>124.95</v>
       </c>
-      <c r="D175" t="s">
-        <v>14</v>
-      </c>
-      <c r="E175">
-        <v>2020</v>
-      </c>
-      <c r="F175" t="s">
+      <c r="D175" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E175" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F175" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A176">
-        <v>1</v>
-      </c>
-      <c r="B176">
+      <c r="G175" s="12"/>
+      <c r="H175" s="12"/>
+      <c r="I175" s="16">
         <v>0</v>
       </c>
-      <c r="C176">
+      <c r="J175" s="16"/>
+      <c r="K175" s="16"/>
+      <c r="L175" s="16"/>
+      <c r="M175" s="12"/>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" s="15">
+        <v>9</v>
+      </c>
+      <c r="B176" s="16">
+        <v>0</v>
+      </c>
+      <c r="C176" s="12">
         <v>0.96269554753309405</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D176" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E176">
-        <v>2020</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="E176" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F176" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G176">
-        <v>8773.0337080000008</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A177">
-        <v>1</v>
-      </c>
-      <c r="B177">
+      <c r="G176" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H176" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I176" s="16">
         <v>0</v>
       </c>
-      <c r="C177">
+      <c r="J176" s="16"/>
+      <c r="K176" s="16"/>
+      <c r="L176" s="16"/>
+      <c r="M176" s="12"/>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A177" s="15">
+        <v>9</v>
+      </c>
+      <c r="B177" s="16">
+        <v>0</v>
+      </c>
+      <c r="C177" s="12">
         <v>8.8567990373044498</v>
       </c>
-      <c r="D177" t="s">
+      <c r="D177" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E177">
-        <v>2020</v>
-      </c>
-      <c r="F177" t="s">
+      <c r="E177" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F177" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A178">
-        <v>1</v>
-      </c>
-      <c r="B178">
+      <c r="G177" s="12"/>
+      <c r="H177" s="12"/>
+      <c r="I177" s="16">
         <v>0</v>
       </c>
-      <c r="C178">
+      <c r="J177" s="16"/>
+      <c r="K177" s="16"/>
+      <c r="L177" s="16"/>
+      <c r="M177" s="12"/>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A178" s="15">
+        <v>9</v>
+      </c>
+      <c r="B178" s="16">
+        <v>0</v>
+      </c>
+      <c r="C178" s="12">
         <v>17.906137184115501</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D178" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E178">
-        <v>2020</v>
-      </c>
-      <c r="F178" t="s">
+      <c r="E178" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F178" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A179">
-        <v>1</v>
-      </c>
-      <c r="B179">
-        <v>44.943820224718998</v>
-      </c>
-      <c r="C179">
+      <c r="G178" s="12"/>
+      <c r="H178" s="12"/>
+      <c r="I178" s="16">
+        <v>0</v>
+      </c>
+      <c r="J178" s="16"/>
+      <c r="K178" s="16"/>
+      <c r="L178" s="16"/>
+      <c r="M178" s="12"/>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179" s="15">
+        <v>9</v>
+      </c>
+      <c r="B179" s="16">
+        <v>59.775281</v>
+      </c>
+      <c r="C179" s="12">
         <v>24.067388688327298</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E179">
-        <v>2020</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="E179" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F179" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A180">
-        <v>1</v>
-      </c>
-      <c r="B180">
-        <v>152.80898876404399</v>
-      </c>
-      <c r="C180">
+      <c r="G179" s="12"/>
+      <c r="H179" s="12"/>
+      <c r="I179" s="16">
+        <v>44.943820219999999</v>
+      </c>
+      <c r="J179" s="16"/>
+      <c r="K179" s="16"/>
+      <c r="L179" s="16"/>
+      <c r="M179" s="12"/>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180" s="15">
+        <v>9</v>
+      </c>
+      <c r="B180" s="16">
+        <v>203.23595499999999</v>
+      </c>
+      <c r="C180" s="12">
         <v>30.036101083032499</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E180">
-        <v>2020</v>
-      </c>
-      <c r="F180" t="s">
+      <c r="E180" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F180" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A181">
-        <v>1</v>
-      </c>
-      <c r="B181">
-        <v>53.932584269662797</v>
-      </c>
-      <c r="C181">
+      <c r="G180" s="12"/>
+      <c r="H180" s="12"/>
+      <c r="I180" s="16">
+        <v>152.80898880000001</v>
+      </c>
+      <c r="J180" s="16"/>
+      <c r="K180" s="16"/>
+      <c r="L180" s="16"/>
+      <c r="M180" s="12"/>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A181" s="15">
+        <v>9</v>
+      </c>
+      <c r="B181" s="16">
+        <v>71.730337000000006</v>
+      </c>
+      <c r="C181" s="12">
         <v>36.004813477737599</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D181" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E181">
-        <v>2020</v>
-      </c>
-      <c r="F181" t="s">
+      <c r="E181" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F181" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A182">
-        <v>1</v>
-      </c>
-      <c r="B182">
-        <v>94.382022471909906</v>
-      </c>
-      <c r="C182">
+      <c r="G181" s="12"/>
+      <c r="H181" s="12"/>
+      <c r="I181" s="16">
+        <v>53.93258427</v>
+      </c>
+      <c r="J181" s="16"/>
+      <c r="K181" s="16"/>
+      <c r="L181" s="16"/>
+      <c r="M181" s="12"/>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A182" s="15">
+        <v>9</v>
+      </c>
+      <c r="B182" s="16">
+        <v>125.52809000000001</v>
+      </c>
+      <c r="C182" s="12">
         <v>37.930204572803802</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E182">
-        <v>2020</v>
-      </c>
-      <c r="F182" t="s">
+      <c r="E182" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F182" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A183">
-        <v>1</v>
-      </c>
-      <c r="B183">
-        <v>49.438202247190901</v>
-      </c>
-      <c r="C183">
+      <c r="G182" s="12"/>
+      <c r="H182" s="12"/>
+      <c r="I182" s="16">
+        <v>94.382022469999995</v>
+      </c>
+      <c r="J182" s="16"/>
+      <c r="K182" s="16"/>
+      <c r="L182" s="16"/>
+      <c r="M182" s="12"/>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A183" s="15">
+        <v>9</v>
+      </c>
+      <c r="B183" s="16">
+        <v>65.752808999999999</v>
+      </c>
+      <c r="C183" s="12">
         <v>40.048134777376603</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E183">
-        <v>2020</v>
-      </c>
-      <c r="F183" t="s">
+      <c r="E183" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F183" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A184">
-        <v>1</v>
-      </c>
-      <c r="B184">
-        <v>89.887640449438095</v>
-      </c>
-      <c r="C184">
+      <c r="G183" s="12"/>
+      <c r="H183" s="12"/>
+      <c r="I183" s="16">
+        <v>49.438202250000003</v>
+      </c>
+      <c r="J183" s="16"/>
+      <c r="K183" s="16"/>
+      <c r="L183" s="16"/>
+      <c r="M183" s="12"/>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A184" s="15">
+        <v>9</v>
+      </c>
+      <c r="B184" s="16">
+        <v>119.550562</v>
+      </c>
+      <c r="C184" s="12">
         <v>41.010830324909698</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E184">
-        <v>2020</v>
-      </c>
-      <c r="F184" t="s">
+      <c r="E184" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F184" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A185">
-        <v>1</v>
-      </c>
-      <c r="B185">
-        <v>98.876404494382001</v>
-      </c>
-      <c r="C185">
+      <c r="G184" s="12"/>
+      <c r="H184" s="12"/>
+      <c r="I184" s="16">
+        <v>89.887640450000006</v>
+      </c>
+      <c r="J184" s="16"/>
+      <c r="K184" s="16"/>
+      <c r="L184" s="16"/>
+      <c r="M184" s="12"/>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A185" s="15">
+        <v>9</v>
+      </c>
+      <c r="B185" s="16">
+        <v>131.505618</v>
+      </c>
+      <c r="C185" s="12">
         <v>46.979542719614898</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D185" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E185">
-        <v>2020</v>
-      </c>
-      <c r="F185" t="s">
+      <c r="E185" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F185" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A186">
-        <v>1</v>
-      </c>
-      <c r="B186">
-        <v>404.49438202247097</v>
-      </c>
-      <c r="C186">
+      <c r="G185" s="12"/>
+      <c r="H185" s="12"/>
+      <c r="I185" s="16">
+        <v>98.876404489999999</v>
+      </c>
+      <c r="J185" s="16"/>
+      <c r="K185" s="16"/>
+      <c r="L185" s="16"/>
+      <c r="M185" s="12"/>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A186" s="15">
+        <v>9</v>
+      </c>
+      <c r="B186" s="16">
+        <v>537.97752800000001</v>
+      </c>
+      <c r="C186" s="12">
         <v>52.948255114320098</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D186" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E186">
-        <v>2020</v>
-      </c>
-      <c r="F186" t="s">
+      <c r="E186" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F186" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A187">
-        <v>1</v>
-      </c>
-      <c r="B187">
-        <v>444.94382022471899</v>
-      </c>
-      <c r="C187">
+      <c r="G186" s="12"/>
+      <c r="H186" s="12"/>
+      <c r="I186" s="16">
+        <v>404.49438199999997</v>
+      </c>
+      <c r="J186" s="16"/>
+      <c r="K186" s="16"/>
+      <c r="L186" s="16"/>
+      <c r="M186" s="12"/>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187" s="15">
+        <v>9</v>
+      </c>
+      <c r="B187" s="16">
+        <v>591.77528099999995</v>
+      </c>
+      <c r="C187" s="12">
         <v>60.072202166064898</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D187" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E187">
-        <v>2020</v>
-      </c>
-      <c r="F187" t="s">
+      <c r="E187" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F187" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A188">
-        <v>1</v>
-      </c>
-      <c r="B188">
-        <v>804.494382022472</v>
-      </c>
-      <c r="C188">
+      <c r="G187" s="12"/>
+      <c r="H187" s="12"/>
+      <c r="I187" s="16">
+        <v>444.9438202</v>
+      </c>
+      <c r="J187" s="16"/>
+      <c r="K187" s="16"/>
+      <c r="L187" s="16"/>
+      <c r="M187" s="12"/>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188" s="15">
+        <v>9</v>
+      </c>
+      <c r="B188" s="16">
+        <v>1069.9775279999999</v>
+      </c>
+      <c r="C188" s="12">
         <v>67.966305655836294</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D188" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E188">
-        <v>2020</v>
-      </c>
-      <c r="F188" t="s">
+      <c r="E188" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F188" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A189">
-        <v>1</v>
-      </c>
-      <c r="B189">
-        <v>611.23595505617902</v>
-      </c>
-      <c r="C189">
+      <c r="G188" s="12"/>
+      <c r="H188" s="12"/>
+      <c r="I188" s="16">
+        <v>804.49438199999997</v>
+      </c>
+      <c r="J188" s="16"/>
+      <c r="K188" s="16"/>
+      <c r="L188" s="16"/>
+      <c r="M188" s="12"/>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189" s="15">
+        <v>9</v>
+      </c>
+      <c r="B189" s="16">
+        <v>812.94381999999996</v>
+      </c>
+      <c r="C189" s="12">
         <v>73.935018050541501</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D189" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E189">
-        <v>2020</v>
-      </c>
-      <c r="F189" t="s">
+      <c r="E189" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F189" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A190">
-        <v>1</v>
-      </c>
-      <c r="B190">
-        <v>853.93258426966202</v>
-      </c>
-      <c r="C190">
+      <c r="G189" s="12"/>
+      <c r="H189" s="12"/>
+      <c r="I189" s="16">
+        <v>611.23595509999996</v>
+      </c>
+      <c r="J189" s="16"/>
+      <c r="K189" s="16"/>
+      <c r="L189" s="16"/>
+      <c r="M189" s="12"/>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A190" s="15">
+        <v>9</v>
+      </c>
+      <c r="B190" s="16">
+        <v>1135.730337</v>
+      </c>
+      <c r="C190" s="12">
         <v>79.903730445246595</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D190" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E190">
-        <v>2020</v>
-      </c>
-      <c r="F190" t="s">
+      <c r="E190" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F190" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A191">
-        <v>1</v>
-      </c>
-      <c r="B191">
-        <v>840.44943820224705</v>
-      </c>
-      <c r="C191">
+      <c r="G190" s="12"/>
+      <c r="H190" s="12"/>
+      <c r="I190" s="16">
+        <v>853.93258430000003</v>
+      </c>
+      <c r="J190" s="16"/>
+      <c r="K190" s="16"/>
+      <c r="L190" s="16"/>
+      <c r="M190" s="12"/>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191" s="15">
+        <v>9</v>
+      </c>
+      <c r="B191" s="16">
+        <v>1117.7977530000001</v>
+      </c>
+      <c r="C191" s="12">
         <v>91.070998796630505</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D191" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E191">
-        <v>2020</v>
-      </c>
-      <c r="F191" t="s">
+      <c r="E191" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F191" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A192">
-        <v>1</v>
-      </c>
-      <c r="B192">
-        <v>1271.9101123595501</v>
-      </c>
-      <c r="C192">
+      <c r="G191" s="12"/>
+      <c r="H191" s="12"/>
+      <c r="I191" s="16">
+        <v>840.44943820000003</v>
+      </c>
+      <c r="J191" s="16"/>
+      <c r="K191" s="16"/>
+      <c r="L191" s="16"/>
+      <c r="M191" s="12"/>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192" s="15">
+        <v>9</v>
+      </c>
+      <c r="B192" s="16">
+        <v>1691.640449</v>
+      </c>
+      <c r="C192" s="12">
         <v>96.077015643802596</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D192" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E192">
-        <v>2020</v>
-      </c>
-      <c r="F192" t="s">
+      <c r="E192" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F192" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A193">
-        <v>1</v>
-      </c>
-      <c r="B193">
-        <v>975.28089887640397</v>
-      </c>
-      <c r="C193">
+      <c r="G192" s="12"/>
+      <c r="H192" s="12"/>
+      <c r="I192" s="16">
+        <v>1271.910112</v>
+      </c>
+      <c r="J192" s="16"/>
+      <c r="K192" s="16"/>
+      <c r="L192" s="16"/>
+      <c r="M192" s="12"/>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" s="15">
+        <v>9</v>
+      </c>
+      <c r="B193" s="16">
+        <v>1297.1235959999999</v>
+      </c>
+      <c r="C193" s="12">
         <v>103.00842358604</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D193" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E193">
-        <v>2020</v>
-      </c>
-      <c r="F193" t="s">
+      <c r="E193" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F193" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A194">
-        <v>1</v>
-      </c>
-      <c r="B194">
-        <v>633.707865168539</v>
-      </c>
-      <c r="C194">
+      <c r="G193" s="12"/>
+      <c r="H193" s="12"/>
+      <c r="I193" s="16">
+        <v>975.28089890000001</v>
+      </c>
+      <c r="J193" s="16"/>
+      <c r="K193" s="16"/>
+      <c r="L193" s="16"/>
+      <c r="M193" s="12"/>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194" s="15">
+        <v>9</v>
+      </c>
+      <c r="B194" s="16">
+        <v>842.83146099999999</v>
+      </c>
+      <c r="C194" s="12">
         <v>108.977135980746</v>
       </c>
-      <c r="D194" t="s">
+      <c r="D194" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E194">
-        <v>2020</v>
-      </c>
-      <c r="F194" t="s">
+      <c r="E194" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F194" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A195">
-        <v>1</v>
-      </c>
-      <c r="B195">
-        <v>759.55056179775295</v>
-      </c>
-      <c r="C195">
+      <c r="G194" s="12"/>
+      <c r="H194" s="12"/>
+      <c r="I194" s="16">
+        <v>633.70786520000001</v>
+      </c>
+      <c r="J194" s="16"/>
+      <c r="K194" s="16"/>
+      <c r="L194" s="16"/>
+      <c r="M194" s="12"/>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" s="15">
+        <v>9</v>
+      </c>
+      <c r="B195" s="16">
+        <v>1010.2022470000001</v>
+      </c>
+      <c r="C195" s="12">
         <v>115.90854392298399</v>
       </c>
-      <c r="D195" t="s">
+      <c r="D195" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E195">
-        <v>2020</v>
-      </c>
-      <c r="F195" t="s">
+      <c r="E195" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F195" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A196">
-        <v>1</v>
-      </c>
-      <c r="B196">
-        <v>350.56179775280901</v>
-      </c>
-      <c r="C196">
+      <c r="G195" s="12"/>
+      <c r="H195" s="12"/>
+      <c r="I195" s="16">
+        <v>759.55056179999997</v>
+      </c>
+      <c r="J195" s="16"/>
+      <c r="K195" s="16"/>
+      <c r="L195" s="16"/>
+      <c r="M195" s="12"/>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" s="15">
+        <v>9</v>
+      </c>
+      <c r="B196" s="16">
+        <v>466.24719099999999</v>
+      </c>
+      <c r="C196" s="12">
         <v>122.069795427196</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D196" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E196">
-        <v>2020</v>
-      </c>
-      <c r="F196" t="s">
+      <c r="E196" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F196" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A197">
-        <v>1</v>
-      </c>
-      <c r="B197">
-        <v>157.30337078651701</v>
-      </c>
-      <c r="C197">
+      <c r="G196" s="12"/>
+      <c r="H196" s="12"/>
+      <c r="I196" s="16">
+        <v>350.56179780000002</v>
+      </c>
+      <c r="J196" s="16"/>
+      <c r="K196" s="16"/>
+      <c r="L196" s="16"/>
+      <c r="M196" s="12"/>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" s="15">
+        <v>9</v>
+      </c>
+      <c r="B197" s="16">
+        <v>209.213483</v>
+      </c>
+      <c r="C197" s="12">
         <v>123.995186522262</v>
       </c>
-      <c r="D197" t="s">
+      <c r="D197" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E197">
-        <v>2020</v>
-      </c>
-      <c r="F197" t="s">
+      <c r="E197" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F197" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A198">
-        <v>1</v>
-      </c>
-      <c r="B198">
-        <v>80.898876404494501</v>
-      </c>
-      <c r="C198">
+      <c r="G197" s="12"/>
+      <c r="H197" s="12"/>
+      <c r="I197" s="16">
+        <v>157.30337080000001</v>
+      </c>
+      <c r="J197" s="16"/>
+      <c r="K197" s="16"/>
+      <c r="L197" s="16"/>
+      <c r="M197" s="12"/>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198" s="15">
+        <v>9</v>
+      </c>
+      <c r="B198" s="16">
+        <v>107.595506</v>
+      </c>
+      <c r="C198" s="12">
         <v>126.113116726835</v>
       </c>
-      <c r="D198" t="s">
+      <c r="D198" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E198">
-        <v>2020</v>
-      </c>
-      <c r="F198" t="s">
+      <c r="E198" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F198" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A199">
-        <v>1</v>
-      </c>
-      <c r="B199">
+      <c r="G198" s="12"/>
+      <c r="H198" s="12"/>
+      <c r="I198" s="16">
+        <v>80.898876400000006</v>
+      </c>
+      <c r="J198" s="16"/>
+      <c r="K198" s="16"/>
+      <c r="L198" s="16"/>
+      <c r="M198" s="12"/>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" s="15">
+        <v>9</v>
+      </c>
+      <c r="B199" s="16">
         <v>0</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="12">
         <v>131.11913357400701</v>
       </c>
-      <c r="D199" t="s">
+      <c r="D199" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E199">
-        <v>2020</v>
-      </c>
-      <c r="F199" t="s">
+      <c r="E199" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F199" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A200">
-        <v>1</v>
-      </c>
-      <c r="B200">
+      <c r="G199" s="12"/>
+      <c r="H199" s="12"/>
+      <c r="I199" s="16">
         <v>0</v>
       </c>
-      <c r="C200">
+      <c r="J199" s="16"/>
+      <c r="K199" s="16"/>
+      <c r="L199" s="16"/>
+      <c r="M199" s="12"/>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A200" s="15">
+        <v>9</v>
+      </c>
+      <c r="B200" s="16">
+        <v>0</v>
+      </c>
+      <c r="C200" s="12">
         <v>137.087845968712</v>
       </c>
-      <c r="D200" t="s">
+      <c r="D200" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E200">
-        <v>2020</v>
-      </c>
-      <c r="F200" t="s">
+      <c r="E200" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F200" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A201">
-        <v>1</v>
-      </c>
-      <c r="B201">
+      <c r="G200" s="12"/>
+      <c r="H200" s="12"/>
+      <c r="I200" s="16">
         <v>0</v>
       </c>
-      <c r="C201">
+      <c r="J200" s="16"/>
+      <c r="K200" s="16"/>
+      <c r="L200" s="16"/>
+      <c r="M200" s="12"/>
+    </row>
+    <row r="201" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A201" s="15">
+        <v>10</v>
+      </c>
+      <c r="B201" s="16">
+        <v>0</v>
+      </c>
+      <c r="C201" s="12">
         <v>2.05378973105134</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D201" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E201">
-        <v>2020</v>
-      </c>
-      <c r="F201" s="2" t="s">
+      <c r="E201" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F201" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="G201">
-        <v>5772.8531860000003</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A202">
-        <v>1</v>
-      </c>
-      <c r="B202">
+      <c r="G201" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H201" s="12"/>
+      <c r="I201" s="16">
         <v>0</v>
       </c>
-      <c r="C202">
+      <c r="J201" s="16"/>
+      <c r="K201" s="16"/>
+      <c r="L201" s="16"/>
+      <c r="M201" s="12"/>
+    </row>
+    <row r="202" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A202" s="15">
+        <v>10</v>
+      </c>
+      <c r="B202" s="16">
+        <v>0</v>
+      </c>
+      <c r="C202" s="12">
         <v>10.9535452322738</v>
       </c>
-      <c r="D202" t="s">
+      <c r="D202" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E202">
-        <v>2020</v>
-      </c>
-      <c r="F202" s="2" t="s">
+      <c r="E202" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F202" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A203">
-        <v>1</v>
-      </c>
-      <c r="B203">
-        <v>36.011080332410501</v>
-      </c>
-      <c r="C203">
+      <c r="G202" s="12"/>
+      <c r="H202" s="12"/>
+      <c r="I202" s="16">
+        <v>0</v>
+      </c>
+      <c r="J202" s="16"/>
+      <c r="K202" s="16"/>
+      <c r="L202" s="16"/>
+      <c r="M202" s="12"/>
+    </row>
+    <row r="203" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A203" s="15">
+        <v>10</v>
+      </c>
+      <c r="B203" s="16">
+        <v>47.894736999999999</v>
+      </c>
+      <c r="C203" s="12">
         <v>22.078239608801901</v>
       </c>
-      <c r="D203" t="s">
-        <v>14</v>
-      </c>
-      <c r="E203">
-        <v>2020</v>
-      </c>
-      <c r="F203" s="2" t="s">
+      <c r="D203" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E203" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F203" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A204">
-        <v>1</v>
-      </c>
-      <c r="B204">
-        <v>121.883656509695</v>
-      </c>
-      <c r="C204">
+      <c r="G203" s="12"/>
+      <c r="H203" s="12"/>
+      <c r="I203" s="16">
+        <v>36.011080329999999</v>
+      </c>
+      <c r="J203" s="16"/>
+      <c r="K203" s="16"/>
+      <c r="L203" s="16"/>
+      <c r="M203" s="12"/>
+    </row>
+    <row r="204" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A204" s="15">
+        <v>10</v>
+      </c>
+      <c r="B204" s="16">
+        <v>162.10526300000001</v>
+      </c>
+      <c r="C204" s="12">
         <v>30.122249388753001</v>
       </c>
-      <c r="D204" t="s">
-        <v>14</v>
-      </c>
-      <c r="E204">
-        <v>2020</v>
-      </c>
-      <c r="F204" s="2" t="s">
+      <c r="D204" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E204" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F204" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A205">
-        <v>1</v>
-      </c>
-      <c r="B205">
-        <v>49.861495844875201</v>
-      </c>
-      <c r="C205">
+      <c r="G204" s="12"/>
+      <c r="H204" s="12"/>
+      <c r="I204" s="16">
+        <v>121.8836565</v>
+      </c>
+      <c r="J204" s="16"/>
+      <c r="K204" s="16"/>
+      <c r="L204" s="16"/>
+      <c r="M204" s="12"/>
+    </row>
+    <row r="205" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A205" s="15">
+        <v>10</v>
+      </c>
+      <c r="B205" s="16">
+        <v>66.315790000000007</v>
+      </c>
+      <c r="C205" s="12">
         <v>37.995110024449801</v>
       </c>
-      <c r="D205" t="s">
-        <v>14</v>
-      </c>
-      <c r="E205">
-        <v>2020</v>
-      </c>
-      <c r="F205" s="2" t="s">
+      <c r="D205" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E205" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F205" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A206">
-        <v>1</v>
-      </c>
-      <c r="B206">
-        <v>545.70637119113496</v>
-      </c>
-      <c r="C206">
+      <c r="G205" s="12"/>
+      <c r="H205" s="12"/>
+      <c r="I205" s="16">
+        <v>49.861495840000003</v>
+      </c>
+      <c r="J205" s="16"/>
+      <c r="K205" s="16"/>
+      <c r="L205" s="16"/>
+      <c r="M205" s="12"/>
+    </row>
+    <row r="206" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A206" s="15">
+        <v>10</v>
+      </c>
+      <c r="B206" s="16">
+        <v>725.78947400000004</v>
+      </c>
+      <c r="C206" s="12">
         <v>46.039119804400897</v>
       </c>
-      <c r="D206" t="s">
-        <v>14</v>
-      </c>
-      <c r="E206">
-        <v>2020</v>
-      </c>
-      <c r="F206" s="2" t="s">
+      <c r="D206" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E206" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F206" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A207">
-        <v>1</v>
-      </c>
-      <c r="B207">
-        <v>80.332409972299004</v>
-      </c>
-      <c r="C207">
+      <c r="G206" s="12"/>
+      <c r="H206" s="12"/>
+      <c r="I206" s="16">
+        <v>545.70637120000004</v>
+      </c>
+      <c r="J206" s="16"/>
+      <c r="K206" s="16"/>
+      <c r="L206" s="16"/>
+      <c r="M206" s="12"/>
+    </row>
+    <row r="207" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A207" s="15">
+        <v>10</v>
+      </c>
+      <c r="B207" s="16">
+        <v>106.842105</v>
+      </c>
+      <c r="C207" s="12">
         <v>48.948655256723697</v>
       </c>
-      <c r="D207" t="s">
-        <v>14</v>
-      </c>
-      <c r="E207">
-        <v>2020</v>
-      </c>
-      <c r="F207" s="2" t="s">
+      <c r="D207" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E207" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F207" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A208">
-        <v>1</v>
-      </c>
-      <c r="B208">
-        <v>282.548476454293</v>
-      </c>
-      <c r="C208">
+      <c r="G207" s="12"/>
+      <c r="H207" s="12"/>
+      <c r="I207" s="16">
+        <v>80.33240997</v>
+      </c>
+      <c r="J207" s="16"/>
+      <c r="K207" s="16"/>
+      <c r="L207" s="16"/>
+      <c r="M207" s="12"/>
+    </row>
+    <row r="208" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A208" s="15">
+        <v>10</v>
+      </c>
+      <c r="B208" s="16">
+        <v>375.78947399999998</v>
+      </c>
+      <c r="C208" s="12">
         <v>51.002444987775</v>
       </c>
-      <c r="D208" t="s">
-        <v>14</v>
-      </c>
-      <c r="E208">
-        <v>2020</v>
-      </c>
-      <c r="F208" s="2" t="s">
+      <c r="D208" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E208" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F208" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A209">
-        <v>1</v>
-      </c>
-      <c r="B209">
-        <v>235.45706371191099</v>
-      </c>
-      <c r="C209">
+      <c r="G208" s="12"/>
+      <c r="H208" s="12"/>
+      <c r="I208" s="16">
+        <v>282.54847649999999</v>
+      </c>
+      <c r="J208" s="16"/>
+      <c r="K208" s="16"/>
+      <c r="L208" s="16"/>
+      <c r="M208" s="12"/>
+    </row>
+    <row r="209" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A209" s="15">
+        <v>10</v>
+      </c>
+      <c r="B209" s="16">
+        <v>313.157895</v>
+      </c>
+      <c r="C209" s="12">
         <v>55.794621026894802</v>
       </c>
-      <c r="D209" t="s">
-        <v>14</v>
-      </c>
-      <c r="E209">
-        <v>2020</v>
-      </c>
-      <c r="F209" s="2" t="s">
+      <c r="D209" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E209" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F209" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A210">
-        <v>1</v>
-      </c>
-      <c r="B210">
-        <v>432.13296398891902</v>
-      </c>
-      <c r="C210">
+      <c r="G209" s="12"/>
+      <c r="H209" s="12"/>
+      <c r="I209" s="16">
+        <v>235.45706369999999</v>
+      </c>
+      <c r="J209" s="16"/>
+      <c r="K209" s="16"/>
+      <c r="L209" s="16"/>
+      <c r="M209" s="12"/>
+    </row>
+    <row r="210" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A210" s="15">
+        <v>10</v>
+      </c>
+      <c r="B210" s="16">
+        <v>574.73684200000002</v>
+      </c>
+      <c r="C210" s="12">
         <v>65.036674816625904</v>
       </c>
-      <c r="D210" t="s">
-        <v>14</v>
-      </c>
-      <c r="E210">
-        <v>2020</v>
-      </c>
-      <c r="F210" s="2" t="s">
+      <c r="D210" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E210" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F210" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A211">
-        <v>1</v>
-      </c>
-      <c r="B211">
-        <v>614.95844875346199</v>
-      </c>
-      <c r="C211">
+      <c r="G210" s="12"/>
+      <c r="H210" s="12"/>
+      <c r="I210" s="16">
+        <v>432.13296400000002</v>
+      </c>
+      <c r="J210" s="16"/>
+      <c r="K210" s="16"/>
+      <c r="L210" s="16"/>
+      <c r="M210" s="12"/>
+    </row>
+    <row r="211" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A211" s="15">
+        <v>10</v>
+      </c>
+      <c r="B211" s="16">
+        <v>817.89473699999996</v>
+      </c>
+      <c r="C211" s="12">
         <v>71.026894865525605</v>
       </c>
-      <c r="D211" t="s">
-        <v>14</v>
-      </c>
-      <c r="E211">
-        <v>2020</v>
-      </c>
-      <c r="F211" s="2" t="s">
+      <c r="D211" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E211" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F211" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A212">
-        <v>1</v>
-      </c>
-      <c r="B212">
-        <v>554.01662049861397</v>
-      </c>
-      <c r="C212">
+      <c r="G211" s="12"/>
+      <c r="H211" s="12"/>
+      <c r="I211" s="16">
+        <v>614.95844880000004</v>
+      </c>
+      <c r="J211" s="16"/>
+      <c r="K211" s="16"/>
+      <c r="L211" s="16"/>
+      <c r="M211" s="12"/>
+    </row>
+    <row r="212" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A212" s="15">
+        <v>10</v>
+      </c>
+      <c r="B212" s="16">
+        <v>736.84210499999995</v>
+      </c>
+      <c r="C212" s="12">
         <v>81.980440097799502</v>
       </c>
-      <c r="D212" t="s">
-        <v>14</v>
-      </c>
-      <c r="E212">
-        <v>2020</v>
-      </c>
-      <c r="F212" s="2" t="s">
+      <c r="D212" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E212" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F212" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A213">
-        <v>1</v>
-      </c>
-      <c r="B213">
-        <v>944.59833795013799</v>
-      </c>
-      <c r="C213">
+      <c r="G212" s="12"/>
+      <c r="H212" s="12"/>
+      <c r="I212" s="16">
+        <v>554.01662050000004</v>
+      </c>
+      <c r="J212" s="16"/>
+      <c r="K212" s="16"/>
+      <c r="L212" s="16"/>
+      <c r="M212" s="12"/>
+    </row>
+    <row r="213" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A213" s="15">
+        <v>10</v>
+      </c>
+      <c r="B213" s="16">
+        <v>1256.3157900000001</v>
+      </c>
+      <c r="C213" s="12">
         <v>86.943765281173597</v>
       </c>
-      <c r="D213" t="s">
-        <v>14</v>
-      </c>
-      <c r="E213">
-        <v>2020</v>
-      </c>
-      <c r="F213" s="2" t="s">
+      <c r="D213" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E213" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F213" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A214">
-        <v>1</v>
-      </c>
-      <c r="B214">
-        <v>739.61218836565001</v>
-      </c>
-      <c r="C214">
+      <c r="G213" s="12"/>
+      <c r="H213" s="12"/>
+      <c r="I213" s="16">
+        <v>944.59833800000001</v>
+      </c>
+      <c r="J213" s="16"/>
+      <c r="K213" s="16"/>
+      <c r="L213" s="16"/>
+      <c r="M213" s="12"/>
+    </row>
+    <row r="214" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A214" s="15">
+        <v>10</v>
+      </c>
+      <c r="B214" s="16">
+        <v>983.684211</v>
+      </c>
+      <c r="C214" s="12">
         <v>93.105134474327599</v>
       </c>
-      <c r="D214" t="s">
-        <v>14</v>
-      </c>
-      <c r="E214">
-        <v>2020</v>
-      </c>
-      <c r="F214" s="2" t="s">
+      <c r="D214" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E214" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F214" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A215">
-        <v>1</v>
-      </c>
-      <c r="B215">
-        <v>645.42936288088595</v>
-      </c>
-      <c r="C215">
+      <c r="G214" s="12"/>
+      <c r="H214" s="12"/>
+      <c r="I214" s="16">
+        <v>739.61218840000004</v>
+      </c>
+      <c r="J214" s="16"/>
+      <c r="K214" s="16"/>
+      <c r="L214" s="16"/>
+      <c r="M214" s="12"/>
+    </row>
+    <row r="215" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A215" s="15">
+        <v>10</v>
+      </c>
+      <c r="B215" s="16">
+        <v>858.42105300000003</v>
+      </c>
+      <c r="C215" s="12">
         <v>100.122249388753</v>
       </c>
-      <c r="D215" t="s">
-        <v>14</v>
-      </c>
-      <c r="E215">
-        <v>2020</v>
-      </c>
-      <c r="F215" s="2" t="s">
+      <c r="D215" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E215" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F215" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A216">
-        <v>1</v>
-      </c>
-      <c r="B216">
-        <v>340.72022160664801</v>
-      </c>
-      <c r="C216">
+      <c r="G215" s="12"/>
+      <c r="H215" s="12"/>
+      <c r="I215" s="16">
+        <v>645.4293629</v>
+      </c>
+      <c r="J215" s="16"/>
+      <c r="K215" s="16"/>
+      <c r="L215" s="16"/>
+      <c r="M215" s="12"/>
+    </row>
+    <row r="216" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A216" s="15">
+        <v>10</v>
+      </c>
+      <c r="B216" s="16">
+        <v>453.157895</v>
+      </c>
+      <c r="C216" s="12">
         <v>107.995110024449</v>
       </c>
-      <c r="D216" t="s">
-        <v>14</v>
-      </c>
-      <c r="E216">
-        <v>2020</v>
-      </c>
-      <c r="F216" s="2" t="s">
+      <c r="D216" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E216" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F216" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A217">
-        <v>1</v>
-      </c>
-      <c r="B217">
-        <v>116.34349030470899</v>
-      </c>
-      <c r="C217">
+      <c r="G216" s="12"/>
+      <c r="H216" s="12"/>
+      <c r="I216" s="16">
+        <v>340.7202216</v>
+      </c>
+      <c r="J216" s="16"/>
+      <c r="K216" s="16"/>
+      <c r="L216" s="16"/>
+      <c r="M216" s="12"/>
+    </row>
+    <row r="217" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A217" s="15">
+        <v>10</v>
+      </c>
+      <c r="B217" s="16">
+        <v>154.736842</v>
+      </c>
+      <c r="C217" s="12">
         <v>113.985330073349</v>
       </c>
-      <c r="D217" t="s">
-        <v>14</v>
-      </c>
-      <c r="E217">
-        <v>2020</v>
-      </c>
-      <c r="F217" s="2" t="s">
+      <c r="D217" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E217" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F217" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A218">
-        <v>1</v>
-      </c>
-      <c r="B218">
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="16">
+        <v>116.3434903</v>
+      </c>
+      <c r="J217" s="16"/>
+      <c r="K217" s="16"/>
+      <c r="L217" s="16"/>
+      <c r="M217" s="12"/>
+    </row>
+    <row r="218" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A218" s="15">
+        <v>10</v>
+      </c>
+      <c r="B218" s="16">
         <v>0</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="12">
         <v>116.0391198044</v>
       </c>
-      <c r="D218" t="s">
-        <v>14</v>
-      </c>
-      <c r="E218">
-        <v>2020</v>
-      </c>
-      <c r="F218" s="2" t="s">
+      <c r="D218" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E218" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F218" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A219">
-        <v>1</v>
-      </c>
-      <c r="B219">
-        <v>30.4709141274238</v>
-      </c>
-      <c r="C219">
+      <c r="G218" s="12"/>
+      <c r="H218" s="12"/>
+      <c r="I218" s="16">
+        <v>0</v>
+      </c>
+      <c r="J218" s="16"/>
+      <c r="K218" s="16"/>
+      <c r="L218" s="16"/>
+      <c r="M218" s="12"/>
+    </row>
+    <row r="219" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A219" s="15">
+        <v>10</v>
+      </c>
+      <c r="B219" s="16">
+        <v>40.526316000000001</v>
+      </c>
+      <c r="C219" s="12">
         <v>117.92176039119801</v>
       </c>
-      <c r="D219" t="s">
-        <v>14</v>
-      </c>
-      <c r="E219">
-        <v>2020</v>
-      </c>
-      <c r="F219" s="2" t="s">
+      <c r="D219" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E219" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F219" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A220">
-        <v>1</v>
-      </c>
-      <c r="B220">
-        <v>2.7700831024931101</v>
-      </c>
-      <c r="C220">
+      <c r="G219" s="12"/>
+      <c r="H219" s="12"/>
+      <c r="I219" s="16">
+        <v>30.470914130000001</v>
+      </c>
+      <c r="J219" s="16"/>
+      <c r="K219" s="16"/>
+      <c r="L219" s="16"/>
+      <c r="M219" s="12"/>
+    </row>
+    <row r="220" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A220" s="15">
+        <v>10</v>
+      </c>
+      <c r="B220" s="16">
+        <v>3.6842109999999999</v>
+      </c>
+      <c r="C220" s="12">
         <v>124.938875305623</v>
       </c>
-      <c r="D220" t="s">
-        <v>14</v>
-      </c>
-      <c r="E220">
-        <v>2020</v>
-      </c>
-      <c r="F220" s="2" t="s">
+      <c r="D220" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E220" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F220" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A221">
-        <v>1</v>
-      </c>
-      <c r="B221">
+      <c r="G220" s="12"/>
+      <c r="H220" s="12"/>
+      <c r="I220" s="16">
+        <v>2.7700831020000001</v>
+      </c>
+      <c r="J220" s="16"/>
+      <c r="K220" s="16"/>
+      <c r="L220" s="16"/>
+      <c r="M220" s="12"/>
+    </row>
+    <row r="221" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A221" s="15">
+        <v>10</v>
+      </c>
+      <c r="B221" s="16">
         <v>0</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="12">
         <v>130.07334963325101</v>
       </c>
-      <c r="D221" t="s">
-        <v>14</v>
-      </c>
-      <c r="E221">
-        <v>2020</v>
-      </c>
-      <c r="F221" s="2" t="s">
+      <c r="D221" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E221" s="12">
+        <v>2020</v>
+      </c>
+      <c r="F221" s="21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A222">
-        <v>1</v>
-      </c>
-      <c r="B222">
+      <c r="G221" s="12"/>
+      <c r="H221" s="12"/>
+      <c r="I221" s="16">
+        <v>0</v>
+      </c>
+      <c r="J221" s="16"/>
+      <c r="K221" s="16"/>
+      <c r="L221" s="16"/>
+      <c r="M221" s="12"/>
+    </row>
+    <row r="222" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A222" s="22">
+        <v>11</v>
+      </c>
+      <c r="B222" s="16">
+        <v>117.845978</v>
+      </c>
+      <c r="C222" s="12">
+        <v>2.1403508771929798</v>
+      </c>
+      <c r="D222" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E222" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F222" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G222" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H222" s="12"/>
+      <c r="I222" s="16">
+        <v>88.56088561</v>
+      </c>
+      <c r="J222" s="16"/>
+      <c r="K222" s="16"/>
+      <c r="L222" s="16"/>
+      <c r="M222" s="12"/>
+    </row>
+    <row r="223" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A223" s="22">
+        <v>11</v>
+      </c>
+      <c r="B223" s="16">
+        <v>125.14760099999999</v>
+      </c>
+      <c r="C223" s="12">
+        <v>14.126315789473599</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E223" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F223" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G223" s="12"/>
+      <c r="H223" s="12"/>
+      <c r="I223" s="16">
+        <v>94.095940959999993</v>
+      </c>
+      <c r="J223" s="16"/>
+      <c r="K223" s="16"/>
+      <c r="L223" s="16"/>
+      <c r="M223" s="12"/>
+    </row>
+    <row r="224" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A224" s="22">
+        <v>11</v>
+      </c>
+      <c r="B224" s="16">
+        <v>382.80442799999997</v>
+      </c>
+      <c r="C224" s="12">
+        <v>29.536842105263101</v>
+      </c>
+      <c r="D224" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E224" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F224" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G224" s="12"/>
+      <c r="H224" s="12"/>
+      <c r="I224" s="16">
+        <v>287.82287819999999</v>
+      </c>
+      <c r="J224" s="16"/>
+      <c r="K224" s="16"/>
+      <c r="L224" s="16"/>
+      <c r="M224" s="12"/>
+    </row>
+    <row r="225" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A225" s="22">
+        <v>11</v>
+      </c>
+      <c r="B225" s="16">
+        <v>566.84501799999998</v>
+      </c>
+      <c r="C225" s="12">
+        <v>36.385964912280599</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E225" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F225" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G225" s="12"/>
+      <c r="H225" s="12"/>
+      <c r="I225" s="16">
+        <v>426.19926199999998</v>
+      </c>
+      <c r="J225" s="16"/>
+      <c r="K225" s="16"/>
+      <c r="L225" s="16"/>
+      <c r="M225" s="12"/>
+    </row>
+    <row r="226" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A226" s="22">
+        <v>11</v>
+      </c>
+      <c r="B226" s="16">
+        <v>1030.6273060000001</v>
+      </c>
+      <c r="C226" s="12">
+        <v>48.371929824561299</v>
+      </c>
+      <c r="D226" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E226" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F226" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G226" s="12"/>
+      <c r="H226" s="12"/>
+      <c r="I226" s="16">
+        <v>774.90774910000005</v>
+      </c>
+      <c r="J226" s="16"/>
+      <c r="K226" s="16"/>
+      <c r="L226" s="16"/>
+      <c r="M226" s="12"/>
+    </row>
+    <row r="227" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A227" s="22">
+        <v>11</v>
+      </c>
+      <c r="B227" s="16">
+        <v>1155.7749080000001</v>
+      </c>
+      <c r="C227" s="12">
+        <v>62.498245614035</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E227" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F227" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G227" s="12"/>
+      <c r="H227" s="12"/>
+      <c r="I227" s="16">
+        <v>869.00369000000001</v>
+      </c>
+      <c r="J227" s="16"/>
+      <c r="K227" s="16"/>
+      <c r="L227" s="16"/>
+      <c r="M227" s="12"/>
+    </row>
+    <row r="228" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A228" s="22">
+        <v>11</v>
+      </c>
+      <c r="B228" s="16">
+        <v>1222.02952</v>
+      </c>
+      <c r="C228" s="12">
+        <v>77.052631578947299</v>
+      </c>
+      <c r="D228" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E228" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F228" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G228" s="12"/>
+      <c r="H228" s="12"/>
+      <c r="I228" s="16">
+        <v>918.81918819999999</v>
+      </c>
+      <c r="J228" s="16"/>
+      <c r="K228" s="16"/>
+      <c r="L228" s="16"/>
+      <c r="M228" s="12"/>
+    </row>
+    <row r="229" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A229" s="22">
+        <v>11</v>
+      </c>
+      <c r="B229" s="16">
+        <v>1185.2214019999999</v>
+      </c>
+      <c r="C229" s="12">
+        <v>89.466666666666598</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E229" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F229" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G229" s="12"/>
+      <c r="H229" s="12"/>
+      <c r="I229" s="16">
+        <v>891.14391139999998</v>
+      </c>
+      <c r="J229" s="16"/>
+      <c r="K229" s="16"/>
+      <c r="L229" s="16"/>
+      <c r="M229" s="12"/>
+    </row>
+    <row r="230" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A230" s="22">
+        <v>11</v>
+      </c>
+      <c r="B230" s="16">
+        <v>449.05904099999998</v>
+      </c>
+      <c r="C230" s="12">
+        <v>104.44912280701701</v>
+      </c>
+      <c r="D230" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E230" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F230" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G230" s="12"/>
+      <c r="H230" s="12"/>
+      <c r="I230" s="16">
+        <v>337.63837640000003</v>
+      </c>
+      <c r="J230" s="16"/>
+      <c r="K230" s="16"/>
+      <c r="L230" s="16"/>
+      <c r="M230" s="12"/>
+    </row>
+    <row r="231" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A231" s="22">
+        <v>11</v>
+      </c>
+      <c r="B231" s="16">
+        <v>375.44280400000002</v>
+      </c>
+      <c r="C231" s="12">
+        <v>121.14385964912201</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E231" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F231" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H231" s="12"/>
+      <c r="I231" s="16">
+        <v>282.28782289999998</v>
+      </c>
+      <c r="J231" s="16"/>
+      <c r="K231" s="16"/>
+      <c r="L231" s="16"/>
+      <c r="M231" s="12"/>
+    </row>
+    <row r="232" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A232" s="22">
+        <v>12</v>
+      </c>
+      <c r="B232" s="16">
+        <v>125.14760099999999</v>
+      </c>
+      <c r="C232" s="12">
+        <v>2.1403508771929798</v>
+      </c>
+      <c r="D232" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E232" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F232" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G232" s="12"/>
+      <c r="H232" s="12"/>
+      <c r="I232" s="16">
+        <v>94.095940959999993</v>
+      </c>
+      <c r="J232" s="16"/>
+      <c r="K232" s="16"/>
+      <c r="L232" s="16"/>
+      <c r="M232" s="12"/>
+    </row>
+    <row r="233" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A233" s="22">
+        <v>12</v>
+      </c>
+      <c r="B233" s="16">
+        <v>132.50922499999999</v>
+      </c>
+      <c r="C233" s="12">
+        <v>14.126315789473599</v>
+      </c>
+      <c r="D233" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E233" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F233" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G233" s="12"/>
+      <c r="H233" s="12"/>
+      <c r="I233" s="16">
+        <v>99.63099631</v>
+      </c>
+      <c r="J233" s="16"/>
+      <c r="K233" s="16"/>
+      <c r="L233" s="16"/>
+      <c r="M233" s="12"/>
+    </row>
+    <row r="234" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A234" s="22">
+        <v>12</v>
+      </c>
+      <c r="B234" s="16">
+        <v>647.82287799999995</v>
+      </c>
+      <c r="C234" s="12">
+        <v>29.108771929824499</v>
+      </c>
+      <c r="D234" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E234" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F234" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G234" s="12"/>
+      <c r="H234" s="12"/>
+      <c r="I234" s="16">
+        <v>487.08487079999998</v>
+      </c>
+      <c r="J234" s="16"/>
+      <c r="K234" s="16"/>
+      <c r="L234" s="16"/>
+      <c r="M234" s="12"/>
+    </row>
+    <row r="235" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A235" s="22">
+        <v>12</v>
+      </c>
+      <c r="B235" s="16">
+        <v>758.24723200000005</v>
+      </c>
+      <c r="C235" s="12">
+        <v>35.957894736842</v>
+      </c>
+      <c r="D235" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E235" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F235" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G235" s="12"/>
+      <c r="H235" s="12"/>
+      <c r="I235" s="16">
+        <v>570.11070110000003</v>
+      </c>
+      <c r="J235" s="16"/>
+      <c r="K235" s="16"/>
+      <c r="L235" s="16"/>
+      <c r="M235" s="12"/>
+    </row>
+    <row r="236" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A236" s="22">
+        <v>12</v>
+      </c>
+      <c r="B236" s="16">
+        <v>1126.328413</v>
+      </c>
+      <c r="C236" s="12">
+        <v>48.371929824561299</v>
+      </c>
+      <c r="D236" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E236" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F236" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G236" s="12"/>
+      <c r="H236" s="12"/>
+      <c r="I236" s="16">
+        <v>846.86346860000003</v>
+      </c>
+      <c r="J236" s="16"/>
+      <c r="K236" s="16"/>
+      <c r="L236" s="16"/>
+      <c r="M236" s="12"/>
+    </row>
+    <row r="237" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A237" s="22">
+        <v>12</v>
+      </c>
+      <c r="B237" s="16">
+        <v>1155.7749080000001</v>
+      </c>
+      <c r="C237" s="12">
+        <v>62.070175438596401</v>
+      </c>
+      <c r="D237" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E237" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F237" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G237" s="12"/>
+      <c r="H237" s="12"/>
+      <c r="I237" s="16">
+        <v>869.00369000000001</v>
+      </c>
+      <c r="J237" s="16"/>
+      <c r="K237" s="16"/>
+      <c r="L237" s="16"/>
+      <c r="M237" s="12"/>
+    </row>
+    <row r="238" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A238" s="22">
+        <v>12</v>
+      </c>
+      <c r="B238" s="16">
+        <v>1560.6642059999999</v>
+      </c>
+      <c r="C238" s="12">
+        <v>77.480701754385905</v>
+      </c>
+      <c r="D238" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E238" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F238" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G238" s="12"/>
+      <c r="H238" s="12"/>
+      <c r="I238" s="16">
+        <v>1173.431734</v>
+      </c>
+      <c r="J238" s="16"/>
+      <c r="K238" s="16"/>
+      <c r="L238" s="16"/>
+      <c r="M238" s="12"/>
+    </row>
+    <row r="239" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A239" s="22">
+        <v>12</v>
+      </c>
+      <c r="B239" s="16">
+        <v>1133.6900370000001</v>
+      </c>
+      <c r="C239" s="12">
+        <v>89.466666666666598</v>
+      </c>
+      <c r="D239" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E239" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F239" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G239" s="12"/>
+      <c r="H239" s="12"/>
+      <c r="I239" s="16">
+        <v>852.39852399999995</v>
+      </c>
+      <c r="J239" s="16"/>
+      <c r="K239" s="16"/>
+      <c r="L239" s="16"/>
+      <c r="M239" s="12"/>
+    </row>
+    <row r="240" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A240" s="22">
+        <v>12</v>
+      </c>
+      <c r="B240" s="16">
+        <v>515.31365300000004</v>
+      </c>
+      <c r="C240" s="12">
+        <v>104.87719298245599</v>
+      </c>
+      <c r="D240" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E240" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F240" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G240" s="12"/>
+      <c r="H240" s="12"/>
+      <c r="I240" s="16">
+        <v>387.45387449999998</v>
+      </c>
+      <c r="J240" s="16"/>
+      <c r="K240" s="16"/>
+      <c r="L240" s="16"/>
+      <c r="M240" s="12"/>
+    </row>
+    <row r="241" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A241" s="22">
+        <v>12</v>
+      </c>
+      <c r="B241" s="16">
+        <v>456.42066399999999</v>
+      </c>
+      <c r="C241" s="12">
+        <v>120.715789473684</v>
+      </c>
+      <c r="D241" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E241" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F241" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G241" s="12"/>
+      <c r="H241" s="12"/>
+      <c r="I241" s="16">
+        <v>343.17343169999998</v>
+      </c>
+      <c r="J241" s="16"/>
+      <c r="K241" s="16"/>
+      <c r="L241" s="16"/>
+      <c r="M241" s="12"/>
+    </row>
+    <row r="242" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A242" s="22">
+        <v>13</v>
+      </c>
+      <c r="B242" s="10">
+        <v>117.845977859778</v>
+      </c>
+      <c r="C242" s="10">
+        <v>1.71228070175436</v>
+      </c>
+      <c r="D242" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E242" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F242" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G242" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H242" s="12"/>
+      <c r="I242" s="10">
         <v>88.560885608856097</v>
       </c>
-      <c r="C222">
-        <v>2.1403508771929798</v>
-      </c>
-      <c r="D222" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E222">
+      <c r="J242" s="12"/>
+      <c r="K242" s="12"/>
+      <c r="L242" s="12"/>
+      <c r="M242" s="12"/>
+    </row>
+    <row r="243" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A243" s="22">
+        <v>13</v>
+      </c>
+      <c r="B243" s="10">
+        <v>125.147601476015</v>
+      </c>
+      <c r="C243" s="10">
+        <v>14.126315789473599</v>
+      </c>
+      <c r="D243" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E243" s="12">
         <v>2011</v>
       </c>
-      <c r="F222" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G222">
-        <v>4970.4797049999997</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A223">
-        <v>1</v>
-      </c>
-      <c r="B223">
+      <c r="F243" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G243" s="12"/>
+      <c r="H243" s="12"/>
+      <c r="I243" s="10">
         <v>94.095940959409702</v>
       </c>
-      <c r="C223">
-        <v>14.126315789473599</v>
-      </c>
-      <c r="D223" t="s">
-        <v>30</v>
-      </c>
-      <c r="E223">
+      <c r="J243" s="12"/>
+      <c r="K243" s="12"/>
+      <c r="L243" s="12"/>
+      <c r="M243" s="12"/>
+    </row>
+    <row r="244" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A244" s="22">
+        <v>13</v>
+      </c>
+      <c r="B244" s="10">
+        <v>125.147601476015</v>
+      </c>
+      <c r="C244" s="10">
+        <v>29.536842105263101</v>
+      </c>
+      <c r="D244" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E244" s="12">
         <v>2011</v>
       </c>
-      <c r="F223" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A224">
-        <v>1</v>
-      </c>
-      <c r="B224">
-        <v>287.82287822878197</v>
-      </c>
-      <c r="C224">
-        <v>29.536842105263101</v>
-      </c>
-      <c r="D224" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E224">
+      <c r="F244" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G244" s="12"/>
+      <c r="H244" s="12"/>
+      <c r="I244" s="10">
+        <v>94.095940959409702</v>
+      </c>
+      <c r="J244" s="12"/>
+      <c r="K244" s="12"/>
+      <c r="L244" s="12"/>
+      <c r="M244" s="12"/>
+    </row>
+    <row r="245" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A245" s="22">
+        <v>13</v>
+      </c>
+      <c r="B245" s="10">
+        <v>493.22878228782201</v>
+      </c>
+      <c r="C245" s="10">
+        <v>36.385964912280599</v>
+      </c>
+      <c r="D245" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="E245" s="12">
         <v>2011</v>
       </c>
-      <c r="F224" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A225">
-        <v>1</v>
-      </c>
-      <c r="B225">
-        <v>426.19926199261999</v>
-      </c>
-      <c r="C225">
-        <v>36.385964912280599</v>
-      </c>
-      <c r="D225" t="s">
-        <v>29</v>
-      </c>
-      <c r="E225">
+      <c r="F245" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G245" s="12"/>
+      <c r="H245" s="12"/>
+      <c r="I245" s="10">
+        <v>370.84870848708402</v>
+      </c>
+      <c r="J245" s="12"/>
+      <c r="K245" s="12"/>
+      <c r="L245" s="12"/>
+      <c r="M245" s="12"/>
+    </row>
+    <row r="246" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A246" s="22">
+        <v>13</v>
+      </c>
+      <c r="B246" s="10">
+        <v>588.92988929889304</v>
+      </c>
+      <c r="C246" s="10">
+        <v>48.371929824561299</v>
+      </c>
+      <c r="D246" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E246" s="12">
         <v>2011</v>
       </c>
-      <c r="F225" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A226">
-        <v>1</v>
-      </c>
-      <c r="B226">
-        <v>774.90774907749096</v>
-      </c>
-      <c r="C226">
-        <v>48.371929824561299</v>
-      </c>
-      <c r="D226" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E226">
+      <c r="F246" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G246" s="12"/>
+      <c r="H246" s="12"/>
+      <c r="I246" s="10">
+        <v>442.80442804427997</v>
+      </c>
+      <c r="J246" s="12"/>
+      <c r="K246" s="12"/>
+      <c r="L246" s="12"/>
+      <c r="M246" s="12"/>
+    </row>
+    <row r="247" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A247" s="22">
+        <v>13</v>
+      </c>
+      <c r="B247" s="10">
+        <v>927.56457564575601</v>
+      </c>
+      <c r="C247" s="10">
+        <v>62.926315789473598</v>
+      </c>
+      <c r="D247" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E247" s="12">
         <v>2011</v>
       </c>
-      <c r="F226" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A227">
-        <v>1</v>
-      </c>
-      <c r="B227">
+      <c r="F247" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G247" s="12"/>
+      <c r="H247" s="12"/>
+      <c r="I247" s="10">
+        <v>697.41697416974102</v>
+      </c>
+      <c r="J247" s="12"/>
+      <c r="K247" s="12"/>
+      <c r="L247" s="12"/>
+      <c r="M247" s="12"/>
+    </row>
+    <row r="248" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A248" s="22">
+        <v>13</v>
+      </c>
+      <c r="B248" s="10">
+        <v>1317.73062730627</v>
+      </c>
+      <c r="C248" s="10">
+        <v>77.480701754385905</v>
+      </c>
+      <c r="D248" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E248" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F248" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G248" s="12"/>
+      <c r="H248" s="12"/>
+      <c r="I248" s="10">
+        <v>990.77490774907699</v>
+      </c>
+      <c r="J248" s="12"/>
+      <c r="K248" s="12"/>
+      <c r="L248" s="12"/>
+      <c r="M248" s="12"/>
+    </row>
+    <row r="249" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A249" s="22">
+        <v>13</v>
+      </c>
+      <c r="B249" s="10">
+        <v>1155.7749077490701</v>
+      </c>
+      <c r="C249" s="10">
+        <v>89.894736842105203</v>
+      </c>
+      <c r="D249" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E249" s="12">
+        <v>2011</v>
+      </c>
+      <c r="F249" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G249" s="12"/>
+      <c r="H249" s="12"/>
+      <c r="I249" s="10">
         <v>869.00369003690003</v>
       </c>
-      <c r="C227">
-        <v>62.498245614035</v>
-      </c>
-      <c r="D227" t="s">
-        <v>29</v>
-      </c>
-      <c r="E227">
+      <c r="J249" s="12"/>
+      <c r="K249" s="12"/>
+      <c r="L249" s="12"/>
+      <c r="M249" s="12"/>
+    </row>
+    <row r="250" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A250" s="22">
+        <v>13</v>
+      </c>
+      <c r="B250" s="10">
+        <v>714.07749077490803</v>
+      </c>
+      <c r="C250" s="10">
+        <v>104.87719298245599</v>
+      </c>
+      <c r="D250" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E250" s="12">
         <v>2011</v>
       </c>
-      <c r="F227" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A228">
-        <v>1</v>
-      </c>
-      <c r="B228">
-        <v>918.81918819188195</v>
-      </c>
-      <c r="C228">
-        <v>77.052631578947299</v>
-      </c>
-      <c r="D228" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E228">
+      <c r="F250" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G250" s="12"/>
+      <c r="H250" s="12"/>
+      <c r="I250" s="10">
+        <v>536.90036900369</v>
+      </c>
+      <c r="J250" s="12"/>
+      <c r="K250" s="12"/>
+      <c r="L250" s="12"/>
+      <c r="M250" s="12"/>
+    </row>
+    <row r="251" spans="1:13" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A251" s="22">
+        <v>13</v>
+      </c>
+      <c r="B251" s="10">
+        <v>559.48339483394795</v>
+      </c>
+      <c r="C251" s="10">
+        <v>121.14385964912201</v>
+      </c>
+      <c r="D251" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E251" s="12">
         <v>2011</v>
       </c>
-      <c r="F228" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A229">
-        <v>1</v>
-      </c>
-      <c r="B229">
-        <v>891.14391143911405</v>
-      </c>
-      <c r="C229">
-        <v>89.466666666666598</v>
-      </c>
-      <c r="D229" t="s">
-        <v>29</v>
-      </c>
-      <c r="E229">
-        <v>2011</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A230">
-        <v>1</v>
-      </c>
-      <c r="B230">
-        <v>337.63837638376299</v>
-      </c>
-      <c r="C230">
-        <v>104.44912280701701</v>
-      </c>
-      <c r="D230" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E230">
-        <v>2011</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A231">
-        <v>1</v>
-      </c>
-      <c r="B231">
-        <v>282.28782287822798</v>
-      </c>
-      <c r="C231">
-        <v>121.14385964912201</v>
-      </c>
-      <c r="D231" t="s">
-        <v>29</v>
-      </c>
-      <c r="E231">
-        <v>2011</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A232">
-        <v>1</v>
-      </c>
-      <c r="B232">
-        <v>94.095940959409702</v>
-      </c>
-      <c r="C232">
-        <v>2.1403508771929798</v>
-      </c>
-      <c r="D232" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E232">
-        <v>2011</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G232">
-        <v>5723.2472319999997</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A233">
-        <v>1</v>
-      </c>
-      <c r="B233">
-        <v>99.630996309963393</v>
-      </c>
-      <c r="C233">
-        <v>14.126315789473599</v>
-      </c>
-      <c r="D233" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E233">
-        <v>2011</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A234">
-        <v>1</v>
-      </c>
-      <c r="B234">
-        <v>487.08487084870802</v>
-      </c>
-      <c r="C234">
-        <v>29.108771929824499</v>
-      </c>
-      <c r="D234" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E234">
-        <v>2011</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A235">
-        <v>1</v>
-      </c>
-      <c r="B235">
-        <v>570.11070110701098</v>
-      </c>
-      <c r="C235">
-        <v>35.957894736842</v>
-      </c>
-      <c r="D235" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E235">
-        <v>2011</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A236">
-        <v>1</v>
-      </c>
-      <c r="B236">
-        <v>846.863468634686</v>
-      </c>
-      <c r="C236">
-        <v>48.371929824561299</v>
-      </c>
-      <c r="D236" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E236">
-        <v>2011</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A237">
-        <v>1</v>
-      </c>
-      <c r="B237">
-        <v>869.00369003690003</v>
-      </c>
-      <c r="C237">
-        <v>62.070175438596401</v>
-      </c>
-      <c r="D237" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E237">
-        <v>2011</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A238">
-        <v>1</v>
-      </c>
-      <c r="B238">
-        <v>1173.43173431734</v>
-      </c>
-      <c r="C238">
-        <v>77.480701754385905</v>
-      </c>
-      <c r="D238" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E238">
-        <v>2011</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A239">
-        <v>1</v>
-      </c>
-      <c r="B239">
-        <v>852.39852398523999</v>
-      </c>
-      <c r="C239">
-        <v>89.466666666666598</v>
-      </c>
-      <c r="D239" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E239">
-        <v>2011</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A240">
-        <v>1</v>
-      </c>
-      <c r="B240">
-        <v>387.45387453874503</v>
-      </c>
-      <c r="C240">
-        <v>104.87719298245599</v>
-      </c>
-      <c r="D240" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E240">
-        <v>2011</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A241">
-        <v>1</v>
-      </c>
-      <c r="B241">
-        <v>343.17343173431698</v>
-      </c>
-      <c r="C241">
-        <v>120.715789473684</v>
-      </c>
-      <c r="D241" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E241">
-        <v>2011</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F251" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G251" s="12"/>
+      <c r="H251" s="12"/>
+      <c r="I251" s="10">
+        <v>420.66420664206601</v>
+      </c>
+      <c r="J251" s="12"/>
+      <c r="K251" s="12"/>
+      <c r="L251" s="12"/>
+      <c r="M251" s="12"/>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A252" s="12"/>
+      <c r="B252" s="12"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="12"/>
+      <c r="E252" s="12"/>
+      <c r="F252" s="12"/>
+      <c r="G252" s="12"/>
+      <c r="H252" s="12"/>
+      <c r="I252" s="12"/>
+      <c r="J252" s="12"/>
+      <c r="K252" s="12"/>
+      <c r="L252" s="12"/>
+      <c r="M252" s="12"/>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A253" s="12"/>
+      <c r="B253" s="12"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="12"/>
+      <c r="E253" s="12"/>
+      <c r="F253" s="12"/>
+      <c r="G253" s="12"/>
+      <c r="H253" s="12"/>
+      <c r="I253" s="12"/>
+      <c r="J253" s="12"/>
+      <c r="K253" s="12"/>
+      <c r="L253" s="12"/>
+      <c r="M253" s="12"/>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A254" s="12"/>
+      <c r="B254" s="12"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="12"/>
+      <c r="E254" s="12"/>
+      <c r="F254" s="12"/>
+      <c r="G254" s="12"/>
+      <c r="H254" s="12"/>
+      <c r="I254" s="12"/>
+      <c r="J254" s="12"/>
+      <c r="K254" s="12"/>
+      <c r="L254" s="12"/>
+      <c r="M254" s="12"/>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A255" s="12"/>
+      <c r="B255" s="12"/>
+      <c r="C255" s="12"/>
+      <c r="D255" s="12"/>
+      <c r="E255" s="12"/>
+      <c r="F255" s="12"/>
+      <c r="G255" s="12"/>
+      <c r="H255" s="12"/>
+      <c r="I255" s="12"/>
+      <c r="J255" s="12"/>
+      <c r="K255" s="12"/>
+      <c r="L255" s="12"/>
+      <c r="M255" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5373,26 +7480,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="109.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.25" customWidth="1"/>
+    <col min="2" max="2" width="109.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2">
-        <v>1</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -5401,9 +7508,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3">
-        <v>2</v>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>50</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -5412,9 +7519,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>3</v>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>51</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -5423,9 +7530,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>4</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>66</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5434,32 +7541,32 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>

--- a/Data/Initial_Database.xlsx
+++ b/Data/Initial_Database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jerry\Documents\GitHub\Methane_Prediction\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\Methane_Prediction\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EA9331-F771-4BC2-8FEB-B37C34AAF0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E3A4AD-3315-411D-B87A-CE0CF7D13412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -244,17 +244,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -314,7 +314,7 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -502,7 +502,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="58" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -569,7 +569,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -848,24 +848,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T251"/>
-  <sheetFormatPr defaultRowHeight="20.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="14" customWidth="1"/>
-    <col min="4" max="6" width="11.7265625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="15.7265625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="19.7265625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="18.6328125" style="14" customWidth="1"/>
-    <col min="10" max="10" width="11.7265625" style="14" customWidth="1"/>
-    <col min="11" max="11" width="12.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="21.9296875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="16.73046875" style="14" customWidth="1"/>
+    <col min="4" max="6" width="11.73046875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="15.73046875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="19.73046875" style="14" customWidth="1"/>
+    <col min="9" max="9" width="18.59765625" style="14" customWidth="1"/>
+    <col min="10" max="10" width="11.73046875" style="14" customWidth="1"/>
+    <col min="11" max="11" width="12.9296875" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="16" width="9" style="1"/>
-    <col min="17" max="17" width="9.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.59765625" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="9" customFormat="1" ht="80" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20" s="9" customFormat="1" ht="79.900000000000006">
       <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
@@ -907,7 +907,7 @@
       <c r="S1" s="8"/>
       <c r="T1" s="8"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -930,7 +930,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20">
       <c r="A3" s="13">
         <v>1</v>
       </c>
@@ -953,7 +953,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:20">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -976,7 +976,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:20">
       <c r="A5" s="13">
         <v>1</v>
       </c>
@@ -999,7 +999,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:20">
       <c r="A6" s="13">
         <v>1</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:20">
       <c r="A7" s="13">
         <v>1</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:20">
       <c r="A8" s="13">
         <v>1</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:20">
       <c r="A9" s="13">
         <v>1</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:20">
       <c r="A10" s="13">
         <v>1</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:20">
       <c r="A11" s="13">
         <v>1</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:20">
       <c r="A12" s="13">
         <v>1</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:20">
       <c r="A13" s="13">
         <v>1</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:20">
       <c r="A14" s="13">
         <v>1</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:20">
       <c r="A15" s="13">
         <v>1</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20">
       <c r="A16" s="13">
         <v>1</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7">
       <c r="A17" s="13">
         <v>1</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7">
       <c r="A18" s="13">
         <v>1</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7">
       <c r="A19" s="13">
         <v>1</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7">
       <c r="A20" s="13">
         <v>1</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7">
       <c r="A21" s="13">
         <v>1</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7">
       <c r="A22" s="16">
         <v>1</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7">
       <c r="A23" s="18">
         <v>2</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7">
       <c r="A24" s="13">
         <v>2</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7">
       <c r="A25" s="13">
         <v>2</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7">
       <c r="A26" s="13">
         <v>2</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7">
       <c r="A27" s="13">
         <v>2</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7">
       <c r="A28" s="13">
         <v>2</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7">
       <c r="A29" s="13">
         <v>2</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7">
       <c r="A30" s="13">
         <v>2</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7">
       <c r="A31" s="13">
         <v>2</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7">
       <c r="A32" s="13">
         <v>2</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7">
       <c r="A33" s="13">
         <v>2</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7">
       <c r="A34" s="13">
         <v>2</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7">
       <c r="A35" s="13">
         <v>2</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7">
       <c r="A36" s="13">
         <v>2</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7">
       <c r="A37" s="13">
         <v>2</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7">
       <c r="A38" s="13">
         <v>2</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7">
       <c r="A39" s="13">
         <v>2</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7">
       <c r="A40" s="13">
         <v>2</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7">
       <c r="A41" s="13">
         <v>2</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7">
       <c r="A42" s="13">
         <v>2</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7">
       <c r="A43" s="13">
         <v>2</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7">
       <c r="A44" s="16">
         <v>2</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7">
       <c r="A45" s="18">
         <v>3</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7">
       <c r="A46" s="13">
         <v>3</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7">
       <c r="A47" s="13">
         <v>3</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7">
       <c r="A48" s="13">
         <v>3</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:19">
       <c r="A49" s="13">
         <v>3</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:19">
       <c r="A50" s="13">
         <v>3</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:19">
       <c r="A51" s="13">
         <v>3</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:19">
       <c r="A52" s="13">
         <v>3</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:19">
       <c r="A53" s="13">
         <v>3</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:19">
       <c r="A54" s="13">
         <v>3</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:19">
       <c r="A55" s="13">
         <v>3</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:19">
       <c r="A56" s="13">
         <v>3</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:19">
       <c r="A57" s="13">
         <v>3</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:19">
       <c r="A58" s="13">
         <v>3</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:19">
       <c r="A59" s="13">
         <v>3</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:19">
       <c r="A60" s="13">
         <v>3</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:19" ht="20.65" thickBot="1">
       <c r="A61" s="21">
         <v>3</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="22" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:19" ht="21.4" thickBot="1">
       <c r="A62" s="23">
         <v>4</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
     </row>
-    <row r="63" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:19" ht="20.65" thickBot="1">
       <c r="A63" s="27">
         <v>4</v>
       </c>
@@ -2346,12 +2346,15 @@
       </c>
       <c r="H63" s="26">
         <v>1351.6258170000001</v>
+      </c>
+      <c r="I63" s="14">
+        <v>212</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
     </row>
-    <row r="64" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:19" ht="20.65" thickBot="1">
       <c r="A64" s="27">
         <v>4</v>
       </c>
@@ -2375,12 +2378,15 @@
       </c>
       <c r="H64" s="26">
         <v>2649.1869919999999</v>
+      </c>
+      <c r="I64" s="14">
+        <v>212</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
     </row>
-    <row r="65" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:19" ht="20.65" thickBot="1">
       <c r="A65" s="27">
         <v>4</v>
       </c>
@@ -2404,12 +2410,15 @@
       </c>
       <c r="H65" s="26">
         <v>3514.2276430000002</v>
+      </c>
+      <c r="I65" s="14">
+        <v>212</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
     </row>
-    <row r="66" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:19" ht="20.65" thickBot="1">
       <c r="A66" s="27">
         <v>4</v>
       </c>
@@ -2433,12 +2442,15 @@
       </c>
       <c r="H66" s="26">
         <v>6325.6097559999998</v>
+      </c>
+      <c r="I66" s="14">
+        <v>212</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
     </row>
-    <row r="67" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:19" ht="20.65" thickBot="1">
       <c r="A67" s="27">
         <v>4</v>
       </c>
@@ -2462,12 +2474,15 @@
       </c>
       <c r="H67" s="26">
         <v>4000.8130080000001</v>
+      </c>
+      <c r="I67" s="14">
+        <v>212</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:19" ht="20.65" thickBot="1">
       <c r="A68" s="27">
         <v>4</v>
       </c>
@@ -2491,12 +2506,15 @@
       </c>
       <c r="H68" s="26">
         <v>4919.9186989999998</v>
+      </c>
+      <c r="I68" s="14">
+        <v>212</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
     </row>
-    <row r="69" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:19" ht="20.65" thickBot="1">
       <c r="A69" s="27">
         <v>4</v>
       </c>
@@ -2520,12 +2538,15 @@
       </c>
       <c r="H69" s="26">
         <v>4217.0731699999997</v>
+      </c>
+      <c r="I69" s="14">
+        <v>212</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
     </row>
-    <row r="70" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:19" ht="20.65" thickBot="1">
       <c r="A70" s="27">
         <v>4</v>
       </c>
@@ -2549,12 +2570,15 @@
       </c>
       <c r="H70" s="26">
         <v>4487.3983740000003</v>
+      </c>
+      <c r="I70" s="14">
+        <v>212</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
     </row>
-    <row r="71" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:19" ht="20.65" thickBot="1">
       <c r="A71" s="27">
         <v>4</v>
       </c>
@@ -2578,12 +2602,15 @@
       </c>
       <c r="H71" s="26">
         <v>5839.0243899999996</v>
+      </c>
+      <c r="I71" s="14">
+        <v>212</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
     </row>
-    <row r="72" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:19" ht="20.65" thickBot="1">
       <c r="A72" s="27">
         <v>4</v>
       </c>
@@ -2607,12 +2634,15 @@
       </c>
       <c r="H72" s="26">
         <v>3946.7479680000001</v>
+      </c>
+      <c r="I72" s="14">
+        <v>212</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
     </row>
-    <row r="73" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:19" ht="20.65" thickBot="1">
       <c r="A73" s="27">
         <v>4</v>
       </c>
@@ -2636,12 +2666,15 @@
       </c>
       <c r="H73" s="26">
         <v>3297.9674799999998</v>
+      </c>
+      <c r="I73" s="14">
+        <v>212</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
     </row>
-    <row r="74" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:19" ht="20.65" thickBot="1">
       <c r="A74" s="27">
         <v>4</v>
       </c>
@@ -2665,12 +2698,15 @@
       </c>
       <c r="H74" s="26">
         <v>3406.097561</v>
+      </c>
+      <c r="I74" s="14">
+        <v>212</v>
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
     </row>
-    <row r="75" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:19" ht="20.65" thickBot="1">
       <c r="A75" s="27">
         <v>4</v>
       </c>
@@ -2694,12 +2730,15 @@
       </c>
       <c r="H75" s="26">
         <v>2973.5772360000001</v>
+      </c>
+      <c r="I75" s="14">
+        <v>212</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
     </row>
-    <row r="76" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:19" ht="20.65" thickBot="1">
       <c r="A76" s="27">
         <v>4</v>
       </c>
@@ -2723,12 +2762,15 @@
       </c>
       <c r="H76" s="26">
         <v>3189.837399</v>
+      </c>
+      <c r="I76" s="14">
+        <v>212</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
     </row>
-    <row r="77" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:19" ht="20.65" thickBot="1">
       <c r="A77" s="27">
         <v>4</v>
       </c>
@@ -2752,12 +2794,15 @@
       </c>
       <c r="H77" s="26">
         <v>3243.902439</v>
+      </c>
+      <c r="I77" s="14">
+        <v>212</v>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
     </row>
-    <row r="78" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:19" ht="20.65" thickBot="1">
       <c r="A78" s="27">
         <v>4</v>
       </c>
@@ -2781,12 +2826,15 @@
       </c>
       <c r="H78" s="26">
         <v>1838.211382</v>
+      </c>
+      <c r="I78" s="14">
+        <v>212</v>
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
     </row>
-    <row r="79" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:19" ht="20.65" thickBot="1">
       <c r="A79" s="27">
         <v>4</v>
       </c>
@@ -2810,12 +2858,15 @@
       </c>
       <c r="H79" s="26">
         <v>2054.4715449999999</v>
+      </c>
+      <c r="I79" s="14">
+        <v>212</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
     </row>
-    <row r="80" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:19" ht="20.65" thickBot="1">
       <c r="A80" s="27">
         <v>4</v>
       </c>
@@ -2839,12 +2890,15 @@
       </c>
       <c r="H80" s="26">
         <v>2108.5365860000002</v>
+      </c>
+      <c r="I80" s="14">
+        <v>212</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" s="2"/>
       <c r="S80" s="2"/>
     </row>
-    <row r="81" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:19" ht="20.65" thickBot="1">
       <c r="A81" s="27">
         <v>4</v>
       </c>
@@ -2868,12 +2922,15 @@
       </c>
       <c r="H81" s="26">
         <v>1838.211382</v>
+      </c>
+      <c r="I81" s="14">
+        <v>212</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
     </row>
-    <row r="82" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:19" ht="20.65" thickBot="1">
       <c r="A82" s="27">
         <v>4</v>
       </c>
@@ -2897,12 +2954,15 @@
       </c>
       <c r="H82" s="26">
         <v>865.04065000000003</v>
+      </c>
+      <c r="I82" s="14">
+        <v>212</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
     </row>
-    <row r="83" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:19" ht="20.65" thickBot="1">
       <c r="A83" s="27">
         <v>4</v>
       </c>
@@ -2926,12 +2986,15 @@
       </c>
       <c r="H83" s="26">
         <v>756.91057000000001</v>
+      </c>
+      <c r="I83" s="14">
+        <v>212</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" s="2"/>
       <c r="S83" s="2"/>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:19">
       <c r="A84" s="28">
         <v>4</v>
       </c>
@@ -2955,12 +3018,15 @@
       </c>
       <c r="H84" s="26">
         <v>432.52032500000001</v>
+      </c>
+      <c r="I84" s="14">
+        <v>212</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" s="2"/>
       <c r="S84" s="2"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:19">
       <c r="A85" s="29">
         <v>5</v>
       </c>
@@ -2992,7 +3058,7 @@
       <c r="R85" s="2"/>
       <c r="S85" s="2"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:19">
       <c r="A86" s="27">
         <v>5</v>
       </c>
@@ -3016,12 +3082,15 @@
       </c>
       <c r="H86" s="26">
         <v>68.578767999999997</v>
+      </c>
+      <c r="I86" s="14">
+        <v>153</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" s="2"/>
       <c r="S86" s="2"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:19">
       <c r="A87" s="27">
         <v>5</v>
       </c>
@@ -3045,12 +3114,15 @@
       </c>
       <c r="H87" s="26">
         <v>380.73702700000001</v>
+      </c>
+      <c r="I87" s="14">
+        <v>153</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" s="2"/>
       <c r="S87" s="2"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:19">
       <c r="A88" s="27">
         <v>5</v>
       </c>
@@ -3074,12 +3146,15 @@
       </c>
       <c r="H88" s="26">
         <v>982.22139700000002</v>
+      </c>
+      <c r="I88" s="14">
+        <v>153</v>
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" s="2"/>
       <c r="S88" s="2"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:19">
       <c r="A89" s="27">
         <v>5</v>
       </c>
@@ -3103,12 +3178,15 @@
       </c>
       <c r="H89" s="26">
         <v>1227.4748790000001</v>
+      </c>
+      <c r="I89" s="14">
+        <v>153</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" s="2"/>
       <c r="S89" s="2"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:19">
       <c r="A90" s="27">
         <v>5</v>
       </c>
@@ -3132,12 +3210,15 @@
       </c>
       <c r="H90" s="26">
         <v>3184.727742</v>
+      </c>
+      <c r="I90" s="14">
+        <v>153</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" s="2"/>
       <c r="S90" s="2"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:19">
       <c r="A91" s="27">
         <v>5</v>
       </c>
@@ -3161,12 +3242,15 @@
       </c>
       <c r="H91" s="26">
         <v>2562.469411</v>
+      </c>
+      <c r="I91" s="14">
+        <v>153</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" s="2"/>
       <c r="S91" s="2"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:19">
       <c r="A92" s="27">
         <v>5</v>
       </c>
@@ -3190,12 +3274,15 @@
       </c>
       <c r="H92" s="26">
         <v>3029.595378</v>
+      </c>
+      <c r="I92" s="14">
+        <v>153</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" s="2"/>
       <c r="S92" s="2"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:19">
       <c r="A93" s="27">
         <v>5</v>
       </c>
@@ -3219,12 +3306,15 @@
       </c>
       <c r="H93" s="26">
         <v>3052.454968</v>
+      </c>
+      <c r="I93" s="14">
+        <v>153</v>
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" s="2"/>
       <c r="S93" s="2"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:19">
       <c r="A94" s="27">
         <v>5</v>
       </c>
@@ -3248,12 +3338,15 @@
       </c>
       <c r="H94" s="26">
         <v>2874.9295360000001</v>
+      </c>
+      <c r="I94" s="14">
+        <v>153</v>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" s="2"/>
       <c r="S94" s="2"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:19">
       <c r="A95" s="27">
         <v>5</v>
       </c>
@@ -3277,12 +3370,15 @@
       </c>
       <c r="H95" s="26">
         <v>2808.4363979999998</v>
+      </c>
+      <c r="I95" s="14">
+        <v>153</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
       <c r="S95" s="2"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:19">
       <c r="A96" s="27">
         <v>5</v>
       </c>
@@ -3306,12 +3402,15 @@
       </c>
       <c r="H96" s="26">
         <v>3386.4848870000001</v>
+      </c>
+      <c r="I96" s="14">
+        <v>153</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
       <c r="S96" s="2"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:19">
       <c r="A97" s="27">
         <v>5</v>
       </c>
@@ -3335,12 +3434,15 @@
       </c>
       <c r="H97" s="26">
         <v>3520.3767670000002</v>
+      </c>
+      <c r="I97" s="14">
+        <v>153</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" s="2"/>
       <c r="S97" s="2"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:19">
       <c r="A98" s="27">
         <v>5</v>
       </c>
@@ -3364,12 +3466,15 @@
       </c>
       <c r="H98" s="26">
         <v>4365.3308569999999</v>
+      </c>
+      <c r="I98" s="14">
+        <v>153</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" s="2"/>
       <c r="S98" s="2"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:19">
       <c r="A99" s="27">
         <v>5</v>
       </c>
@@ -3393,12 +3498,15 @@
       </c>
       <c r="H99" s="26">
         <v>5188.5779430000002</v>
+      </c>
+      <c r="I99" s="14">
+        <v>153</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:19">
       <c r="A100" s="27">
         <v>5</v>
       </c>
@@ -3422,12 +3530,15 @@
       </c>
       <c r="H100" s="26">
         <v>3010.3856390000001</v>
+      </c>
+      <c r="I100" s="14">
+        <v>153</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" s="2"/>
       <c r="S100" s="2"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:19">
       <c r="A101" s="27">
         <v>5</v>
       </c>
@@ -3451,12 +3562,15 @@
       </c>
       <c r="H101" s="26">
         <v>2833.6560399999998</v>
+      </c>
+      <c r="I101" s="14">
+        <v>153</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:19">
       <c r="A102" s="27">
         <v>5</v>
       </c>
@@ -3480,12 +3594,15 @@
       </c>
       <c r="H102" s="26">
         <v>1367.8431860000001</v>
+      </c>
+      <c r="I102" s="14">
+        <v>153</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:19">
       <c r="A103" s="27">
         <v>5</v>
       </c>
@@ -3509,12 +3626,15 @@
       </c>
       <c r="H103" s="26">
         <v>2191.419582</v>
+      </c>
+      <c r="I103" s="14">
+        <v>153</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" s="2"/>
       <c r="S103" s="2"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:19">
       <c r="A104" s="27">
         <v>5</v>
       </c>
@@ -3538,12 +3658,15 @@
       </c>
       <c r="H104" s="26">
         <v>1525.829567</v>
+      </c>
+      <c r="I104" s="14">
+        <v>153</v>
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" s="2"/>
       <c r="S104" s="2"/>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:19">
       <c r="A105" s="27">
         <v>5</v>
       </c>
@@ -3567,12 +3690,15 @@
       </c>
       <c r="H105" s="26">
         <v>82.080470000000005</v>
+      </c>
+      <c r="I105" s="14">
+        <v>153</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" s="2"/>
       <c r="S105" s="2"/>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:19">
       <c r="A106" s="27">
         <v>5</v>
       </c>
@@ -3596,12 +3722,15 @@
       </c>
       <c r="H106" s="26">
         <v>950.11369000000002</v>
+      </c>
+      <c r="I106" s="14">
+        <v>153</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" s="2"/>
       <c r="S106" s="2"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:19">
       <c r="A107" s="27">
         <v>5</v>
       </c>
@@ -3625,12 +3754,15 @@
       </c>
       <c r="H107" s="26">
         <v>506.80779899999999</v>
+      </c>
+      <c r="I107" s="14">
+        <v>153</v>
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" s="2"/>
       <c r="S107" s="2"/>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:19">
       <c r="A108" s="27">
         <v>5</v>
       </c>
@@ -3654,12 +3786,15 @@
       </c>
       <c r="H108" s="26">
         <v>485.04590899999999</v>
+      </c>
+      <c r="I108" s="14">
+        <v>153</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" s="2"/>
       <c r="S108" s="2"/>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:19">
       <c r="A109" s="27">
         <v>5</v>
       </c>
@@ -3683,12 +3818,15 @@
       </c>
       <c r="H109" s="26">
         <v>463.14680700000002</v>
+      </c>
+      <c r="I109" s="14">
+        <v>153</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" s="2"/>
       <c r="S109" s="2"/>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:19">
       <c r="A110" s="27">
         <v>5</v>
       </c>
@@ -3712,12 +3850,15 @@
       </c>
       <c r="H110" s="26">
         <v>2019.4924169999999</v>
+      </c>
+      <c r="I110" s="14">
+        <v>153</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
     </row>
-    <row r="111" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:19" ht="20.65" thickBot="1">
       <c r="A111" s="30">
         <v>5</v>
       </c>
@@ -3741,13 +3882,16 @@
       </c>
       <c r="H111" s="26">
         <v>19.539048999999999</v>
+      </c>
+      <c r="I111" s="14">
+        <v>153</v>
       </c>
       <c r="L111" s="4"/>
       <c r="Q111" s="2"/>
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
     </row>
-    <row r="112" spans="1:19" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:19" ht="20.65" thickBot="1">
       <c r="A112" s="31">
         <v>6</v>
       </c>
@@ -3780,7 +3924,7 @@
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
     </row>
-    <row r="113" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:12" ht="20.65" thickBot="1">
       <c r="A113" s="34">
         <v>6</v>
       </c>
@@ -3805,10 +3949,12 @@
       <c r="H113" s="33">
         <v>334.81649609999999</v>
       </c>
-      <c r="I113" s="33"/>
+      <c r="I113" s="14">
+        <v>401</v>
+      </c>
       <c r="L113" s="5"/>
     </row>
-    <row r="114" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:12" ht="20.65" thickBot="1">
       <c r="A114" s="34">
         <v>6</v>
       </c>
@@ -3833,10 +3979,12 @@
       <c r="H114" s="33">
         <v>2696.8962729999998</v>
       </c>
-      <c r="I114" s="33"/>
+      <c r="I114" s="14">
+        <v>401</v>
+      </c>
       <c r="L114" s="5"/>
     </row>
-    <row r="115" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:12" ht="20.65" thickBot="1">
       <c r="A115" s="34">
         <v>6</v>
       </c>
@@ -3861,10 +4009,12 @@
       <c r="H115" s="33">
         <v>1966.0119950000001</v>
       </c>
-      <c r="I115" s="33"/>
+      <c r="I115" s="14">
+        <v>401</v>
+      </c>
       <c r="L115" s="5"/>
     </row>
-    <row r="116" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:12" ht="20.65" thickBot="1">
       <c r="A116" s="34">
         <v>6</v>
       </c>
@@ -3889,10 +4039,12 @@
       <c r="H116" s="33">
         <v>2896.9985809999998</v>
       </c>
-      <c r="I116" s="33"/>
+      <c r="I116" s="14">
+        <v>401</v>
+      </c>
       <c r="L116" s="5"/>
     </row>
-    <row r="117" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:12" ht="20.65" thickBot="1">
       <c r="A117" s="34">
         <v>6</v>
       </c>
@@ -3917,10 +4069,12 @@
       <c r="H117" s="33">
         <v>1733.8620080000001</v>
       </c>
-      <c r="I117" s="33"/>
+      <c r="I117" s="14">
+        <v>401</v>
+      </c>
       <c r="L117" s="5"/>
     </row>
-    <row r="118" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:12" ht="20.65" thickBot="1">
       <c r="A118" s="34">
         <v>6</v>
       </c>
@@ -3945,10 +4099,12 @@
       <c r="H118" s="33">
         <v>2930.7765720000002</v>
       </c>
-      <c r="I118" s="33"/>
+      <c r="I118" s="14">
+        <v>401</v>
+      </c>
       <c r="L118" s="5"/>
     </row>
-    <row r="119" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:12" ht="20.65" thickBot="1">
       <c r="A119" s="34">
         <v>6</v>
       </c>
@@ -3973,10 +4129,12 @@
       <c r="H119" s="33">
         <v>1634.5169000000001</v>
       </c>
-      <c r="I119" s="33"/>
+      <c r="I119" s="14">
+        <v>401</v>
+      </c>
       <c r="L119" s="5"/>
     </row>
-    <row r="120" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:12" ht="20.65" thickBot="1">
       <c r="A120" s="34">
         <v>6</v>
       </c>
@@ -4001,10 +4159,12 @@
       <c r="H120" s="33">
         <v>2699.044245</v>
       </c>
-      <c r="I120" s="33"/>
+      <c r="I120" s="14">
+        <v>401</v>
+      </c>
       <c r="L120" s="5"/>
     </row>
-    <row r="121" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:12" ht="20.65" thickBot="1">
       <c r="A121" s="34">
         <v>6</v>
       </c>
@@ -4029,10 +4189,12 @@
       <c r="H121" s="33">
         <v>2367.4099289999999</v>
       </c>
-      <c r="I121" s="33"/>
+      <c r="I121" s="14">
+        <v>401</v>
+      </c>
       <c r="L121" s="5"/>
     </row>
-    <row r="122" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:12" ht="20.65" thickBot="1">
       <c r="A122" s="34">
         <v>6</v>
       </c>
@@ -4057,10 +4219,12 @@
       <c r="H122" s="33">
         <v>4761.7163840000003</v>
       </c>
-      <c r="I122" s="33"/>
+      <c r="I122" s="14">
+        <v>401</v>
+      </c>
       <c r="L122" s="5"/>
     </row>
-    <row r="123" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:12" ht="20.65" thickBot="1">
       <c r="A123" s="34">
         <v>6</v>
       </c>
@@ -4085,10 +4249,12 @@
       <c r="H123" s="33">
         <v>5361.1084309999997</v>
       </c>
-      <c r="I123" s="33"/>
+      <c r="I123" s="14">
+        <v>401</v>
+      </c>
       <c r="L123" s="5"/>
     </row>
-    <row r="124" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:12" ht="20.65" thickBot="1">
       <c r="A124" s="34">
         <v>6</v>
       </c>
@@ -4113,10 +4279,12 @@
       <c r="H124" s="33">
         <v>4696.9448110000003</v>
       </c>
-      <c r="I124" s="33"/>
+      <c r="I124" s="14">
+        <v>401</v>
+      </c>
       <c r="L124" s="5"/>
     </row>
-    <row r="125" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:12" ht="20.65" thickBot="1">
       <c r="A125" s="34">
         <v>6</v>
       </c>
@@ -4141,10 +4309,12 @@
       <c r="H125" s="33">
         <v>5097.0499840000002</v>
       </c>
-      <c r="I125" s="33"/>
+      <c r="I125" s="14">
+        <v>401</v>
+      </c>
       <c r="L125" s="5"/>
     </row>
-    <row r="126" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:12" ht="20.65" thickBot="1">
       <c r="A126" s="34">
         <v>6</v>
       </c>
@@ -4169,10 +4339,12 @@
       <c r="H126" s="33">
         <v>3302.9510100000002</v>
       </c>
-      <c r="I126" s="33"/>
+      <c r="I126" s="14">
+        <v>401</v>
+      </c>
       <c r="L126" s="5"/>
     </row>
-    <row r="127" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:12" ht="20.65" thickBot="1">
       <c r="A127" s="34">
         <v>6</v>
       </c>
@@ -4197,10 +4369,12 @@
       <c r="H127" s="33">
         <v>4899.0757590000003</v>
       </c>
-      <c r="I127" s="33"/>
+      <c r="I127" s="14">
+        <v>401</v>
+      </c>
       <c r="L127" s="5"/>
     </row>
-    <row r="128" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:12" ht="20.65" thickBot="1">
       <c r="A128" s="34">
         <v>6</v>
       </c>
@@ -4225,10 +4399,12 @@
       <c r="H128" s="33">
         <v>1509.806691</v>
       </c>
-      <c r="I128" s="33"/>
+      <c r="I128" s="14">
+        <v>401</v>
+      </c>
       <c r="L128" s="5"/>
     </row>
-    <row r="129" spans="1:13" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:13" ht="20.65" thickBot="1">
       <c r="A129" s="34">
         <v>6</v>
       </c>
@@ -4253,10 +4429,12 @@
       <c r="H129" s="33">
         <v>14.89658092</v>
       </c>
-      <c r="I129" s="33"/>
+      <c r="I129" s="14">
+        <v>401</v>
+      </c>
       <c r="L129" s="5"/>
     </row>
-    <row r="130" spans="1:13" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:13" ht="20.65" thickBot="1">
       <c r="A130" s="34">
         <v>6</v>
       </c>
@@ -4281,11 +4459,13 @@
       <c r="H130" s="33">
         <v>1378.712233</v>
       </c>
-      <c r="I130" s="33"/>
+      <c r="I130" s="14">
+        <v>401</v>
+      </c>
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:13" ht="20.65" thickBot="1">
       <c r="A131" s="34">
         <v>6</v>
       </c>
@@ -4310,11 +4490,13 @@
       <c r="H131" s="33">
         <v>9889.18318</v>
       </c>
-      <c r="I131" s="33"/>
+      <c r="I131" s="14">
+        <v>401</v>
+      </c>
       <c r="L131" s="2"/>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:13">
       <c r="A132" s="35">
         <v>6</v>
       </c>
@@ -4339,11 +4521,13 @@
       <c r="H132" s="33">
         <v>17.561656809999999</v>
       </c>
-      <c r="I132" s="33"/>
+      <c r="I132" s="14">
+        <v>401</v>
+      </c>
       <c r="L132" s="2"/>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:13">
       <c r="A133" s="37">
         <v>7</v>
       </c>
@@ -4374,7 +4558,7 @@
       <c r="L133" s="2"/>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:13">
       <c r="A134" s="34">
         <v>7</v>
       </c>
@@ -4399,11 +4583,13 @@
       <c r="H134" s="33">
         <v>21.604938270000002</v>
       </c>
-      <c r="I134" s="33"/>
+      <c r="I134" s="14">
+        <v>346</v>
+      </c>
       <c r="L134" s="2"/>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:13">
       <c r="A135" s="34">
         <v>7</v>
       </c>
@@ -4428,11 +4614,13 @@
       <c r="H135" s="33">
         <v>367.28395060000003</v>
       </c>
-      <c r="I135" s="33"/>
+      <c r="I135" s="14">
+        <v>346</v>
+      </c>
       <c r="L135" s="2"/>
       <c r="M135" s="3"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:13">
       <c r="A136" s="34">
         <v>7</v>
       </c>
@@ -4457,11 +4645,13 @@
       <c r="H136" s="33">
         <v>1555.555556</v>
       </c>
-      <c r="I136" s="33"/>
+      <c r="I136" s="14">
+        <v>346</v>
+      </c>
       <c r="L136" s="2"/>
       <c r="M136" s="3"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:13">
       <c r="A137" s="34">
         <v>7</v>
       </c>
@@ -4486,11 +4676,13 @@
       <c r="H137" s="33">
         <v>2074.0740740000001</v>
       </c>
-      <c r="I137" s="33"/>
+      <c r="I137" s="14">
+        <v>346</v>
+      </c>
       <c r="L137" s="2"/>
       <c r="M137" s="3"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:13">
       <c r="A138" s="34">
         <v>7</v>
       </c>
@@ -4515,11 +4707,13 @@
       <c r="H138" s="33">
         <v>3132.7160490000001</v>
       </c>
-      <c r="I138" s="33"/>
+      <c r="I138" s="14">
+        <v>346</v>
+      </c>
       <c r="L138" s="2"/>
       <c r="M138" s="3"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:13">
       <c r="A139" s="34">
         <v>7</v>
       </c>
@@ -4544,11 +4738,13 @@
       <c r="H139" s="33">
         <v>3175.9259259999999</v>
       </c>
-      <c r="I139" s="33"/>
+      <c r="I139" s="14">
+        <v>346</v>
+      </c>
       <c r="L139" s="2"/>
       <c r="M139" s="3"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:13">
       <c r="A140" s="34">
         <v>7</v>
       </c>
@@ -4573,11 +4769,13 @@
       <c r="H140" s="33">
         <v>3391.9753089999999</v>
       </c>
-      <c r="I140" s="33"/>
+      <c r="I140" s="14">
+        <v>346</v>
+      </c>
       <c r="L140" s="2"/>
       <c r="M140" s="3"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:13">
       <c r="A141" s="34">
         <v>7</v>
       </c>
@@ -4602,10 +4800,12 @@
       <c r="H141" s="33">
         <v>4277.7777779999997</v>
       </c>
-      <c r="I141" s="33"/>
+      <c r="I141" s="14">
+        <v>346</v>
+      </c>
       <c r="L141" s="5"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:13">
       <c r="A142" s="34">
         <v>7</v>
       </c>
@@ -4630,10 +4830,12 @@
       <c r="H142" s="33">
         <v>4472.2222220000003</v>
       </c>
-      <c r="I142" s="33"/>
+      <c r="I142" s="14">
+        <v>346</v>
+      </c>
       <c r="L142" s="5"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:13">
       <c r="A143" s="34">
         <v>7</v>
       </c>
@@ -4658,10 +4860,12 @@
       <c r="H143" s="33">
         <v>4472.2222220000003</v>
       </c>
-      <c r="I143" s="33"/>
+      <c r="I143" s="14">
+        <v>346</v>
+      </c>
       <c r="L143" s="5"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:13">
       <c r="A144" s="34">
         <v>7</v>
       </c>
@@ -4686,10 +4890,12 @@
       <c r="H144" s="33">
         <v>4407.4074069999997</v>
       </c>
-      <c r="I144" s="33"/>
+      <c r="I144" s="14">
+        <v>346</v>
+      </c>
       <c r="L144" s="5"/>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:12">
       <c r="A145" s="34">
         <v>7</v>
       </c>
@@ -4714,10 +4920,12 @@
       <c r="H145" s="33">
         <v>3478.3950620000001</v>
       </c>
-      <c r="I145" s="33"/>
+      <c r="I145" s="14">
+        <v>346</v>
+      </c>
       <c r="L145" s="5"/>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:12">
       <c r="A146" s="34">
         <v>7</v>
       </c>
@@ -4742,10 +4950,12 @@
       <c r="H146" s="33">
         <v>3262.345679</v>
       </c>
-      <c r="I146" s="33"/>
+      <c r="I146" s="14">
+        <v>346</v>
+      </c>
       <c r="L146" s="5"/>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:12">
       <c r="A147" s="34">
         <v>7</v>
       </c>
@@ -4770,10 +4980,12 @@
       <c r="H147" s="33">
         <v>3089.5061730000002</v>
       </c>
-      <c r="I147" s="33"/>
+      <c r="I147" s="14">
+        <v>346</v>
+      </c>
       <c r="L147" s="5"/>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:12">
       <c r="A148" s="34">
         <v>7</v>
       </c>
@@ -4798,10 +5010,12 @@
       <c r="H148" s="33">
         <v>3024.691358</v>
       </c>
-      <c r="I148" s="33"/>
+      <c r="I148" s="14">
+        <v>346</v>
+      </c>
       <c r="L148" s="5"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:12">
       <c r="A149" s="34">
         <v>7</v>
       </c>
@@ -4826,10 +5040,12 @@
       <c r="H149" s="33">
         <v>2527.7777780000001</v>
       </c>
-      <c r="I149" s="33"/>
+      <c r="I149" s="14">
+        <v>346</v>
+      </c>
       <c r="L149" s="5"/>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:12">
       <c r="A150" s="34">
         <v>7</v>
       </c>
@@ -4854,10 +5070,12 @@
       <c r="H150" s="33">
         <v>1469.135802</v>
       </c>
-      <c r="I150" s="33"/>
+      <c r="I150" s="14">
+        <v>346</v>
+      </c>
       <c r="L150" s="5"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:12">
       <c r="A151" s="34">
         <v>7</v>
       </c>
@@ -4882,10 +5100,12 @@
       <c r="H151" s="33">
         <v>151.2345679</v>
       </c>
-      <c r="I151" s="33"/>
+      <c r="I151" s="14">
+        <v>346</v>
+      </c>
       <c r="L151" s="5"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:12">
       <c r="A152" s="34">
         <v>7</v>
       </c>
@@ -4910,10 +5130,12 @@
       <c r="H152" s="33">
         <v>280.86419749999999</v>
       </c>
-      <c r="I152" s="33"/>
+      <c r="I152" s="14">
+        <v>346</v>
+      </c>
       <c r="L152" s="5"/>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:12">
       <c r="A153" s="35">
         <v>7</v>
       </c>
@@ -4938,10 +5160,12 @@
       <c r="H153" s="33">
         <v>0</v>
       </c>
-      <c r="I153" s="33"/>
+      <c r="I153" s="14">
+        <v>346</v>
+      </c>
       <c r="L153" s="5"/>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:12">
       <c r="A154" s="37">
         <v>8</v>
       </c>
@@ -4975,7 +5199,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="5"/>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:12">
       <c r="A155" s="34">
         <v>8</v>
       </c>
@@ -5000,10 +5224,12 @@
       <c r="H155" s="33">
         <v>843.37349400000005</v>
       </c>
-      <c r="I155" s="33"/>
+      <c r="I155" s="14">
+        <v>136</v>
+      </c>
       <c r="L155" s="5"/>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:12">
       <c r="A156" s="34">
         <v>8</v>
       </c>
@@ -5028,10 +5254,12 @@
       <c r="H156" s="33">
         <v>6662.6506019999997</v>
       </c>
-      <c r="I156" s="33"/>
+      <c r="I156" s="14">
+        <v>136</v>
+      </c>
       <c r="L156" s="5"/>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:12">
       <c r="A157" s="34">
         <v>8</v>
       </c>
@@ -5056,10 +5284,12 @@
       <c r="H157" s="33">
         <v>168.67469879999999</v>
       </c>
-      <c r="I157" s="33"/>
+      <c r="I157" s="14">
+        <v>136</v>
+      </c>
       <c r="L157" s="5"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:12">
       <c r="A158" s="34">
         <v>8</v>
       </c>
@@ -5084,10 +5314,12 @@
       <c r="H158" s="33">
         <v>927.71084340000004</v>
       </c>
-      <c r="I158" s="33"/>
+      <c r="I158" s="14">
+        <v>136</v>
+      </c>
       <c r="L158" s="5"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:12">
       <c r="A159" s="34">
         <v>8</v>
       </c>
@@ -5112,10 +5344,12 @@
       <c r="H159" s="33">
         <v>801.20481930000005</v>
       </c>
-      <c r="I159" s="33"/>
+      <c r="I159" s="14">
+        <v>136</v>
+      </c>
       <c r="L159" s="5"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:12">
       <c r="A160" s="34">
         <v>8</v>
       </c>
@@ -5140,10 +5374,12 @@
       <c r="H160" s="33">
         <v>1644.578313</v>
       </c>
-      <c r="I160" s="33"/>
+      <c r="I160" s="14">
+        <v>136</v>
+      </c>
       <c r="L160" s="5"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:12">
       <c r="A161" s="34">
         <v>8</v>
       </c>
@@ -5168,10 +5404,12 @@
       <c r="H161" s="33">
         <v>1391.5662649999999</v>
       </c>
-      <c r="I161" s="33"/>
+      <c r="I161" s="14">
+        <v>136</v>
+      </c>
       <c r="L161" s="5"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:12">
       <c r="A162" s="34">
         <v>8</v>
       </c>
@@ -5196,10 +5434,12 @@
       <c r="H162" s="33">
         <v>1602.409639</v>
       </c>
-      <c r="I162" s="33"/>
+      <c r="I162" s="14">
+        <v>136</v>
+      </c>
       <c r="L162" s="5"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:12">
       <c r="A163" s="34">
         <v>8</v>
       </c>
@@ -5224,10 +5464,12 @@
       <c r="H163" s="33">
         <v>1855.421687</v>
       </c>
-      <c r="I163" s="33"/>
+      <c r="I163" s="14">
+        <v>136</v>
+      </c>
       <c r="L163" s="5"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:12">
       <c r="A164" s="34">
         <v>8</v>
       </c>
@@ -5252,10 +5494,12 @@
       <c r="H164" s="33">
         <v>1096.385542</v>
       </c>
-      <c r="I164" s="33"/>
+      <c r="I164" s="14">
+        <v>136</v>
+      </c>
       <c r="L164" s="5"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:12">
       <c r="A165" s="34">
         <v>8</v>
       </c>
@@ -5280,10 +5524,12 @@
       <c r="H165" s="33">
         <v>1012.048193</v>
       </c>
-      <c r="I165" s="33"/>
+      <c r="I165" s="14">
+        <v>136</v>
+      </c>
       <c r="L165" s="5"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:12">
       <c r="A166" s="34">
         <v>8</v>
       </c>
@@ -5308,10 +5554,12 @@
       <c r="H166" s="33">
         <v>1012.048193</v>
       </c>
-      <c r="I166" s="33"/>
+      <c r="I166" s="14">
+        <v>136</v>
+      </c>
       <c r="L166" s="5"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:12">
       <c r="A167" s="34">
         <v>8</v>
       </c>
@@ -5336,10 +5584,12 @@
       <c r="H167" s="33">
         <v>1012.048193</v>
       </c>
-      <c r="I167" s="33"/>
+      <c r="I167" s="14">
+        <v>136</v>
+      </c>
       <c r="L167" s="5"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:12">
       <c r="A168" s="34">
         <v>8</v>
       </c>
@@ -5364,10 +5614,12 @@
       <c r="H168" s="33">
         <v>590.36144579999996</v>
       </c>
-      <c r="I168" s="33"/>
+      <c r="I168" s="14">
+        <v>136</v>
+      </c>
       <c r="L168" s="5"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:12">
       <c r="A169" s="34">
         <v>8</v>
       </c>
@@ -5392,10 +5644,12 @@
       <c r="H169" s="33">
         <v>253.01204820000001</v>
       </c>
-      <c r="I169" s="33"/>
+      <c r="I169" s="14">
+        <v>136</v>
+      </c>
       <c r="L169" s="5"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:12">
       <c r="A170" s="34">
         <v>8</v>
       </c>
@@ -5420,10 +5674,12 @@
       <c r="H170" s="33">
         <v>674.69879519999995</v>
       </c>
-      <c r="I170" s="33"/>
+      <c r="I170" s="14">
+        <v>136</v>
+      </c>
       <c r="L170" s="5"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:12">
       <c r="A171" s="34">
         <v>8</v>
       </c>
@@ -5448,10 +5704,12 @@
       <c r="H171" s="33">
         <v>168.67469879999999</v>
       </c>
-      <c r="I171" s="33"/>
+      <c r="I171" s="14">
+        <v>136</v>
+      </c>
       <c r="L171" s="5"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:12">
       <c r="A172" s="34">
         <v>8</v>
       </c>
@@ -5476,10 +5734,12 @@
       <c r="H172" s="33">
         <v>126.5060241</v>
       </c>
-      <c r="I172" s="33"/>
+      <c r="I172" s="14">
+        <v>136</v>
+      </c>
       <c r="L172" s="5"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:12">
       <c r="A173" s="34">
         <v>8</v>
       </c>
@@ -5504,10 +5764,12 @@
       <c r="H173" s="33">
         <v>84.337349399999994</v>
       </c>
-      <c r="I173" s="33"/>
+      <c r="I173" s="14">
+        <v>136</v>
+      </c>
       <c r="L173" s="5"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:12">
       <c r="A174" s="34">
         <v>8</v>
       </c>
@@ -5532,10 +5794,12 @@
       <c r="H174" s="33">
         <v>0</v>
       </c>
-      <c r="I174" s="33"/>
+      <c r="I174" s="14">
+        <v>136</v>
+      </c>
       <c r="L174" s="5"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:12">
       <c r="A175" s="35">
         <v>8</v>
       </c>
@@ -5560,10 +5824,12 @@
       <c r="H175" s="33">
         <v>0</v>
       </c>
-      <c r="I175" s="33"/>
+      <c r="I175" s="14">
+        <v>136</v>
+      </c>
       <c r="L175" s="5"/>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:12">
       <c r="A176" s="37">
         <v>9</v>
       </c>
@@ -5597,7 +5863,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="5"/>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:12">
       <c r="A177" s="34">
         <v>9</v>
       </c>
@@ -5622,10 +5888,12 @@
       <c r="H177" s="33">
         <v>0</v>
       </c>
-      <c r="I177" s="33"/>
+      <c r="I177" s="14">
+        <v>57</v>
+      </c>
       <c r="L177" s="5"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:12">
       <c r="A178" s="34">
         <v>9</v>
       </c>
@@ -5650,10 +5918,12 @@
       <c r="H178" s="33">
         <v>0</v>
       </c>
-      <c r="I178" s="33"/>
+      <c r="I178" s="14">
+        <v>57</v>
+      </c>
       <c r="L178" s="5"/>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:12">
       <c r="A179" s="34">
         <v>9</v>
       </c>
@@ -5678,10 +5948,12 @@
       <c r="H179" s="33">
         <v>44.943820219999999</v>
       </c>
-      <c r="I179" s="33"/>
+      <c r="I179" s="14">
+        <v>57</v>
+      </c>
       <c r="L179" s="5"/>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:12">
       <c r="A180" s="34">
         <v>9</v>
       </c>
@@ -5706,10 +5978,12 @@
       <c r="H180" s="33">
         <v>152.80898880000001</v>
       </c>
-      <c r="I180" s="33"/>
+      <c r="I180" s="14">
+        <v>57</v>
+      </c>
       <c r="L180" s="5"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:12">
       <c r="A181" s="34">
         <v>9</v>
       </c>
@@ -5734,10 +6008,12 @@
       <c r="H181" s="33">
         <v>53.93258427</v>
       </c>
-      <c r="I181" s="33"/>
+      <c r="I181" s="14">
+        <v>57</v>
+      </c>
       <c r="L181" s="5"/>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:12">
       <c r="A182" s="34">
         <v>9</v>
       </c>
@@ -5762,10 +6038,12 @@
       <c r="H182" s="33">
         <v>94.382022469999995</v>
       </c>
-      <c r="I182" s="33"/>
+      <c r="I182" s="14">
+        <v>57</v>
+      </c>
       <c r="L182" s="5"/>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:12">
       <c r="A183" s="34">
         <v>9</v>
       </c>
@@ -5790,10 +6068,12 @@
       <c r="H183" s="33">
         <v>49.438202250000003</v>
       </c>
-      <c r="I183" s="33"/>
+      <c r="I183" s="14">
+        <v>57</v>
+      </c>
       <c r="L183" s="5"/>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:12">
       <c r="A184" s="34">
         <v>9</v>
       </c>
@@ -5818,10 +6098,12 @@
       <c r="H184" s="33">
         <v>89.887640450000006</v>
       </c>
-      <c r="I184" s="33"/>
+      <c r="I184" s="14">
+        <v>57</v>
+      </c>
       <c r="L184" s="5"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:12">
       <c r="A185" s="34">
         <v>9</v>
       </c>
@@ -5846,10 +6128,12 @@
       <c r="H185" s="33">
         <v>98.876404489999999</v>
       </c>
-      <c r="I185" s="33"/>
+      <c r="I185" s="14">
+        <v>57</v>
+      </c>
       <c r="L185" s="5"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:12">
       <c r="A186" s="34">
         <v>9</v>
       </c>
@@ -5874,10 +6158,12 @@
       <c r="H186" s="33">
         <v>404.49438199999997</v>
       </c>
-      <c r="I186" s="33"/>
+      <c r="I186" s="14">
+        <v>57</v>
+      </c>
       <c r="L186" s="5"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:12">
       <c r="A187" s="34">
         <v>9</v>
       </c>
@@ -5902,10 +6188,12 @@
       <c r="H187" s="33">
         <v>444.9438202</v>
       </c>
-      <c r="I187" s="33"/>
+      <c r="I187" s="14">
+        <v>57</v>
+      </c>
       <c r="L187" s="5"/>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:12">
       <c r="A188" s="34">
         <v>9</v>
       </c>
@@ -5930,10 +6218,12 @@
       <c r="H188" s="33">
         <v>804.49438199999997</v>
       </c>
-      <c r="I188" s="33"/>
+      <c r="I188" s="14">
+        <v>57</v>
+      </c>
       <c r="L188" s="5"/>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:12">
       <c r="A189" s="34">
         <v>9</v>
       </c>
@@ -5958,10 +6248,12 @@
       <c r="H189" s="33">
         <v>611.23595509999996</v>
       </c>
-      <c r="I189" s="33"/>
+      <c r="I189" s="14">
+        <v>57</v>
+      </c>
       <c r="L189" s="5"/>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:12">
       <c r="A190" s="34">
         <v>9</v>
       </c>
@@ -5986,10 +6278,12 @@
       <c r="H190" s="33">
         <v>853.93258430000003</v>
       </c>
-      <c r="I190" s="33"/>
+      <c r="I190" s="14">
+        <v>57</v>
+      </c>
       <c r="L190" s="5"/>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:12">
       <c r="A191" s="34">
         <v>9</v>
       </c>
@@ -6014,10 +6308,12 @@
       <c r="H191" s="33">
         <v>840.44943820000003</v>
       </c>
-      <c r="I191" s="33"/>
+      <c r="I191" s="14">
+        <v>57</v>
+      </c>
       <c r="L191" s="5"/>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:12">
       <c r="A192" s="34">
         <v>9</v>
       </c>
@@ -6042,10 +6338,12 @@
       <c r="H192" s="33">
         <v>1271.910112</v>
       </c>
-      <c r="I192" s="33"/>
+      <c r="I192" s="14">
+        <v>57</v>
+      </c>
       <c r="L192" s="5"/>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:12">
       <c r="A193" s="34">
         <v>9</v>
       </c>
@@ -6070,10 +6368,12 @@
       <c r="H193" s="33">
         <v>975.28089890000001</v>
       </c>
-      <c r="I193" s="33"/>
+      <c r="I193" s="14">
+        <v>57</v>
+      </c>
       <c r="L193" s="5"/>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:12">
       <c r="A194" s="34">
         <v>9</v>
       </c>
@@ -6098,10 +6398,12 @@
       <c r="H194" s="33">
         <v>633.70786520000001</v>
       </c>
-      <c r="I194" s="33"/>
+      <c r="I194" s="14">
+        <v>57</v>
+      </c>
       <c r="L194" s="5"/>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:12">
       <c r="A195" s="34">
         <v>9</v>
       </c>
@@ -6126,10 +6428,12 @@
       <c r="H195" s="33">
         <v>759.55056179999997</v>
       </c>
-      <c r="I195" s="33"/>
+      <c r="I195" s="14">
+        <v>57</v>
+      </c>
       <c r="L195" s="5"/>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:12">
       <c r="A196" s="34">
         <v>9</v>
       </c>
@@ -6154,10 +6458,12 @@
       <c r="H196" s="33">
         <v>350.56179780000002</v>
       </c>
-      <c r="I196" s="33"/>
+      <c r="I196" s="14">
+        <v>57</v>
+      </c>
       <c r="L196" s="5"/>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:12">
       <c r="A197" s="34">
         <v>9</v>
       </c>
@@ -6182,10 +6488,12 @@
       <c r="H197" s="33">
         <v>157.30337080000001</v>
       </c>
-      <c r="I197" s="33"/>
+      <c r="I197" s="14">
+        <v>57</v>
+      </c>
       <c r="L197" s="5"/>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:12">
       <c r="A198" s="34">
         <v>9</v>
       </c>
@@ -6210,10 +6518,12 @@
       <c r="H198" s="33">
         <v>80.898876400000006</v>
       </c>
-      <c r="I198" s="33"/>
+      <c r="I198" s="14">
+        <v>57</v>
+      </c>
       <c r="L198" s="5"/>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:12">
       <c r="A199" s="34">
         <v>9</v>
       </c>
@@ -6238,10 +6548,12 @@
       <c r="H199" s="33">
         <v>0</v>
       </c>
-      <c r="I199" s="33"/>
+      <c r="I199" s="14">
+        <v>57</v>
+      </c>
       <c r="L199" s="5"/>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:12">
       <c r="A200" s="35">
         <v>9</v>
       </c>
@@ -6266,10 +6578,12 @@
       <c r="H200" s="33">
         <v>0</v>
       </c>
-      <c r="I200" s="33"/>
+      <c r="I200" s="14">
+        <v>57</v>
+      </c>
       <c r="L200" s="5"/>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:12">
       <c r="A201" s="37">
         <v>10</v>
       </c>
@@ -6299,7 +6613,7 @@
       </c>
       <c r="L201" s="5"/>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:12">
       <c r="A202" s="34">
         <v>10</v>
       </c>
@@ -6324,10 +6638,12 @@
       <c r="H202" s="33">
         <v>0</v>
       </c>
-      <c r="I202" s="33"/>
+      <c r="I202" s="14">
+        <v>38</v>
+      </c>
       <c r="L202" s="5"/>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:12">
       <c r="A203" s="34">
         <v>10</v>
       </c>
@@ -6352,10 +6668,12 @@
       <c r="H203" s="33">
         <v>36.011080329999999</v>
       </c>
-      <c r="I203" s="33"/>
+      <c r="I203" s="14">
+        <v>38</v>
+      </c>
       <c r="L203" s="5"/>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:12">
       <c r="A204" s="34">
         <v>10</v>
       </c>
@@ -6380,10 +6698,12 @@
       <c r="H204" s="33">
         <v>121.8836565</v>
       </c>
-      <c r="I204" s="33"/>
+      <c r="I204" s="14">
+        <v>38</v>
+      </c>
       <c r="L204" s="5"/>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:12">
       <c r="A205" s="34">
         <v>10</v>
       </c>
@@ -6408,10 +6728,12 @@
       <c r="H205" s="33">
         <v>49.861495840000003</v>
       </c>
-      <c r="I205" s="33"/>
+      <c r="I205" s="14">
+        <v>38</v>
+      </c>
       <c r="L205" s="5"/>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:12">
       <c r="A206" s="34">
         <v>10</v>
       </c>
@@ -6436,10 +6758,12 @@
       <c r="H206" s="33">
         <v>545.70637120000004</v>
       </c>
-      <c r="I206" s="33"/>
+      <c r="I206" s="14">
+        <v>38</v>
+      </c>
       <c r="L206" s="5"/>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:12">
       <c r="A207" s="34">
         <v>10</v>
       </c>
@@ -6464,10 +6788,12 @@
       <c r="H207" s="33">
         <v>80.33240997</v>
       </c>
-      <c r="I207" s="33"/>
+      <c r="I207" s="14">
+        <v>38</v>
+      </c>
       <c r="L207" s="5"/>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:12">
       <c r="A208" s="34">
         <v>10</v>
       </c>
@@ -6492,10 +6818,12 @@
       <c r="H208" s="33">
         <v>282.54847649999999</v>
       </c>
-      <c r="I208" s="33"/>
+      <c r="I208" s="14">
+        <v>38</v>
+      </c>
       <c r="L208" s="5"/>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:12">
       <c r="A209" s="34">
         <v>10</v>
       </c>
@@ -6520,10 +6848,12 @@
       <c r="H209" s="33">
         <v>235.45706369999999</v>
       </c>
-      <c r="I209" s="33"/>
+      <c r="I209" s="14">
+        <v>38</v>
+      </c>
       <c r="L209" s="5"/>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:12">
       <c r="A210" s="34">
         <v>10</v>
       </c>
@@ -6548,10 +6878,12 @@
       <c r="H210" s="33">
         <v>432.13296400000002</v>
       </c>
-      <c r="I210" s="33"/>
+      <c r="I210" s="14">
+        <v>38</v>
+      </c>
       <c r="L210" s="5"/>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:12">
       <c r="A211" s="34">
         <v>10</v>
       </c>
@@ -6576,10 +6908,12 @@
       <c r="H211" s="33">
         <v>614.95844880000004</v>
       </c>
-      <c r="I211" s="33"/>
+      <c r="I211" s="14">
+        <v>38</v>
+      </c>
       <c r="L211" s="5"/>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:12">
       <c r="A212" s="34">
         <v>10</v>
       </c>
@@ -6604,10 +6938,12 @@
       <c r="H212" s="33">
         <v>554.01662050000004</v>
       </c>
-      <c r="I212" s="33"/>
+      <c r="I212" s="14">
+        <v>38</v>
+      </c>
       <c r="L212" s="5"/>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:12">
       <c r="A213" s="34">
         <v>10</v>
       </c>
@@ -6632,10 +6968,12 @@
       <c r="H213" s="33">
         <v>944.59833800000001</v>
       </c>
-      <c r="I213" s="33"/>
+      <c r="I213" s="14">
+        <v>38</v>
+      </c>
       <c r="L213" s="5"/>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:12">
       <c r="A214" s="34">
         <v>10</v>
       </c>
@@ -6660,10 +6998,12 @@
       <c r="H214" s="33">
         <v>739.61218840000004</v>
       </c>
-      <c r="I214" s="33"/>
+      <c r="I214" s="14">
+        <v>38</v>
+      </c>
       <c r="L214" s="5"/>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:12">
       <c r="A215" s="34">
         <v>10</v>
       </c>
@@ -6688,10 +7028,12 @@
       <c r="H215" s="33">
         <v>645.4293629</v>
       </c>
-      <c r="I215" s="33"/>
+      <c r="I215" s="14">
+        <v>38</v>
+      </c>
       <c r="L215" s="5"/>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:12">
       <c r="A216" s="34">
         <v>10</v>
       </c>
@@ -6716,10 +7058,12 @@
       <c r="H216" s="33">
         <v>340.7202216</v>
       </c>
-      <c r="I216" s="33"/>
+      <c r="I216" s="14">
+        <v>38</v>
+      </c>
       <c r="L216" s="5"/>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:12">
       <c r="A217" s="34">
         <v>10</v>
       </c>
@@ -6744,10 +7088,12 @@
       <c r="H217" s="33">
         <v>116.3434903</v>
       </c>
-      <c r="I217" s="33"/>
+      <c r="I217" s="14">
+        <v>38</v>
+      </c>
       <c r="L217" s="5"/>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:12">
       <c r="A218" s="34">
         <v>10</v>
       </c>
@@ -6772,10 +7118,12 @@
       <c r="H218" s="33">
         <v>0</v>
       </c>
-      <c r="I218" s="33"/>
+      <c r="I218" s="14">
+        <v>38</v>
+      </c>
       <c r="L218" s="5"/>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:12">
       <c r="A219" s="34">
         <v>10</v>
       </c>
@@ -6800,10 +7148,12 @@
       <c r="H219" s="33">
         <v>30.470914130000001</v>
       </c>
-      <c r="I219" s="33"/>
+      <c r="I219" s="14">
+        <v>38</v>
+      </c>
       <c r="L219" s="5"/>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:12">
       <c r="A220" s="34">
         <v>10</v>
       </c>
@@ -6828,10 +7178,12 @@
       <c r="H220" s="33">
         <v>2.7700831020000001</v>
       </c>
-      <c r="I220" s="33"/>
+      <c r="I220" s="14">
+        <v>38</v>
+      </c>
       <c r="L220" s="5"/>
     </row>
-    <row r="221" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:12" ht="20.65" thickBot="1">
       <c r="A221" s="39">
         <v>10</v>
       </c>
@@ -6856,10 +7208,12 @@
       <c r="H221" s="33">
         <v>0</v>
       </c>
-      <c r="I221" s="33"/>
+      <c r="I221" s="14">
+        <v>38</v>
+      </c>
       <c r="L221" s="5"/>
     </row>
-    <row r="222" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:12" ht="20.65" thickBot="1">
       <c r="A222" s="41">
         <v>11</v>
       </c>
@@ -6889,7 +7243,7 @@
       </c>
       <c r="L222" s="5"/>
     </row>
-    <row r="223" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:12" ht="20.65" thickBot="1">
       <c r="A223" s="42">
         <v>11</v>
       </c>
@@ -6914,10 +7268,12 @@
       <c r="H223" s="33">
         <v>94.095940959999993</v>
       </c>
-      <c r="I223" s="33"/>
+      <c r="I223" s="14">
+        <v>60</v>
+      </c>
       <c r="L223" s="5"/>
     </row>
-    <row r="224" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:12" ht="20.65" thickBot="1">
       <c r="A224" s="42">
         <v>11</v>
       </c>
@@ -6942,10 +7298,12 @@
       <c r="H224" s="33">
         <v>287.82287819999999</v>
       </c>
-      <c r="I224" s="33"/>
+      <c r="I224" s="14">
+        <v>60</v>
+      </c>
       <c r="L224" s="5"/>
     </row>
-    <row r="225" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:12" ht="20.65" thickBot="1">
       <c r="A225" s="42">
         <v>11</v>
       </c>
@@ -6970,10 +7328,12 @@
       <c r="H225" s="33">
         <v>426.19926199999998</v>
       </c>
-      <c r="I225" s="33"/>
+      <c r="I225" s="14">
+        <v>60</v>
+      </c>
       <c r="L225" s="5"/>
     </row>
-    <row r="226" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:12" ht="20.65" thickBot="1">
       <c r="A226" s="42">
         <v>11</v>
       </c>
@@ -6998,10 +7358,12 @@
       <c r="H226" s="33">
         <v>774.90774910000005</v>
       </c>
-      <c r="I226" s="33"/>
+      <c r="I226" s="14">
+        <v>60</v>
+      </c>
       <c r="L226" s="5"/>
     </row>
-    <row r="227" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:12" ht="20.65" thickBot="1">
       <c r="A227" s="42">
         <v>11</v>
       </c>
@@ -7026,10 +7388,12 @@
       <c r="H227" s="33">
         <v>869.00369000000001</v>
       </c>
-      <c r="I227" s="33"/>
+      <c r="I227" s="14">
+        <v>60</v>
+      </c>
       <c r="L227" s="5"/>
     </row>
-    <row r="228" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:12" ht="20.65" thickBot="1">
       <c r="A228" s="42">
         <v>11</v>
       </c>
@@ -7054,10 +7418,12 @@
       <c r="H228" s="33">
         <v>918.81918819999999</v>
       </c>
-      <c r="I228" s="33"/>
+      <c r="I228" s="14">
+        <v>60</v>
+      </c>
       <c r="L228" s="5"/>
     </row>
-    <row r="229" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:12" ht="20.65" thickBot="1">
       <c r="A229" s="42">
         <v>11</v>
       </c>
@@ -7082,10 +7448,12 @@
       <c r="H229" s="33">
         <v>891.14391139999998</v>
       </c>
-      <c r="I229" s="33"/>
+      <c r="I229" s="14">
+        <v>60</v>
+      </c>
       <c r="L229" s="5"/>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:12">
       <c r="A230" s="43">
         <v>11</v>
       </c>
@@ -7110,10 +7478,12 @@
       <c r="H230" s="33">
         <v>337.63837640000003</v>
       </c>
-      <c r="I230" s="33"/>
+      <c r="I230" s="14">
+        <v>60</v>
+      </c>
       <c r="L230" s="5"/>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:12">
       <c r="A231" s="44">
         <v>12</v>
       </c>
@@ -7143,7 +7513,7 @@
       </c>
       <c r="L231" s="5"/>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:12">
       <c r="A232" s="42">
         <v>12</v>
       </c>
@@ -7168,10 +7538,12 @@
       <c r="H232" s="33">
         <v>94.095940959999993</v>
       </c>
-      <c r="I232" s="33"/>
+      <c r="I232" s="14">
+        <v>69</v>
+      </c>
       <c r="L232" s="5"/>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:12">
       <c r="A233" s="42">
         <v>12</v>
       </c>
@@ -7196,10 +7568,12 @@
       <c r="H233" s="33">
         <v>99.63099631</v>
       </c>
-      <c r="I233" s="33"/>
+      <c r="I233" s="14">
+        <v>69</v>
+      </c>
       <c r="L233" s="5"/>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:12">
       <c r="A234" s="42">
         <v>12</v>
       </c>
@@ -7224,10 +7598,12 @@
       <c r="H234" s="33">
         <v>487.08487079999998</v>
       </c>
-      <c r="I234" s="33"/>
+      <c r="I234" s="14">
+        <v>69</v>
+      </c>
       <c r="L234" s="5"/>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:12">
       <c r="A235" s="42">
         <v>12</v>
       </c>
@@ -7252,10 +7628,12 @@
       <c r="H235" s="33">
         <v>570.11070110000003</v>
       </c>
-      <c r="I235" s="33"/>
+      <c r="I235" s="14">
+        <v>69</v>
+      </c>
       <c r="L235" s="5"/>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:12">
       <c r="A236" s="42">
         <v>12</v>
       </c>
@@ -7280,10 +7658,12 @@
       <c r="H236" s="33">
         <v>846.86346860000003</v>
       </c>
-      <c r="I236" s="33"/>
+      <c r="I236" s="14">
+        <v>69</v>
+      </c>
       <c r="L236" s="5"/>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:12">
       <c r="A237" s="42">
         <v>12</v>
       </c>
@@ -7308,10 +7688,12 @@
       <c r="H237" s="33">
         <v>869.00369000000001</v>
       </c>
-      <c r="I237" s="33"/>
+      <c r="I237" s="14">
+        <v>69</v>
+      </c>
       <c r="L237" s="5"/>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:12">
       <c r="A238" s="42">
         <v>12</v>
       </c>
@@ -7336,10 +7718,12 @@
       <c r="H238" s="33">
         <v>1173.431734</v>
       </c>
-      <c r="I238" s="33"/>
+      <c r="I238" s="14">
+        <v>69</v>
+      </c>
       <c r="L238" s="5"/>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:12">
       <c r="A239" s="42">
         <v>12</v>
       </c>
@@ -7364,10 +7748,12 @@
       <c r="H239" s="33">
         <v>852.39852399999995</v>
       </c>
-      <c r="I239" s="33"/>
+      <c r="I239" s="14">
+        <v>69</v>
+      </c>
       <c r="L239" s="5"/>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:12">
       <c r="A240" s="42">
         <v>12</v>
       </c>
@@ -7392,10 +7778,12 @@
       <c r="H240" s="33">
         <v>387.45387449999998</v>
       </c>
-      <c r="I240" s="33"/>
+      <c r="I240" s="14">
+        <v>69</v>
+      </c>
       <c r="L240" s="5"/>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:12">
       <c r="A241" s="43">
         <v>12</v>
       </c>
@@ -7420,10 +7808,12 @@
       <c r="H241" s="33">
         <v>343.17343169999998</v>
       </c>
-      <c r="I241" s="33"/>
+      <c r="I241" s="14">
+        <v>69</v>
+      </c>
       <c r="L241" s="5"/>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:12">
       <c r="A242" s="44">
         <v>13</v>
       </c>
@@ -7452,7 +7842,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:12">
       <c r="A243" s="42">
         <v>13</v>
       </c>
@@ -7477,9 +7867,11 @@
       <c r="H243" s="26">
         <v>94.095940959409702</v>
       </c>
-      <c r="I243" s="26"/>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="I243" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12">
       <c r="A244" s="42">
         <v>13</v>
       </c>
@@ -7504,9 +7896,11 @@
       <c r="H244" s="26">
         <v>94.095940959409702</v>
       </c>
-      <c r="I244" s="26"/>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="I244" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12">
       <c r="A245" s="42">
         <v>13</v>
       </c>
@@ -7531,9 +7925,11 @@
       <c r="H245" s="26">
         <v>370.84870848708402</v>
       </c>
-      <c r="I245" s="26"/>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="I245" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12">
       <c r="A246" s="42">
         <v>13</v>
       </c>
@@ -7558,9 +7954,11 @@
       <c r="H246" s="26">
         <v>442.80442804427997</v>
       </c>
-      <c r="I246" s="26"/>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="I246" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12">
       <c r="A247" s="42">
         <v>13</v>
       </c>
@@ -7585,9 +7983,11 @@
       <c r="H247" s="26">
         <v>697.41697416974102</v>
       </c>
-      <c r="I247" s="26"/>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="I247" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12">
       <c r="A248" s="42">
         <v>13</v>
       </c>
@@ -7612,9 +8012,11 @@
       <c r="H248" s="26">
         <v>990.77490774907699</v>
       </c>
-      <c r="I248" s="26"/>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="I248" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12">
       <c r="A249" s="42">
         <v>13</v>
       </c>
@@ -7639,9 +8041,11 @@
       <c r="H249" s="26">
         <v>869.00369003690003</v>
       </c>
-      <c r="I249" s="26"/>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="I249" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12">
       <c r="A250" s="42">
         <v>13</v>
       </c>
@@ -7666,9 +8070,11 @@
       <c r="H250" s="26">
         <v>536.90036900369</v>
       </c>
-      <c r="I250" s="26"/>
-    </row>
-    <row r="251" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="I250" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" ht="20.65" thickBot="1">
       <c r="A251" s="48">
         <v>13</v>
       </c>
@@ -7693,7 +8099,9 @@
       <c r="H251" s="26">
         <v>420.66420664206601</v>
       </c>
-      <c r="I251" s="26"/>
+      <c r="I251" s="14">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7704,14 +8112,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="109.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.26953125" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="109.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.4">
       <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
@@ -7722,7 +8130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15.4">
       <c r="A2" s="11" t="s">
         <v>30</v>
       </c>
@@ -7733,7 +8141,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15.4">
       <c r="A3" s="6" t="s">
         <v>31</v>
       </c>
@@ -7744,7 +8152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="15.4">
       <c r="A4" s="6" t="s">
         <v>32</v>
       </c>
@@ -7755,7 +8163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="15.4">
       <c r="A5" s="6" t="s">
         <v>43</v>
       </c>
@@ -7766,42 +8174,42 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="15.4">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
     </row>
-    <row r="7" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="15.4">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="15.4">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="15.4">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="15.4">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="15.4">
       <c r="A11" s="6">
         <v>10</v>
       </c>

--- a/Data/Initial_Database.xlsx
+++ b/Data/Initial_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\Methane_Prediction\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E3A4AD-3315-411D-B87A-CE0CF7D13412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F81B28-3F2E-4ECA-9A7D-966D6346C60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="43">
   <si>
     <t>Paper_Title</t>
   </si>
@@ -145,46 +145,7 @@
     <t>Calmati-202</t>
   </si>
   <si>
-    <t>Calmati-203</t>
-  </si>
-  <si>
-    <t>Calmati-204</t>
-  </si>
-  <si>
-    <t>Calmati-205</t>
-  </si>
-  <si>
-    <t>Calmati-206</t>
-  </si>
-  <si>
-    <t>Calmati-207</t>
-  </si>
-  <si>
-    <t>Calmati-208</t>
-  </si>
-  <si>
-    <t>Calmati-209</t>
-  </si>
-  <si>
-    <t>Calmati-210</t>
-  </si>
-  <si>
-    <t>Calmati-211</t>
-  </si>
-  <si>
     <t>11~13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Original_Emission_g_CH4-C_ha-1_day-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Original_Cumulative_CH_4-C_kg_ha-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cumulative_seaonal_kg_CH4_ha-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -238,6 +199,15 @@
   <si>
     <t>Days_After_Flooding</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cumulative_seaonal_kg_CH4_ha</t>
+  </si>
+  <si>
+    <t>Original_Emission_g_CH4-C_ha_day</t>
+  </si>
+  <si>
+    <t>Original_Cumulative_CH_4-C_kg_ha</t>
   </si>
 </sst>
 </file>
@@ -850,22 +820,23 @@
   <dimension ref="A1:T251"/>
   <sheetFormatPr defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="1" width="11.73046875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="21.9296875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="16.73046875" style="14" customWidth="1"/>
-    <col min="4" max="6" width="11.73046875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="15.73046875" style="14" customWidth="1"/>
-    <col min="8" max="8" width="19.73046875" style="14" customWidth="1"/>
-    <col min="9" max="9" width="18.59765625" style="14" customWidth="1"/>
-    <col min="10" max="10" width="11.73046875" style="14" customWidth="1"/>
-    <col min="11" max="11" width="12.9296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="22" style="14" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.7109375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="14" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" style="14" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="14" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="16" width="9" style="1"/>
-    <col min="17" max="17" width="9.06640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="9" customFormat="1" ht="79.900000000000006">
+    <row r="1" spans="1:20" s="9" customFormat="1" ht="81">
       <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
@@ -873,7 +844,7 @@
         <v>13</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>4</v>
@@ -885,16 +856,16 @@
         <v>6</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -2264,7 +2235,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="20.65" thickBot="1">
+    <row r="61" spans="1:19" ht="21" thickBot="1">
       <c r="A61" s="21">
         <v>3</v>
       </c>
@@ -2287,7 +2258,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="21.4" thickBot="1">
+    <row r="62" spans="1:19" ht="21.75" thickBot="1">
       <c r="A62" s="23">
         <v>4</v>
       </c>
@@ -2316,13 +2287,13 @@
         <v>212</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
     </row>
-    <row r="63" spans="1:19" ht="20.65" thickBot="1">
+    <row r="63" spans="1:19" ht="21" thickBot="1">
       <c r="A63" s="27">
         <v>4</v>
       </c>
@@ -2354,7 +2325,7 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
     </row>
-    <row r="64" spans="1:19" ht="20.65" thickBot="1">
+    <row r="64" spans="1:19" ht="21" thickBot="1">
       <c r="A64" s="27">
         <v>4</v>
       </c>
@@ -2386,7 +2357,7 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
     </row>
-    <row r="65" spans="1:19" ht="20.65" thickBot="1">
+    <row r="65" spans="1:19" ht="21" thickBot="1">
       <c r="A65" s="27">
         <v>4</v>
       </c>
@@ -2418,7 +2389,7 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
     </row>
-    <row r="66" spans="1:19" ht="20.65" thickBot="1">
+    <row r="66" spans="1:19" ht="21" thickBot="1">
       <c r="A66" s="27">
         <v>4</v>
       </c>
@@ -2450,7 +2421,7 @@
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
     </row>
-    <row r="67" spans="1:19" ht="20.65" thickBot="1">
+    <row r="67" spans="1:19" ht="21" thickBot="1">
       <c r="A67" s="27">
         <v>4</v>
       </c>
@@ -2482,7 +2453,7 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68" spans="1:19" ht="20.65" thickBot="1">
+    <row r="68" spans="1:19" ht="21" thickBot="1">
       <c r="A68" s="27">
         <v>4</v>
       </c>
@@ -2514,7 +2485,7 @@
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
     </row>
-    <row r="69" spans="1:19" ht="20.65" thickBot="1">
+    <row r="69" spans="1:19" ht="21" thickBot="1">
       <c r="A69" s="27">
         <v>4</v>
       </c>
@@ -2546,7 +2517,7 @@
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
     </row>
-    <row r="70" spans="1:19" ht="20.65" thickBot="1">
+    <row r="70" spans="1:19" ht="21" thickBot="1">
       <c r="A70" s="27">
         <v>4</v>
       </c>
@@ -2578,7 +2549,7 @@
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
     </row>
-    <row r="71" spans="1:19" ht="20.65" thickBot="1">
+    <row r="71" spans="1:19" ht="21" thickBot="1">
       <c r="A71" s="27">
         <v>4</v>
       </c>
@@ -2610,7 +2581,7 @@
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
     </row>
-    <row r="72" spans="1:19" ht="20.65" thickBot="1">
+    <row r="72" spans="1:19" ht="21" thickBot="1">
       <c r="A72" s="27">
         <v>4</v>
       </c>
@@ -2642,7 +2613,7 @@
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
     </row>
-    <row r="73" spans="1:19" ht="20.65" thickBot="1">
+    <row r="73" spans="1:19" ht="21" thickBot="1">
       <c r="A73" s="27">
         <v>4</v>
       </c>
@@ -2674,7 +2645,7 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
     </row>
-    <row r="74" spans="1:19" ht="20.65" thickBot="1">
+    <row r="74" spans="1:19" ht="21" thickBot="1">
       <c r="A74" s="27">
         <v>4</v>
       </c>
@@ -2706,7 +2677,7 @@
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
     </row>
-    <row r="75" spans="1:19" ht="20.65" thickBot="1">
+    <row r="75" spans="1:19" ht="21" thickBot="1">
       <c r="A75" s="27">
         <v>4</v>
       </c>
@@ -2738,7 +2709,7 @@
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
     </row>
-    <row r="76" spans="1:19" ht="20.65" thickBot="1">
+    <row r="76" spans="1:19" ht="21" thickBot="1">
       <c r="A76" s="27">
         <v>4</v>
       </c>
@@ -2770,7 +2741,7 @@
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
     </row>
-    <row r="77" spans="1:19" ht="20.65" thickBot="1">
+    <row r="77" spans="1:19" ht="21" thickBot="1">
       <c r="A77" s="27">
         <v>4</v>
       </c>
@@ -2802,7 +2773,7 @@
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
     </row>
-    <row r="78" spans="1:19" ht="20.65" thickBot="1">
+    <row r="78" spans="1:19" ht="21" thickBot="1">
       <c r="A78" s="27">
         <v>4</v>
       </c>
@@ -2834,7 +2805,7 @@
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
     </row>
-    <row r="79" spans="1:19" ht="20.65" thickBot="1">
+    <row r="79" spans="1:19" ht="21" thickBot="1">
       <c r="A79" s="27">
         <v>4</v>
       </c>
@@ -2866,7 +2837,7 @@
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
     </row>
-    <row r="80" spans="1:19" ht="20.65" thickBot="1">
+    <row r="80" spans="1:19" ht="21" thickBot="1">
       <c r="A80" s="27">
         <v>4</v>
       </c>
@@ -2898,7 +2869,7 @@
       <c r="R80" s="2"/>
       <c r="S80" s="2"/>
     </row>
-    <row r="81" spans="1:19" ht="20.65" thickBot="1">
+    <row r="81" spans="1:19" ht="21" thickBot="1">
       <c r="A81" s="27">
         <v>4</v>
       </c>
@@ -2930,7 +2901,7 @@
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
     </row>
-    <row r="82" spans="1:19" ht="20.65" thickBot="1">
+    <row r="82" spans="1:19" ht="21" thickBot="1">
       <c r="A82" s="27">
         <v>4</v>
       </c>
@@ -2962,7 +2933,7 @@
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
     </row>
-    <row r="83" spans="1:19" ht="20.65" thickBot="1">
+    <row r="83" spans="1:19" ht="21" thickBot="1">
       <c r="A83" s="27">
         <v>4</v>
       </c>
@@ -3858,7 +3829,7 @@
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
     </row>
-    <row r="111" spans="1:19" ht="20.65" thickBot="1">
+    <row r="111" spans="1:19" ht="21" thickBot="1">
       <c r="A111" s="30">
         <v>5</v>
       </c>
@@ -3891,7 +3862,7 @@
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
     </row>
-    <row r="112" spans="1:19" ht="20.65" thickBot="1">
+    <row r="112" spans="1:19" ht="21" thickBot="1">
       <c r="A112" s="31">
         <v>6</v>
       </c>
@@ -3924,7 +3895,7 @@
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
     </row>
-    <row r="113" spans="1:12" ht="20.65" thickBot="1">
+    <row r="113" spans="1:12" ht="21" thickBot="1">
       <c r="A113" s="34">
         <v>6</v>
       </c>
@@ -3954,7 +3925,7 @@
       </c>
       <c r="L113" s="5"/>
     </row>
-    <row r="114" spans="1:12" ht="20.65" thickBot="1">
+    <row r="114" spans="1:12" ht="21" thickBot="1">
       <c r="A114" s="34">
         <v>6</v>
       </c>
@@ -3984,7 +3955,7 @@
       </c>
       <c r="L114" s="5"/>
     </row>
-    <row r="115" spans="1:12" ht="20.65" thickBot="1">
+    <row r="115" spans="1:12" ht="21" thickBot="1">
       <c r="A115" s="34">
         <v>6</v>
       </c>
@@ -4014,7 +3985,7 @@
       </c>
       <c r="L115" s="5"/>
     </row>
-    <row r="116" spans="1:12" ht="20.65" thickBot="1">
+    <row r="116" spans="1:12" ht="21" thickBot="1">
       <c r="A116" s="34">
         <v>6</v>
       </c>
@@ -4044,7 +4015,7 @@
       </c>
       <c r="L116" s="5"/>
     </row>
-    <row r="117" spans="1:12" ht="20.65" thickBot="1">
+    <row r="117" spans="1:12" ht="21" thickBot="1">
       <c r="A117" s="34">
         <v>6</v>
       </c>
@@ -4074,7 +4045,7 @@
       </c>
       <c r="L117" s="5"/>
     </row>
-    <row r="118" spans="1:12" ht="20.65" thickBot="1">
+    <row r="118" spans="1:12" ht="21" thickBot="1">
       <c r="A118" s="34">
         <v>6</v>
       </c>
@@ -4104,7 +4075,7 @@
       </c>
       <c r="L118" s="5"/>
     </row>
-    <row r="119" spans="1:12" ht="20.65" thickBot="1">
+    <row r="119" spans="1:12" ht="21" thickBot="1">
       <c r="A119" s="34">
         <v>6</v>
       </c>
@@ -4134,7 +4105,7 @@
       </c>
       <c r="L119" s="5"/>
     </row>
-    <row r="120" spans="1:12" ht="20.65" thickBot="1">
+    <row r="120" spans="1:12" ht="21" thickBot="1">
       <c r="A120" s="34">
         <v>6</v>
       </c>
@@ -4164,7 +4135,7 @@
       </c>
       <c r="L120" s="5"/>
     </row>
-    <row r="121" spans="1:12" ht="20.65" thickBot="1">
+    <row r="121" spans="1:12" ht="21" thickBot="1">
       <c r="A121" s="34">
         <v>6</v>
       </c>
@@ -4194,7 +4165,7 @@
       </c>
       <c r="L121" s="5"/>
     </row>
-    <row r="122" spans="1:12" ht="20.65" thickBot="1">
+    <row r="122" spans="1:12" ht="21" thickBot="1">
       <c r="A122" s="34">
         <v>6</v>
       </c>
@@ -4224,7 +4195,7 @@
       </c>
       <c r="L122" s="5"/>
     </row>
-    <row r="123" spans="1:12" ht="20.65" thickBot="1">
+    <row r="123" spans="1:12" ht="21" thickBot="1">
       <c r="A123" s="34">
         <v>6</v>
       </c>
@@ -4254,7 +4225,7 @@
       </c>
       <c r="L123" s="5"/>
     </row>
-    <row r="124" spans="1:12" ht="20.65" thickBot="1">
+    <row r="124" spans="1:12" ht="21" thickBot="1">
       <c r="A124" s="34">
         <v>6</v>
       </c>
@@ -4284,7 +4255,7 @@
       </c>
       <c r="L124" s="5"/>
     </row>
-    <row r="125" spans="1:12" ht="20.65" thickBot="1">
+    <row r="125" spans="1:12" ht="21" thickBot="1">
       <c r="A125" s="34">
         <v>6</v>
       </c>
@@ -4314,7 +4285,7 @@
       </c>
       <c r="L125" s="5"/>
     </row>
-    <row r="126" spans="1:12" ht="20.65" thickBot="1">
+    <row r="126" spans="1:12" ht="21" thickBot="1">
       <c r="A126" s="34">
         <v>6</v>
       </c>
@@ -4344,7 +4315,7 @@
       </c>
       <c r="L126" s="5"/>
     </row>
-    <row r="127" spans="1:12" ht="20.65" thickBot="1">
+    <row r="127" spans="1:12" ht="21" thickBot="1">
       <c r="A127" s="34">
         <v>6</v>
       </c>
@@ -4374,7 +4345,7 @@
       </c>
       <c r="L127" s="5"/>
     </row>
-    <row r="128" spans="1:12" ht="20.65" thickBot="1">
+    <row r="128" spans="1:12" ht="21" thickBot="1">
       <c r="A128" s="34">
         <v>6</v>
       </c>
@@ -4404,7 +4375,7 @@
       </c>
       <c r="L128" s="5"/>
     </row>
-    <row r="129" spans="1:13" ht="20.65" thickBot="1">
+    <row r="129" spans="1:13" ht="21" thickBot="1">
       <c r="A129" s="34">
         <v>6</v>
       </c>
@@ -4434,7 +4405,7 @@
       </c>
       <c r="L129" s="5"/>
     </row>
-    <row r="130" spans="1:13" ht="20.65" thickBot="1">
+    <row r="130" spans="1:13" ht="21" thickBot="1">
       <c r="A130" s="34">
         <v>6</v>
       </c>
@@ -4465,7 +4436,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" ht="20.65" thickBot="1">
+    <row r="131" spans="1:13" ht="21" thickBot="1">
       <c r="A131" s="34">
         <v>6</v>
       </c>
@@ -5194,7 +5165,7 @@
         <v>136</v>
       </c>
       <c r="J154" s="14" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="5"/>
@@ -5858,7 +5829,7 @@
         <v>57</v>
       </c>
       <c r="J176" s="14" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="5"/>
@@ -7183,7 +7154,7 @@
       </c>
       <c r="L220" s="5"/>
     </row>
-    <row r="221" spans="1:12" ht="20.65" thickBot="1">
+    <row r="221" spans="1:12" ht="21" thickBot="1">
       <c r="A221" s="39">
         <v>10</v>
       </c>
@@ -7213,7 +7184,7 @@
       </c>
       <c r="L221" s="5"/>
     </row>
-    <row r="222" spans="1:12" ht="20.65" thickBot="1">
+    <row r="222" spans="1:12" ht="21" thickBot="1">
       <c r="A222" s="41">
         <v>11</v>
       </c>
@@ -7243,7 +7214,7 @@
       </c>
       <c r="L222" s="5"/>
     </row>
-    <row r="223" spans="1:12" ht="20.65" thickBot="1">
+    <row r="223" spans="1:12" ht="21" thickBot="1">
       <c r="A223" s="42">
         <v>11</v>
       </c>
@@ -7273,7 +7244,7 @@
       </c>
       <c r="L223" s="5"/>
     </row>
-    <row r="224" spans="1:12" ht="20.65" thickBot="1">
+    <row r="224" spans="1:12" ht="21" thickBot="1">
       <c r="A224" s="42">
         <v>11</v>
       </c>
@@ -7303,7 +7274,7 @@
       </c>
       <c r="L224" s="5"/>
     </row>
-    <row r="225" spans="1:12" ht="20.65" thickBot="1">
+    <row r="225" spans="1:12" ht="21" thickBot="1">
       <c r="A225" s="42">
         <v>11</v>
       </c>
@@ -7333,7 +7304,7 @@
       </c>
       <c r="L225" s="5"/>
     </row>
-    <row r="226" spans="1:12" ht="20.65" thickBot="1">
+    <row r="226" spans="1:12" ht="21" thickBot="1">
       <c r="A226" s="42">
         <v>11</v>
       </c>
@@ -7363,7 +7334,7 @@
       </c>
       <c r="L226" s="5"/>
     </row>
-    <row r="227" spans="1:12" ht="20.65" thickBot="1">
+    <row r="227" spans="1:12" ht="21" thickBot="1">
       <c r="A227" s="42">
         <v>11</v>
       </c>
@@ -7393,7 +7364,7 @@
       </c>
       <c r="L227" s="5"/>
     </row>
-    <row r="228" spans="1:12" ht="20.65" thickBot="1">
+    <row r="228" spans="1:12" ht="21" thickBot="1">
       <c r="A228" s="42">
         <v>11</v>
       </c>
@@ -7423,7 +7394,7 @@
       </c>
       <c r="L228" s="5"/>
     </row>
-    <row r="229" spans="1:12" ht="20.65" thickBot="1">
+    <row r="229" spans="1:12" ht="21" thickBot="1">
       <c r="A229" s="42">
         <v>11</v>
       </c>
@@ -7852,8 +7823,8 @@
       <c r="C243" s="26">
         <v>14.126315789473599</v>
       </c>
-      <c r="D243" s="14" t="s">
-        <v>34</v>
+      <c r="D243" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E243" s="14">
         <v>2011</v>
@@ -7881,8 +7852,8 @@
       <c r="C244" s="26">
         <v>29.536842105263101</v>
       </c>
-      <c r="D244" s="14" t="s">
-        <v>35</v>
+      <c r="D244" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E244" s="14">
         <v>2011</v>
@@ -7910,8 +7881,8 @@
       <c r="C245" s="26">
         <v>36.385964912280599</v>
       </c>
-      <c r="D245" s="14" t="s">
-        <v>36</v>
+      <c r="D245" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E245" s="14">
         <v>2011</v>
@@ -7939,8 +7910,8 @@
       <c r="C246" s="26">
         <v>48.371929824561299</v>
       </c>
-      <c r="D246" s="14" t="s">
-        <v>37</v>
+      <c r="D246" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E246" s="14">
         <v>2011</v>
@@ -7968,8 +7939,8 @@
       <c r="C247" s="26">
         <v>62.926315789473598</v>
       </c>
-      <c r="D247" s="14" t="s">
-        <v>38</v>
+      <c r="D247" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E247" s="14">
         <v>2011</v>
@@ -7997,8 +7968,8 @@
       <c r="C248" s="26">
         <v>77.480701754385905</v>
       </c>
-      <c r="D248" s="14" t="s">
-        <v>39</v>
+      <c r="D248" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E248" s="14">
         <v>2011</v>
@@ -8026,8 +7997,8 @@
       <c r="C249" s="26">
         <v>89.894736842105203</v>
       </c>
-      <c r="D249" s="14" t="s">
-        <v>40</v>
+      <c r="D249" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E249" s="14">
         <v>2011</v>
@@ -8055,8 +8026,8 @@
       <c r="C250" s="26">
         <v>104.87719298245599</v>
       </c>
-      <c r="D250" s="14" t="s">
-        <v>41</v>
+      <c r="D250" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E250" s="14">
         <v>2011</v>
@@ -8074,7 +8045,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="20.65" thickBot="1">
+    <row r="251" spans="1:12" ht="21" thickBot="1">
       <c r="A251" s="48">
         <v>13</v>
       </c>
@@ -8084,8 +8055,8 @@
       <c r="C251" s="49">
         <v>121.14385964912201</v>
       </c>
-      <c r="D251" s="22" t="s">
-        <v>42</v>
+      <c r="D251" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="E251" s="22">
         <v>2011</v>
@@ -8112,14 +8083,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="109.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.265625" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="109.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.4">
+    <row r="1" spans="1:3" ht="15.75">
       <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
@@ -8130,7 +8101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.4">
+    <row r="2" spans="1:3" ht="15.75">
       <c r="A2" s="11" t="s">
         <v>30</v>
       </c>
@@ -8141,7 +8112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.4">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="6" t="s">
         <v>31</v>
       </c>
@@ -8152,7 +8123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.4">
+    <row r="4" spans="1:3" ht="15.75">
       <c r="A4" s="6" t="s">
         <v>32</v>
       </c>
@@ -8163,9 +8134,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.4">
+    <row r="5" spans="1:3" ht="15.75">
       <c r="A5" s="6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -8174,42 +8145,42 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.4">
+    <row r="6" spans="1:3" ht="15.75">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
     </row>
-    <row r="7" spans="1:3" ht="15.4">
+    <row r="7" spans="1:3" ht="15.75">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="1:3" ht="15.4">
+    <row r="8" spans="1:3" ht="15.75">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:3" ht="15.4">
+    <row r="9" spans="1:3" ht="15.75">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:3" ht="15.4">
+    <row r="10" spans="1:3" ht="15.75">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="15.4">
+    <row r="11" spans="1:3" ht="15.75">
       <c r="A11" s="6">
         <v>10</v>
       </c>

--- a/Data/Initial_Database.xlsx
+++ b/Data/Initial_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\Methane_Prediction\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F81B28-3F2E-4ECA-9A7D-966D6346C60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302AEC22-886E-4BCC-83BF-39E2898C2A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -820,23 +820,23 @@
   <dimension ref="A1:T251"/>
   <sheetFormatPr defaultRowHeight="20.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" style="14" customWidth="1"/>
     <col min="2" max="2" width="22" style="14" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" style="14" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" style="14" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="14" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" style="14" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" style="14" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="16.73046875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.73046875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="15.73046875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="19.73046875" style="14" customWidth="1"/>
+    <col min="9" max="9" width="18.59765625" style="14" customWidth="1"/>
+    <col min="10" max="10" width="11.73046875" style="14" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="16" width="9" style="1"/>
     <col min="17" max="17" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.59765625" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="9" customFormat="1" ht="81">
+    <row r="1" spans="1:20" s="9" customFormat="1" ht="60">
       <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="21" thickBot="1">
+    <row r="61" spans="1:19" ht="20.65" thickBot="1">
       <c r="A61" s="21">
         <v>3</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="21.75" thickBot="1">
+    <row r="62" spans="1:19" ht="21.4" thickBot="1">
       <c r="A62" s="23">
         <v>4</v>
       </c>
@@ -2293,7 +2293,7 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
     </row>
-    <row r="63" spans="1:19" ht="21" thickBot="1">
+    <row r="63" spans="1:19" ht="20.65" thickBot="1">
       <c r="A63" s="27">
         <v>4</v>
       </c>
@@ -2325,7 +2325,7 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
     </row>
-    <row r="64" spans="1:19" ht="21" thickBot="1">
+    <row r="64" spans="1:19" ht="20.65" thickBot="1">
       <c r="A64" s="27">
         <v>4</v>
       </c>
@@ -2357,7 +2357,7 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
     </row>
-    <row r="65" spans="1:19" ht="21" thickBot="1">
+    <row r="65" spans="1:19" ht="20.65" thickBot="1">
       <c r="A65" s="27">
         <v>4</v>
       </c>
@@ -2389,7 +2389,7 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
     </row>
-    <row r="66" spans="1:19" ht="21" thickBot="1">
+    <row r="66" spans="1:19" ht="20.65" thickBot="1">
       <c r="A66" s="27">
         <v>4</v>
       </c>
@@ -2421,7 +2421,7 @@
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
     </row>
-    <row r="67" spans="1:19" ht="21" thickBot="1">
+    <row r="67" spans="1:19" ht="20.65" thickBot="1">
       <c r="A67" s="27">
         <v>4</v>
       </c>
@@ -2453,7 +2453,7 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68" spans="1:19" ht="21" thickBot="1">
+    <row r="68" spans="1:19" ht="20.65" thickBot="1">
       <c r="A68" s="27">
         <v>4</v>
       </c>
@@ -2485,7 +2485,7 @@
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
     </row>
-    <row r="69" spans="1:19" ht="21" thickBot="1">
+    <row r="69" spans="1:19" ht="20.65" thickBot="1">
       <c r="A69" s="27">
         <v>4</v>
       </c>
@@ -2517,7 +2517,7 @@
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
     </row>
-    <row r="70" spans="1:19" ht="21" thickBot="1">
+    <row r="70" spans="1:19" ht="20.65" thickBot="1">
       <c r="A70" s="27">
         <v>4</v>
       </c>
@@ -2549,7 +2549,7 @@
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
     </row>
-    <row r="71" spans="1:19" ht="21" thickBot="1">
+    <row r="71" spans="1:19" ht="20.65" thickBot="1">
       <c r="A71" s="27">
         <v>4</v>
       </c>
@@ -2581,7 +2581,7 @@
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
     </row>
-    <row r="72" spans="1:19" ht="21" thickBot="1">
+    <row r="72" spans="1:19" ht="20.65" thickBot="1">
       <c r="A72" s="27">
         <v>4</v>
       </c>
@@ -2613,7 +2613,7 @@
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
     </row>
-    <row r="73" spans="1:19" ht="21" thickBot="1">
+    <row r="73" spans="1:19" ht="20.65" thickBot="1">
       <c r="A73" s="27">
         <v>4</v>
       </c>
@@ -2645,7 +2645,7 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
     </row>
-    <row r="74" spans="1:19" ht="21" thickBot="1">
+    <row r="74" spans="1:19" ht="20.65" thickBot="1">
       <c r="A74" s="27">
         <v>4</v>
       </c>
@@ -2677,7 +2677,7 @@
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
     </row>
-    <row r="75" spans="1:19" ht="21" thickBot="1">
+    <row r="75" spans="1:19" ht="20.65" thickBot="1">
       <c r="A75" s="27">
         <v>4</v>
       </c>
@@ -2709,7 +2709,7 @@
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
     </row>
-    <row r="76" spans="1:19" ht="21" thickBot="1">
+    <row r="76" spans="1:19" ht="20.65" thickBot="1">
       <c r="A76" s="27">
         <v>4</v>
       </c>
@@ -2741,7 +2741,7 @@
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
     </row>
-    <row r="77" spans="1:19" ht="21" thickBot="1">
+    <row r="77" spans="1:19" ht="20.65" thickBot="1">
       <c r="A77" s="27">
         <v>4</v>
       </c>
@@ -2773,7 +2773,7 @@
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
     </row>
-    <row r="78" spans="1:19" ht="21" thickBot="1">
+    <row r="78" spans="1:19" ht="20.65" thickBot="1">
       <c r="A78" s="27">
         <v>4</v>
       </c>
@@ -2805,7 +2805,7 @@
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
     </row>
-    <row r="79" spans="1:19" ht="21" thickBot="1">
+    <row r="79" spans="1:19" ht="20.65" thickBot="1">
       <c r="A79" s="27">
         <v>4</v>
       </c>
@@ -2837,7 +2837,7 @@
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
     </row>
-    <row r="80" spans="1:19" ht="21" thickBot="1">
+    <row r="80" spans="1:19" ht="20.65" thickBot="1">
       <c r="A80" s="27">
         <v>4</v>
       </c>
@@ -2869,7 +2869,7 @@
       <c r="R80" s="2"/>
       <c r="S80" s="2"/>
     </row>
-    <row r="81" spans="1:19" ht="21" thickBot="1">
+    <row r="81" spans="1:19" ht="20.65" thickBot="1">
       <c r="A81" s="27">
         <v>4</v>
       </c>
@@ -2901,7 +2901,7 @@
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
     </row>
-    <row r="82" spans="1:19" ht="21" thickBot="1">
+    <row r="82" spans="1:19" ht="20.65" thickBot="1">
       <c r="A82" s="27">
         <v>4</v>
       </c>
@@ -2933,7 +2933,7 @@
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
     </row>
-    <row r="83" spans="1:19" ht="21" thickBot="1">
+    <row r="83" spans="1:19" ht="20.65" thickBot="1">
       <c r="A83" s="27">
         <v>4</v>
       </c>
@@ -3829,7 +3829,7 @@
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
     </row>
-    <row r="111" spans="1:19" ht="21" thickBot="1">
+    <row r="111" spans="1:19" ht="20.65" thickBot="1">
       <c r="A111" s="30">
         <v>5</v>
       </c>
@@ -3862,7 +3862,7 @@
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
     </row>
-    <row r="112" spans="1:19" ht="21" thickBot="1">
+    <row r="112" spans="1:19" ht="20.65" thickBot="1">
       <c r="A112" s="31">
         <v>6</v>
       </c>
@@ -3895,7 +3895,7 @@
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
     </row>
-    <row r="113" spans="1:12" ht="21" thickBot="1">
+    <row r="113" spans="1:12" ht="20.65" thickBot="1">
       <c r="A113" s="34">
         <v>6</v>
       </c>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="L113" s="5"/>
     </row>
-    <row r="114" spans="1:12" ht="21" thickBot="1">
+    <row r="114" spans="1:12" ht="20.65" thickBot="1">
       <c r="A114" s="34">
         <v>6</v>
       </c>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="L114" s="5"/>
     </row>
-    <row r="115" spans="1:12" ht="21" thickBot="1">
+    <row r="115" spans="1:12" ht="20.65" thickBot="1">
       <c r="A115" s="34">
         <v>6</v>
       </c>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="L115" s="5"/>
     </row>
-    <row r="116" spans="1:12" ht="21" thickBot="1">
+    <row r="116" spans="1:12" ht="20.65" thickBot="1">
       <c r="A116" s="34">
         <v>6</v>
       </c>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="L116" s="5"/>
     </row>
-    <row r="117" spans="1:12" ht="21" thickBot="1">
+    <row r="117" spans="1:12" ht="20.65" thickBot="1">
       <c r="A117" s="34">
         <v>6</v>
       </c>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="L117" s="5"/>
     </row>
-    <row r="118" spans="1:12" ht="21" thickBot="1">
+    <row r="118" spans="1:12" ht="20.65" thickBot="1">
       <c r="A118" s="34">
         <v>6</v>
       </c>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L118" s="5"/>
     </row>
-    <row r="119" spans="1:12" ht="21" thickBot="1">
+    <row r="119" spans="1:12" ht="20.65" thickBot="1">
       <c r="A119" s="34">
         <v>6</v>
       </c>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="L119" s="5"/>
     </row>
-    <row r="120" spans="1:12" ht="21" thickBot="1">
+    <row r="120" spans="1:12" ht="20.65" thickBot="1">
       <c r="A120" s="34">
         <v>6</v>
       </c>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="L120" s="5"/>
     </row>
-    <row r="121" spans="1:12" ht="21" thickBot="1">
+    <row r="121" spans="1:12" ht="20.65" thickBot="1">
       <c r="A121" s="34">
         <v>6</v>
       </c>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="L121" s="5"/>
     </row>
-    <row r="122" spans="1:12" ht="21" thickBot="1">
+    <row r="122" spans="1:12" ht="20.65" thickBot="1">
       <c r="A122" s="34">
         <v>6</v>
       </c>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="L122" s="5"/>
     </row>
-    <row r="123" spans="1:12" ht="21" thickBot="1">
+    <row r="123" spans="1:12" ht="20.65" thickBot="1">
       <c r="A123" s="34">
         <v>6</v>
       </c>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="L123" s="5"/>
     </row>
-    <row r="124" spans="1:12" ht="21" thickBot="1">
+    <row r="124" spans="1:12" ht="20.65" thickBot="1">
       <c r="A124" s="34">
         <v>6</v>
       </c>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="L124" s="5"/>
     </row>
-    <row r="125" spans="1:12" ht="21" thickBot="1">
+    <row r="125" spans="1:12" ht="20.65" thickBot="1">
       <c r="A125" s="34">
         <v>6</v>
       </c>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="L125" s="5"/>
     </row>
-    <row r="126" spans="1:12" ht="21" thickBot="1">
+    <row r="126" spans="1:12" ht="20.65" thickBot="1">
       <c r="A126" s="34">
         <v>6</v>
       </c>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="L126" s="5"/>
     </row>
-    <row r="127" spans="1:12" ht="21" thickBot="1">
+    <row r="127" spans="1:12" ht="20.65" thickBot="1">
       <c r="A127" s="34">
         <v>6</v>
       </c>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="L127" s="5"/>
     </row>
-    <row r="128" spans="1:12" ht="21" thickBot="1">
+    <row r="128" spans="1:12" ht="20.65" thickBot="1">
       <c r="A128" s="34">
         <v>6</v>
       </c>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="L128" s="5"/>
     </row>
-    <row r="129" spans="1:13" ht="21" thickBot="1">
+    <row r="129" spans="1:13" ht="20.65" thickBot="1">
       <c r="A129" s="34">
         <v>6</v>
       </c>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="L129" s="5"/>
     </row>
-    <row r="130" spans="1:13" ht="21" thickBot="1">
+    <row r="130" spans="1:13" ht="20.65" thickBot="1">
       <c r="A130" s="34">
         <v>6</v>
       </c>
@@ -4436,7 +4436,7 @@
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13" ht="21" thickBot="1">
+    <row r="131" spans="1:13" ht="20.65" thickBot="1">
       <c r="A131" s="34">
         <v>6</v>
       </c>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="L220" s="5"/>
     </row>
-    <row r="221" spans="1:12" ht="21" thickBot="1">
+    <row r="221" spans="1:12" ht="20.65" thickBot="1">
       <c r="A221" s="39">
         <v>10</v>
       </c>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="L221" s="5"/>
     </row>
-    <row r="222" spans="1:12" ht="21" thickBot="1">
+    <row r="222" spans="1:12" ht="20.65" thickBot="1">
       <c r="A222" s="41">
         <v>11</v>
       </c>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="L222" s="5"/>
     </row>
-    <row r="223" spans="1:12" ht="21" thickBot="1">
+    <row r="223" spans="1:12" ht="20.65" thickBot="1">
       <c r="A223" s="42">
         <v>11</v>
       </c>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="L223" s="5"/>
     </row>
-    <row r="224" spans="1:12" ht="21" thickBot="1">
+    <row r="224" spans="1:12" ht="20.65" thickBot="1">
       <c r="A224" s="42">
         <v>11</v>
       </c>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="L224" s="5"/>
     </row>
-    <row r="225" spans="1:12" ht="21" thickBot="1">
+    <row r="225" spans="1:12" ht="20.65" thickBot="1">
       <c r="A225" s="42">
         <v>11</v>
       </c>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="L225" s="5"/>
     </row>
-    <row r="226" spans="1:12" ht="21" thickBot="1">
+    <row r="226" spans="1:12" ht="20.65" thickBot="1">
       <c r="A226" s="42">
         <v>11</v>
       </c>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="L226" s="5"/>
     </row>
-    <row r="227" spans="1:12" ht="21" thickBot="1">
+    <row r="227" spans="1:12" ht="20.65" thickBot="1">
       <c r="A227" s="42">
         <v>11</v>
       </c>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="L227" s="5"/>
     </row>
-    <row r="228" spans="1:12" ht="21" thickBot="1">
+    <row r="228" spans="1:12" ht="20.65" thickBot="1">
       <c r="A228" s="42">
         <v>11</v>
       </c>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L228" s="5"/>
     </row>
-    <row r="229" spans="1:12" ht="21" thickBot="1">
+    <row r="229" spans="1:12" ht="20.65" thickBot="1">
       <c r="A229" s="42">
         <v>11</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="21" thickBot="1">
+    <row r="251" spans="1:12" ht="20.65" thickBot="1">
       <c r="A251" s="48">
         <v>13</v>
       </c>
@@ -8083,14 +8083,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="109.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" customWidth="1"/>
+    <col min="1" max="1" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="119.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:3" ht="15.4">
       <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
@@ -8101,7 +8101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75">
+    <row r="2" spans="1:3" ht="15.4">
       <c r="A2" s="11" t="s">
         <v>30</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.4">
       <c r="A3" s="6" t="s">
         <v>31</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75">
+    <row r="4" spans="1:3" ht="15.4">
       <c r="A4" s="6" t="s">
         <v>32</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75">
+    <row r="5" spans="1:3" ht="15.4">
       <c r="A5" s="6" t="s">
         <v>34</v>
       </c>
@@ -8145,42 +8145,42 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75">
+    <row r="6" spans="1:3" ht="15.4">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
     </row>
-    <row r="7" spans="1:3" ht="15.75">
+    <row r="7" spans="1:3" ht="15.4">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="1:3" ht="15.75">
+    <row r="8" spans="1:3" ht="15.4">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:3" ht="15.75">
+    <row r="9" spans="1:3" ht="15.4">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:3" ht="15.75">
+    <row r="10" spans="1:3" ht="15.4">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="15.75">
+    <row r="11" spans="1:3" ht="15.4">
       <c r="A11" s="6">
         <v>10</v>
       </c>
